--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122802656</v>
+        <v>122805416</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480666</v>
+        <v>480631</v>
       </c>
       <c r="R2" t="n">
-        <v>7026858</v>
+        <v>7026842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +767,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,12 +793,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805210</v>
+        <v>122805987</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,56 +832,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480670</v>
+        <v>480615</v>
       </c>
       <c r="R3" t="n">
-        <v>7026876</v>
+        <v>7026767</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,11 +894,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -920,7 +905,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805416</v>
+        <v>122805210</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,36 +959,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,13 +1002,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480631</v>
+        <v>480670</v>
       </c>
       <c r="R4" t="n">
-        <v>7026842</v>
+        <v>7026876</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,6 +1040,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1042,26 +1057,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,7 +1077,7 @@
         <v>122806407</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122805987</v>
+        <v>122806449</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,13 +1240,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480615</v>
+        <v>480607</v>
       </c>
       <c r="R6" t="n">
-        <v>7026767</v>
+        <v>7026875</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1332,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805780</v>
+        <v>122805346</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,13 +1367,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480659</v>
+        <v>480637</v>
       </c>
       <c r="R7" t="n">
-        <v>7026743</v>
+        <v>7026856</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1410,11 +1405,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1426,7 +1416,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1464,10 +1454,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122806449</v>
+        <v>122805780</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1504,10 +1494,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480607</v>
+        <v>480659</v>
       </c>
       <c r="R8" t="n">
-        <v>7026875</v>
+        <v>7026743</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1540,6 +1530,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1591,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122805346</v>
+        <v>122802656</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480637</v>
+        <v>480666</v>
       </c>
       <c r="R9" t="n">
-        <v>7026856</v>
+        <v>7026858</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,6 +1662,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2018,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122802625</v>
+        <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2030,42 +2030,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2073,14 +2074,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480667</v>
+        <v>480640</v>
       </c>
       <c r="R12" t="n">
-        <v>7026892</v>
+        <v>7026997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2117,7 +2118,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,12 +2127,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2149,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815560</v>
+        <v>122802625</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2161,43 +2168,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2205,14 +2211,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480640</v>
+        <v>480667</v>
       </c>
       <c r="R13" t="n">
-        <v>7026997</v>
+        <v>7026892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2249,7 +2255,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2258,18 +2264,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,6 +2285,3251 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122880098</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100621</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>480632</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7026950</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122891907</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>480588</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7026921</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122878222</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>480731</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7026971</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122891882</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>480710</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7026891</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122879071</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>480723</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7026941</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122880672</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>480679</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7026935</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122882054</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>480707</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7026891</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122879095</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>480694</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7026965</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122880310</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>480679</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7026950</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122879230</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100621</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>480678</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7026984</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122881168</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>480648</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7026848</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122882519</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>480735</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7026895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122877780</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>480713</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7026987</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122883150</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>480584</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7026773</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122880539</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>480649</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7026970</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122880817</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100621</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>480637</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7026903</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122880031</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>480624</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7026948</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122880249</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100621</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>480665</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7026974</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122880746</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>480639</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7026895</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122879519</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>480673</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7026982</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122891927</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>480619</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7026865</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122891912</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>480572</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7026904</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122891948</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>480613</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7026955</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122891969</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>480602</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7026970</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122891989</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>480640</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7026997</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805416</v>
+        <v>122805346</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480631</v>
+        <v>480637</v>
       </c>
       <c r="R2" t="n">
-        <v>7026842</v>
+        <v>7026856</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805987</v>
+        <v>122805780</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -856,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480615</v>
+        <v>480659</v>
       </c>
       <c r="R3" t="n">
-        <v>7026767</v>
+        <v>7026743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,6 +880,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +896,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -943,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805210</v>
+        <v>122806449</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,56 +950,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480670</v>
+        <v>480607</v>
       </c>
       <c r="R4" t="n">
-        <v>7026876</v>
+        <v>7026875</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1040,11 +1012,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1056,7 +1023,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1200,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122806449</v>
+        <v>122805416</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,37 +1203,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480607</v>
+        <v>480631</v>
       </c>
       <c r="R6" t="n">
-        <v>7026875</v>
+        <v>7026842</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1304,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1327,7 +1328,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805346</v>
+        <v>122802656</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480637</v>
+        <v>480666</v>
       </c>
       <c r="R7" t="n">
-        <v>7026856</v>
+        <v>7026858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,6 +1404,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,7 +1460,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805780</v>
+        <v>122805987</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1494,13 +1500,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480659</v>
+        <v>480615</v>
       </c>
       <c r="R8" t="n">
-        <v>7026743</v>
+        <v>7026767</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1532,11 +1538,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1549,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1586,10 +1587,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122802656</v>
+        <v>122805210</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,37 +1603,56 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480666</v>
+        <v>480670</v>
       </c>
       <c r="R9" t="n">
-        <v>7026858</v>
+        <v>7026876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1666,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,26 +1701,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815554</v>
+        <v>122815560</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1730,35 +1730,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1766,17 +1774,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480630</v>
+        <v>480640</v>
       </c>
       <c r="R10" t="n">
-        <v>7026966</v>
+        <v>7026997</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1810,7 +1818,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1819,6 +1827,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1829,27 +1838,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1867,7 +1856,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122805020</v>
+        <v>122815554</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1900,19 +1889,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1922,17 +1904,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480704</v>
+        <v>480630</v>
       </c>
       <c r="R11" t="n">
-        <v>7026893</v>
+        <v>7026966</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1966,7 +1948,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,6 +1965,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1995,12 +1982,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2018,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815560</v>
+        <v>122805020</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2030,43 +2017,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2074,14 +2060,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480640</v>
+        <v>480704</v>
       </c>
       <c r="R12" t="n">
-        <v>7026997</v>
+        <v>7026893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2118,7 +2104,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2127,7 +2113,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2136,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122880098</v>
+        <v>122878222</v>
       </c>
       <c r="B14" t="n">
-        <v>100621</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,31 +2299,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2337,13 +2346,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480632</v>
+        <v>480731</v>
       </c>
       <c r="R14" t="n">
-        <v>7026950</v>
+        <v>7026971</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2373,6 +2382,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2404,7 +2418,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122891907</v>
+        <v>122880746</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2438,22 +2452,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480588</v>
+        <v>480639</v>
       </c>
       <c r="R15" t="n">
-        <v>7026921</v>
+        <v>7026895</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2477,12 +2488,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2491,7 +2502,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2535,7 +2545,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122878222</v>
+        <v>122880031</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2570,7 +2580,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2594,10 +2604,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480731</v>
+        <v>480624</v>
       </c>
       <c r="R16" t="n">
-        <v>7026971</v>
+        <v>7026948</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2634,7 +2644,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2666,10 +2676,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122891882</v>
+        <v>122880249</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>100621</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2678,33 +2688,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2714,17 +2722,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480710</v>
+        <v>480665</v>
       </c>
       <c r="R17" t="n">
-        <v>7026891</v>
+        <v>7026974</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2748,17 +2756,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2772,32 +2775,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2815,10 +2793,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122879071</v>
+        <v>122881168</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2827,60 +2805,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480723</v>
+        <v>480648</v>
       </c>
       <c r="R18" t="n">
-        <v>7026941</v>
+        <v>7026848</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2914,7 +2873,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2928,7 +2887,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2946,10 +2925,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122880672</v>
+        <v>122879230</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>100621</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2958,41 +2937,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480679</v>
+        <v>480678</v>
       </c>
       <c r="R19" t="n">
-        <v>7026935</v>
+        <v>7026984</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3036,26 +3020,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3073,10 +3037,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882054</v>
+        <v>122879519</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,31 +3049,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3119,17 +3092,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480707</v>
+        <v>480673</v>
       </c>
       <c r="R20" t="n">
-        <v>7026891</v>
+        <v>7026982</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3163,7 +3136,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3178,26 +3151,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3215,7 +3168,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122879095</v>
+        <v>122880310</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3255,13 +3208,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480694</v>
+        <v>480679</v>
       </c>
       <c r="R21" t="n">
-        <v>7026965</v>
+        <v>7026950</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3304,27 +3257,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3342,10 +3275,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122880310</v>
+        <v>122880539</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3354,38 +3287,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480679</v>
+        <v>480649</v>
       </c>
       <c r="R22" t="n">
-        <v>7026950</v>
+        <v>7026970</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3418,6 +3370,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,10 +3406,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122879230</v>
+        <v>122883150</v>
       </c>
       <c r="B23" t="n">
-        <v>100621</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3461,46 +3418,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480678</v>
+        <v>480584</v>
       </c>
       <c r="R23" t="n">
-        <v>7026984</v>
+        <v>7026773</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3532,6 +3494,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3544,6 +3511,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3561,7 +3548,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122881168</v>
+        <v>122880672</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3601,10 +3588,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480648</v>
+        <v>480679</v>
       </c>
       <c r="R24" t="n">
-        <v>7026848</v>
+        <v>7026935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3639,11 +3626,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3655,7 +3637,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3670,12 +3652,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3693,10 +3675,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122882519</v>
+        <v>122891882</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3709,51 +3691,49 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480735</v>
+        <v>480710</v>
       </c>
       <c r="R25" t="n">
-        <v>7026895</v>
+        <v>7026891</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3777,17 +3757,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3804,6 +3784,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3816,12 +3801,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3839,10 +3824,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122877780</v>
+        <v>122880098</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>100621</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3851,41 +3836,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480713</v>
+        <v>480632</v>
       </c>
       <c r="R26" t="n">
-        <v>7026987</v>
+        <v>7026950</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3917,11 +3912,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3934,26 +3924,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3971,10 +3941,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122883150</v>
+        <v>122879071</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3983,31 +3953,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4017,14 +3996,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480584</v>
+        <v>480723</v>
       </c>
       <c r="R27" t="n">
-        <v>7026773</v>
+        <v>7026941</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -4061,7 +4040,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4076,26 +4055,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4113,10 +4072,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880539</v>
+        <v>122880817</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>100621</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4125,45 +4084,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4172,10 +4117,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480649</v>
+        <v>480637</v>
       </c>
       <c r="R28" t="n">
-        <v>7026970</v>
+        <v>7026903</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4208,11 +4153,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4244,10 +4184,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122880817</v>
+        <v>122882054</v>
       </c>
       <c r="B29" t="n">
-        <v>100621</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4256,46 +4196,51 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480637</v>
+        <v>480707</v>
       </c>
       <c r="R29" t="n">
-        <v>7026903</v>
+        <v>7026891</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4327,6 +4272,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4338,7 +4288,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4356,10 +4326,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122880031</v>
+        <v>122882519</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>90962</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4368,45 +4338,40 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4415,10 +4380,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480624</v>
+        <v>480735</v>
       </c>
       <c r="R30" t="n">
-        <v>7026948</v>
+        <v>7026895</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4455,7 +4420,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4469,7 +4434,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4487,10 +4472,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122880249</v>
+        <v>122877780</v>
       </c>
       <c r="B31" t="n">
-        <v>100621</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4499,51 +4484,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480665</v>
+        <v>480713</v>
       </c>
       <c r="R31" t="n">
-        <v>7026974</v>
+        <v>7026987</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4575,6 +4550,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4587,6 +4567,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,7 +4604,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880746</v>
+        <v>122891907</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -4638,19 +4638,22 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480639</v>
+        <v>480588</v>
       </c>
       <c r="R32" t="n">
-        <v>7026895</v>
+        <v>7026921</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4674,12 +4677,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4688,6 +4691,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4731,10 +4735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122879519</v>
+        <v>122879095</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,60 +4747,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480673</v>
+        <v>480694</v>
       </c>
       <c r="R33" t="n">
-        <v>7026982</v>
+        <v>7026965</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4828,11 +4813,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4845,6 +4825,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891927</v>
+        <v>122891989</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480619</v>
+        <v>480640</v>
       </c>
       <c r="R34" t="n">
-        <v>7026865</v>
+        <v>7026997</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,6 +4941,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4993,7 +4998,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122891912</v>
+        <v>122892027</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5036,10 +5041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480572</v>
+        <v>480633</v>
       </c>
       <c r="R35" t="n">
-        <v>7026904</v>
+        <v>7026985</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5072,11 +5077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5396,7 +5396,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891989</v>
+        <v>122892032</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480640</v>
+        <v>480671</v>
       </c>
       <c r="R38" t="n">
-        <v>7026997</v>
+        <v>7026952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5529,6 +5529,545 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122891912</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>480572</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7026904</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122891927</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>480619</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7026865</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122892039</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>480657</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7026989</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122892038</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Per-Olsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>480638</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7026959</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805346</v>
+        <v>122805780</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480637</v>
+        <v>480659</v>
       </c>
       <c r="R2" t="n">
-        <v>7026856</v>
+        <v>7026743</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +753,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -802,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805780</v>
+        <v>122805987</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -842,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480659</v>
+        <v>480615</v>
       </c>
       <c r="R3" t="n">
-        <v>7026743</v>
+        <v>7026767</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +885,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -934,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122806449</v>
+        <v>122805346</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480607</v>
+        <v>480637</v>
       </c>
       <c r="R4" t="n">
-        <v>7026875</v>
+        <v>7026856</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1061,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122806407</v>
+        <v>122806449</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,55 +1073,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480615</v>
+        <v>480607</v>
       </c>
       <c r="R5" t="n">
-        <v>7026855</v>
+        <v>7026875</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,11 +1139,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,6 +1151,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122805416</v>
+        <v>122802656</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,48 +1204,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480631</v>
+        <v>480666</v>
       </c>
       <c r="R6" t="n">
-        <v>7026842</v>
+        <v>7026858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,6 +1266,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1305,12 +1297,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122802656</v>
+        <v>122806407</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,41 +1332,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480666</v>
+        <v>480615</v>
       </c>
       <c r="R7" t="n">
-        <v>7026858</v>
+        <v>7026855</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1408,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,27 +1428,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1460,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805987</v>
+        <v>122805416</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,34 +1462,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480615</v>
+        <v>480631</v>
       </c>
       <c r="R8" t="n">
-        <v>7026767</v>
+        <v>7026842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815560</v>
+        <v>122815554</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1730,43 +1730,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1774,17 +1766,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480640</v>
+        <v>480630</v>
       </c>
       <c r="R10" t="n">
-        <v>7026997</v>
+        <v>7026966</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1818,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,7 +1819,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1838,7 +1829,27 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1856,7 +1867,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815554</v>
+        <v>122805020</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1889,12 +1900,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1904,17 +1922,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480630</v>
+        <v>480704</v>
       </c>
       <c r="R11" t="n">
-        <v>7026966</v>
+        <v>7026893</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1948,7 +1966,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1965,11 +1983,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1982,12 +1995,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2005,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122805020</v>
+        <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2017,42 +2030,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2060,14 +2074,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480704</v>
+        <v>480640</v>
       </c>
       <c r="R12" t="n">
-        <v>7026893</v>
+        <v>7026997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2104,7 +2118,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,6 +2127,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2121,24 +2136,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122878222</v>
+        <v>122879230</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>100623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,45 +2299,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2346,13 +2332,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480731</v>
+        <v>480678</v>
       </c>
       <c r="R14" t="n">
-        <v>7026971</v>
+        <v>7026984</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2384,11 +2370,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2400,7 +2381,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2418,10 +2399,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880746</v>
+        <v>122879519</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2430,41 +2411,60 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480639</v>
+        <v>480673</v>
       </c>
       <c r="R15" t="n">
-        <v>7026895</v>
+        <v>7026982</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2496,6 +2496,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2507,27 +2512,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2545,10 +2530,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122880031</v>
+        <v>122880098</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>100623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,40 +2542,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2604,13 +2580,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480624</v>
+        <v>480632</v>
       </c>
       <c r="R16" t="n">
-        <v>7026948</v>
+        <v>7026950</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2640,11 +2616,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2676,10 +2647,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122880249</v>
+        <v>122879095</v>
       </c>
       <c r="B17" t="n">
-        <v>100621</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2688,51 +2659,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480665</v>
+        <v>480694</v>
       </c>
       <c r="R17" t="n">
-        <v>7026974</v>
+        <v>7026965</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2775,7 +2736,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2793,10 +2774,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122881168</v>
+        <v>122882519</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2809,37 +2790,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480648</v>
+        <v>480735</v>
       </c>
       <c r="R18" t="n">
-        <v>7026848</v>
+        <v>7026895</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2873,7 +2868,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2887,7 +2882,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2902,12 +2897,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2925,10 +2920,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122879230</v>
+        <v>122880031</v>
       </c>
       <c r="B19" t="n">
-        <v>100621</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2937,31 +2932,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2970,13 +2979,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480678</v>
+        <v>480624</v>
       </c>
       <c r="R19" t="n">
-        <v>7026984</v>
+        <v>7026948</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3008,6 +3017,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3019,7 +3033,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3037,10 +3051,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122879519</v>
+        <v>122878222</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3072,7 +3086,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3096,10 +3110,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480673</v>
+        <v>480731</v>
       </c>
       <c r="R20" t="n">
-        <v>7026982</v>
+        <v>7026971</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3136,7 +3150,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3150,7 +3164,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3168,10 +3182,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122880310</v>
+        <v>122880249</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>100623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3180,41 +3194,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480679</v>
+        <v>480665</v>
       </c>
       <c r="R21" t="n">
-        <v>7026950</v>
+        <v>7026974</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3275,10 +3299,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122880539</v>
+        <v>122891907</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3287,57 +3311,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480649</v>
+        <v>480588</v>
       </c>
       <c r="R22" t="n">
-        <v>7026970</v>
+        <v>7026921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3364,17 +3372,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3383,12 +3386,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3406,7 +3430,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122883150</v>
+        <v>122891882</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3440,9 +3464,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3456,13 +3482,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480584</v>
+        <v>480710</v>
       </c>
       <c r="R23" t="n">
-        <v>7026773</v>
+        <v>7026891</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3486,17 +3512,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3513,6 +3539,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3525,12 +3556,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3548,7 +3579,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122880672</v>
+        <v>122881168</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3588,10 +3619,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480679</v>
+        <v>480648</v>
       </c>
       <c r="R24" t="n">
-        <v>7026935</v>
+        <v>7026848</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3626,6 +3657,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3637,7 +3673,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3652,12 +3688,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3675,7 +3711,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122891882</v>
+        <v>122882054</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3709,8 +3745,6 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3727,13 +3761,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480710</v>
+        <v>480707</v>
       </c>
       <c r="R25" t="n">
         <v>7026891</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3757,17 +3791,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3784,11 +3818,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3801,12 +3830,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3824,10 +3853,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122880098</v>
+        <v>122880672</v>
       </c>
       <c r="B26" t="n">
-        <v>100621</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3836,48 +3865,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480632</v>
+        <v>480679</v>
       </c>
       <c r="R26" t="n">
-        <v>7026950</v>
+        <v>7026935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3923,7 +3942,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3941,10 +3980,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122879071</v>
+        <v>122877780</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3953,60 +3992,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480723</v>
+        <v>480713</v>
       </c>
       <c r="R27" t="n">
-        <v>7026941</v>
+        <v>7026987</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4040,7 +4060,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4054,7 +4074,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4072,10 +4112,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880817</v>
+        <v>122883150</v>
       </c>
       <c r="B28" t="n">
-        <v>100621</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4084,46 +4124,51 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480637</v>
+        <v>480584</v>
       </c>
       <c r="R28" t="n">
-        <v>7026903</v>
+        <v>7026773</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4155,6 +4200,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4166,7 +4216,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,10 +4254,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122882054</v>
+        <v>122880817</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>100623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4196,51 +4266,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480707</v>
+        <v>480637</v>
       </c>
       <c r="R29" t="n">
-        <v>7026891</v>
+        <v>7026903</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4272,11 +4337,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4288,27 +4348,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4326,10 +4366,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122882519</v>
+        <v>122880539</v>
       </c>
       <c r="B30" t="n">
-        <v>90962</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4338,40 +4378,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4380,13 +4425,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480735</v>
+        <v>480649</v>
       </c>
       <c r="R30" t="n">
-        <v>7026895</v>
+        <v>7026970</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4420,7 +4465,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4434,27 +4479,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4472,10 +4497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122877780</v>
+        <v>122879071</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4484,41 +4509,60 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480713</v>
+        <v>480723</v>
       </c>
       <c r="R31" t="n">
-        <v>7026987</v>
+        <v>7026941</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4552,7 +4596,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4566,27 +4610,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,7 +4628,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122891907</v>
+        <v>122880310</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -4638,19 +4662,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480588</v>
+        <v>480679</v>
       </c>
       <c r="R32" t="n">
-        <v>7026921</v>
+        <v>7026950</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4677,12 +4698,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4691,33 +4712,12 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122879095</v>
+        <v>122880746</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480694</v>
+        <v>480639</v>
       </c>
       <c r="R33" t="n">
-        <v>7026965</v>
+        <v>7026895</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4862,7 +4862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891989</v>
+        <v>122891969</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480640</v>
+        <v>480602</v>
       </c>
       <c r="R34" t="n">
-        <v>7026997</v>
+        <v>7026970</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4941,11 +4941,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4998,7 +4993,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122892027</v>
+        <v>122891912</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5041,10 +5036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480633</v>
+        <v>480572</v>
       </c>
       <c r="R35" t="n">
-        <v>7026985</v>
+        <v>7026904</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5077,6 +5072,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891948</v>
+        <v>122892032</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480613</v>
+        <v>480671</v>
       </c>
       <c r="R36" t="n">
-        <v>7026955</v>
+        <v>7026952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122891969</v>
+        <v>122892027</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480602</v>
+        <v>480633</v>
       </c>
       <c r="R37" t="n">
-        <v>7026970</v>
+        <v>7026985</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122892032</v>
+        <v>122891989</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480671</v>
+        <v>480640</v>
       </c>
       <c r="R38" t="n">
-        <v>7026952</v>
+        <v>7026997</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891912</v>
+        <v>122891948</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480572</v>
+        <v>480613</v>
       </c>
       <c r="R39" t="n">
-        <v>7026904</v>
+        <v>7026955</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122891927</v>
+        <v>122892038</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480619</v>
+        <v>480638</v>
       </c>
       <c r="R40" t="n">
-        <v>7026865</v>
+        <v>7026959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5747,6 +5747,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5935,7 +5940,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122892038</v>
+        <v>122891927</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480638</v>
+        <v>480619</v>
       </c>
       <c r="R42" t="n">
-        <v>7026959</v>
+        <v>7026865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6014,11 +6019,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122879230</v>
+        <v>122879519</v>
       </c>
       <c r="B14" t="n">
-        <v>100623</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,31 +2299,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2332,13 +2346,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480678</v>
+        <v>480673</v>
       </c>
       <c r="R14" t="n">
-        <v>7026984</v>
+        <v>7026982</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2368,6 +2382,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2399,10 +2418,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122879519</v>
+        <v>122879230</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>100623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2411,45 +2430,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2458,13 +2463,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480673</v>
+        <v>480678</v>
       </c>
       <c r="R15" t="n">
-        <v>7026982</v>
+        <v>7026984</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2494,11 +2499,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2530,10 +2530,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122880098</v>
+        <v>122879095</v>
       </c>
       <c r="B16" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2542,51 +2542,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480632</v>
+        <v>480694</v>
       </c>
       <c r="R16" t="n">
-        <v>7026950</v>
+        <v>7026965</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2629,7 +2619,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2647,10 +2657,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122879095</v>
+        <v>122880098</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>100623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2659,41 +2669,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480694</v>
+        <v>480632</v>
       </c>
       <c r="R17" t="n">
-        <v>7026965</v>
+        <v>7026950</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2736,27 +2756,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122880672</v>
+        <v>122877780</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480679</v>
+        <v>480713</v>
       </c>
       <c r="R26" t="n">
-        <v>7026935</v>
+        <v>7026987</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3931,6 +3931,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3942,27 +3947,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3980,7 +3985,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122877780</v>
+        <v>122880672</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -4020,13 +4025,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480713</v>
+        <v>480679</v>
       </c>
       <c r="R27" t="n">
-        <v>7026987</v>
+        <v>7026935</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4058,11 +4063,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4074,27 +4074,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -1061,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122806449</v>
+        <v>122806407</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,41 +1073,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480607</v>
+        <v>480615</v>
       </c>
       <c r="R5" t="n">
-        <v>7026875</v>
+        <v>7026855</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,6 +1153,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1151,26 +1170,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1188,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122802656</v>
+        <v>122806449</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1228,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480666</v>
+        <v>480607</v>
       </c>
       <c r="R6" t="n">
-        <v>7026858</v>
+        <v>7026875</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,11 +1265,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1282,7 +1276,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,10 +1314,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122806407</v>
+        <v>122802656</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,55 +1326,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480615</v>
+        <v>480666</v>
       </c>
       <c r="R7" t="n">
-        <v>7026855</v>
+        <v>7026858</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1414,7 +1394,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1408,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -1061,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122806407</v>
+        <v>122806449</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,55 +1073,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480615</v>
+        <v>480607</v>
       </c>
       <c r="R5" t="n">
-        <v>7026855</v>
+        <v>7026875</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,11 +1139,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,6 +1151,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,7 +1188,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122806449</v>
+        <v>122802656</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1227,13 +1228,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480607</v>
+        <v>480666</v>
       </c>
       <c r="R6" t="n">
-        <v>7026875</v>
+        <v>7026858</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,6 +1266,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1276,7 +1282,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122802656</v>
+        <v>122806407</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1326,41 +1332,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480666</v>
+        <v>480615</v>
       </c>
       <c r="R7" t="n">
-        <v>7026858</v>
+        <v>7026855</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,27 +1428,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805780</v>
+        <v>122805346</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480659</v>
+        <v>480637</v>
       </c>
       <c r="R2" t="n">
-        <v>7026743</v>
+        <v>7026856</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,11 +753,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,7 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805987</v>
+        <v>122805416</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +818,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480615</v>
+        <v>480631</v>
       </c>
       <c r="R3" t="n">
-        <v>7026767</v>
+        <v>7026842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +905,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -911,12 +920,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805346</v>
+        <v>122802656</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -974,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480637</v>
+        <v>480666</v>
       </c>
       <c r="R4" t="n">
-        <v>7026856</v>
+        <v>7026858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +1019,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122806449</v>
+        <v>122806407</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,41 +1087,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480607</v>
+        <v>480615</v>
       </c>
       <c r="R5" t="n">
-        <v>7026875</v>
+        <v>7026855</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,6 +1167,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1151,26 +1184,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1188,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122802656</v>
+        <v>122805210</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,37 +1217,56 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480666</v>
+        <v>480670</v>
       </c>
       <c r="R6" t="n">
-        <v>7026858</v>
+        <v>7026876</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,7 +1300,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,26 +1315,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,10 +1332,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122806407</v>
+        <v>122805987</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,42 +1344,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
@@ -1377,10 +1375,10 @@
         <v>480615</v>
       </c>
       <c r="R7" t="n">
-        <v>7026855</v>
+        <v>7026767</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1412,11 +1410,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1428,7 +1421,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1459,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805416</v>
+        <v>122806449</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,51 +1475,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480631</v>
+        <v>480607</v>
       </c>
       <c r="R8" t="n">
-        <v>7026842</v>
+        <v>7026875</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1549,7 +1548,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1564,12 +1563,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1587,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122805210</v>
+        <v>122805780</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1603,56 +1602,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480670</v>
+        <v>480659</v>
       </c>
       <c r="R9" t="n">
-        <v>7026876</v>
+        <v>7026743</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1686,7 +1666,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,7 +1680,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815554</v>
+        <v>122805020</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1751,12 +1751,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1766,17 +1773,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480630</v>
+        <v>480704</v>
       </c>
       <c r="R10" t="n">
-        <v>7026966</v>
+        <v>7026893</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1810,7 +1817,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,11 +1834,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1844,12 +1846,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1867,7 +1869,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122805020</v>
+        <v>122802625</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1907,7 +1909,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1926,10 +1928,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480704</v>
+        <v>480667</v>
       </c>
       <c r="R11" t="n">
-        <v>7026893</v>
+        <v>7026892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1966,7 +1968,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,26 +1983,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2018,10 +2000,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815560</v>
+        <v>122815554</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2030,43 +2012,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2074,17 +2048,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480640</v>
+        <v>480630</v>
       </c>
       <c r="R12" t="n">
-        <v>7026997</v>
+        <v>7026966</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2118,7 +2092,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2127,7 +2101,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2138,7 +2111,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2149,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122802625</v>
+        <v>122815560</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,42 +2161,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2211,14 +2205,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480667</v>
+        <v>480640</v>
       </c>
       <c r="R13" t="n">
-        <v>7026892</v>
+        <v>7026997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2255,7 +2249,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,12 +2258,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122879519</v>
+        <v>122877780</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,57 +2299,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480673</v>
+        <v>480713</v>
       </c>
       <c r="R14" t="n">
-        <v>7026982</v>
+        <v>7026987</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2386,7 +2367,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2400,7 +2381,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2418,7 +2419,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122879230</v>
+        <v>122880817</v>
       </c>
       <c r="B15" t="n">
         <v>100623</v>
@@ -2463,13 +2464,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480678</v>
+        <v>480637</v>
       </c>
       <c r="R15" t="n">
-        <v>7026984</v>
+        <v>7026903</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2512,7 +2513,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2530,7 +2531,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122879095</v>
+        <v>122880672</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2570,13 +2571,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480694</v>
+        <v>480679</v>
       </c>
       <c r="R16" t="n">
-        <v>7026965</v>
+        <v>7026935</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2657,10 +2658,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122880098</v>
+        <v>122881168</v>
       </c>
       <c r="B17" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2669,48 +2670,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480632</v>
+        <v>480648</v>
       </c>
       <c r="R17" t="n">
-        <v>7026950</v>
+        <v>7026848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2745,6 +2736,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2757,6 +2753,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2774,10 +2790,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122882519</v>
+        <v>122879230</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>100623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2786,40 +2802,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2828,13 +2835,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480735</v>
+        <v>480678</v>
       </c>
       <c r="R18" t="n">
-        <v>7026895</v>
+        <v>7026984</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2866,11 +2873,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2883,26 +2885,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2920,10 +2902,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122880031</v>
+        <v>122880310</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2932,60 +2914,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480624</v>
+        <v>480679</v>
       </c>
       <c r="R19" t="n">
-        <v>7026948</v>
+        <v>7026950</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3015,11 +2978,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3182,10 +3140,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122880249</v>
+        <v>122880746</v>
       </c>
       <c r="B21" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3194,51 +3152,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480665</v>
+        <v>480639</v>
       </c>
       <c r="R21" t="n">
-        <v>7026974</v>
+        <v>7026895</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3282,6 +3230,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3299,7 +3267,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122891907</v>
+        <v>122879095</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3333,22 +3301,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480588</v>
+        <v>480694</v>
       </c>
       <c r="R22" t="n">
-        <v>7026921</v>
+        <v>7026965</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3372,12 +3337,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3386,13 +3351,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3579,10 +3543,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122881168</v>
+        <v>122882054</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3595,37 +3559,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480648</v>
+        <v>480707</v>
       </c>
       <c r="R24" t="n">
-        <v>7026848</v>
+        <v>7026891</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3659,7 +3633,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3673,7 +3647,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3688,12 +3662,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3711,10 +3685,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122882054</v>
+        <v>122879519</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3723,31 +3697,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3757,17 +3740,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480707</v>
+        <v>480673</v>
       </c>
       <c r="R25" t="n">
-        <v>7026891</v>
+        <v>7026982</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3801,7 +3784,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3816,26 +3799,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3853,10 +3816,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122877780</v>
+        <v>122883150</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3869,37 +3832,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480713</v>
+        <v>480584</v>
       </c>
       <c r="R26" t="n">
-        <v>7026987</v>
+        <v>7026773</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3933,7 +3906,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3947,27 +3920,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3985,10 +3958,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122880672</v>
+        <v>122880098</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>100623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3997,38 +3970,48 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480679</v>
+        <v>480632</v>
       </c>
       <c r="R27" t="n">
-        <v>7026935</v>
+        <v>7026950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4074,27 +4057,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4112,10 +4075,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122883150</v>
+        <v>122879071</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4124,31 +4087,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4158,14 +4130,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480584</v>
+        <v>480723</v>
       </c>
       <c r="R28" t="n">
-        <v>7026773</v>
+        <v>7026941</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4202,7 +4174,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4217,26 +4189,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4254,10 +4206,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122880817</v>
+        <v>122882519</v>
       </c>
       <c r="B29" t="n">
-        <v>100623</v>
+        <v>90962</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4266,31 +4218,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4299,13 +4260,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480637</v>
+        <v>480735</v>
       </c>
       <c r="R29" t="n">
-        <v>7026903</v>
+        <v>7026895</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4337,6 +4298,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4348,7 +4314,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4366,10 +4352,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122880539</v>
+        <v>122880249</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>100623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4378,40 +4364,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4425,13 +4402,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480649</v>
+        <v>480665</v>
       </c>
       <c r="R30" t="n">
-        <v>7026970</v>
+        <v>7026974</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4461,11 +4438,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4497,10 +4469,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122879071</v>
+        <v>122891907</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4509,60 +4481,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480723</v>
+        <v>480588</v>
       </c>
       <c r="R31" t="n">
-        <v>7026941</v>
+        <v>7026921</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4586,17 +4542,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4605,12 +4556,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4628,10 +4600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880310</v>
+        <v>122880031</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4640,41 +4612,60 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480679</v>
+        <v>480624</v>
       </c>
       <c r="R32" t="n">
-        <v>7026950</v>
+        <v>7026948</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4704,6 +4695,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4735,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122880746</v>
+        <v>122880539</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4747,41 +4743,60 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480639</v>
+        <v>480649</v>
       </c>
       <c r="R33" t="n">
-        <v>7026895</v>
+        <v>7026970</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4813,6 +4828,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4825,26 +4845,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891969</v>
+        <v>122892032</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480602</v>
+        <v>480671</v>
       </c>
       <c r="R34" t="n">
-        <v>7026970</v>
+        <v>7026952</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4941,6 +4941,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5129,7 +5134,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122892032</v>
+        <v>122891989</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480671</v>
+        <v>480640</v>
       </c>
       <c r="R36" t="n">
-        <v>7026952</v>
+        <v>7026997</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5396,7 +5401,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891989</v>
+        <v>122891927</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5439,10 +5444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480640</v>
+        <v>480619</v>
       </c>
       <c r="R38" t="n">
-        <v>7026997</v>
+        <v>7026865</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5475,11 +5480,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5668,7 +5668,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122892038</v>
+        <v>122891969</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480638</v>
+        <v>480602</v>
       </c>
       <c r="R40" t="n">
-        <v>7026959</v>
+        <v>7026970</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5747,11 +5747,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5804,7 +5799,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122892039</v>
+        <v>122892038</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480657</v>
+        <v>480638</v>
       </c>
       <c r="R41" t="n">
-        <v>7026989</v>
+        <v>7026959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5940,7 +5935,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122891927</v>
+        <v>122892039</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480619</v>
+        <v>480657</v>
       </c>
       <c r="R42" t="n">
-        <v>7026865</v>
+        <v>7026989</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6019,6 +6014,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122805210</v>
+        <v>122805987</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,56 +1217,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480670</v>
+        <v>480615</v>
       </c>
       <c r="R6" t="n">
-        <v>7026876</v>
+        <v>7026767</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,11 +1279,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1314,7 +1290,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1332,7 +1328,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805987</v>
+        <v>122806449</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1372,13 +1368,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480615</v>
+        <v>480607</v>
       </c>
       <c r="R7" t="n">
-        <v>7026767</v>
+        <v>7026875</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1421,7 +1417,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1459,7 +1455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122806449</v>
+        <v>122805780</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1499,10 +1495,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480607</v>
+        <v>480659</v>
       </c>
       <c r="R8" t="n">
-        <v>7026875</v>
+        <v>7026743</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1535,6 +1531,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,10 +1587,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122805780</v>
+        <v>122805020</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,37 +1603,56 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480659</v>
+        <v>480704</v>
       </c>
       <c r="R9" t="n">
-        <v>7026743</v>
+        <v>7026893</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1666,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,7 +1700,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1695,12 +1715,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,7 +1738,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122805020</v>
+        <v>122802625</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1758,7 +1778,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1777,10 +1797,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480704</v>
+        <v>480667</v>
       </c>
       <c r="R10" t="n">
-        <v>7026893</v>
+        <v>7026892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1817,7 +1837,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1832,26 +1852,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1902,19 +1902,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1924,17 +1917,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R11" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1968,7 +1961,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,6 +1976,31 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2000,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815554</v>
+        <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2012,35 +2030,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2048,17 +2074,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480630</v>
+        <v>480640</v>
       </c>
       <c r="R12" t="n">
-        <v>7026966</v>
+        <v>7026997</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2118,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2101,6 +2127,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2111,27 +2138,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2149,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815560</v>
+        <v>122877780</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2161,61 +2168,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480640</v>
+        <v>480713</v>
       </c>
       <c r="R13" t="n">
-        <v>7026997</v>
+        <v>7026987</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2239,17 +2226,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2258,18 +2245,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2287,10 +2288,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122877780</v>
+        <v>122880817</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>100623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,41 +2300,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480713</v>
+        <v>480637</v>
       </c>
       <c r="R14" t="n">
-        <v>7026987</v>
+        <v>7026903</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2365,11 +2371,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2382,26 +2383,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2419,10 +2400,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880817</v>
+        <v>122880672</v>
       </c>
       <c r="B15" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2431,43 +2412,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480637</v>
+        <v>480679</v>
       </c>
       <c r="R15" t="n">
-        <v>7026903</v>
+        <v>7026935</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2513,7 +2489,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2531,7 +2527,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122880672</v>
+        <v>122881168</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2571,10 +2567,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480679</v>
+        <v>480648</v>
       </c>
       <c r="R16" t="n">
-        <v>7026935</v>
+        <v>7026848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2609,6 +2605,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2620,7 +2621,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2635,12 +2636,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2658,10 +2659,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122881168</v>
+        <v>122879230</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>100623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2670,41 +2671,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480648</v>
+        <v>480678</v>
       </c>
       <c r="R17" t="n">
-        <v>7026848</v>
+        <v>7026984</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2736,11 +2742,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2752,27 +2753,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2790,10 +2771,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122879230</v>
+        <v>122880310</v>
       </c>
       <c r="B18" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2802,46 +2783,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480678</v>
+        <v>480679</v>
       </c>
       <c r="R18" t="n">
-        <v>7026984</v>
+        <v>7026950</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2884,7 +2860,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2902,10 +2878,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122880310</v>
+        <v>122878222</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2914,41 +2890,60 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480679</v>
+        <v>480731</v>
       </c>
       <c r="R19" t="n">
-        <v>7026950</v>
+        <v>7026971</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2978,6 +2973,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3009,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122878222</v>
+        <v>122880746</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,60 +3021,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480731</v>
+        <v>480639</v>
       </c>
       <c r="R20" t="n">
-        <v>7026971</v>
+        <v>7026895</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3106,11 +3087,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3123,6 +3099,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3140,7 +3136,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122880746</v>
+        <v>122879095</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3180,10 +3176,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480639</v>
+        <v>480694</v>
       </c>
       <c r="R21" t="n">
-        <v>7026895</v>
+        <v>7026965</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3229,7 +3225,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3267,10 +3263,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122879095</v>
+        <v>122891882</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3283,37 +3279,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480694</v>
+        <v>480710</v>
       </c>
       <c r="R22" t="n">
-        <v>7026965</v>
+        <v>7026891</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3337,12 +3345,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3359,6 +3372,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3371,12 +3389,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3394,7 +3412,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122891882</v>
+        <v>122882054</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3428,8 +3446,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3446,13 +3462,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480710</v>
+        <v>480707</v>
       </c>
       <c r="R23" t="n">
         <v>7026891</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3476,17 +3492,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3503,11 +3519,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3520,12 +3531,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3543,10 +3554,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122882054</v>
+        <v>122879519</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3555,31 +3566,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3589,17 +3609,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480707</v>
+        <v>480673</v>
       </c>
       <c r="R24" t="n">
-        <v>7026891</v>
+        <v>7026982</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3633,7 +3653,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3648,26 +3668,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122879519</v>
+        <v>122883150</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3697,40 +3697,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3740,17 +3731,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480673</v>
+        <v>480584</v>
       </c>
       <c r="R25" t="n">
-        <v>7026982</v>
+        <v>7026773</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3784,7 +3775,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3799,6 +3790,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3816,10 +3827,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122883150</v>
+        <v>122880098</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>100623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3828,31 +3839,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3862,17 +3873,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480584</v>
+        <v>480632</v>
       </c>
       <c r="R26" t="n">
-        <v>7026773</v>
+        <v>7026950</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3904,11 +3915,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3920,27 +3926,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3958,10 +3944,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122880098</v>
+        <v>122879071</v>
       </c>
       <c r="B27" t="n">
-        <v>100623</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3970,31 +3956,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4008,13 +4003,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480632</v>
+        <v>480723</v>
       </c>
       <c r="R27" t="n">
-        <v>7026950</v>
+        <v>7026941</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4046,6 +4041,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122879071</v>
+        <v>122880249</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>100623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4087,40 +4087,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4134,13 +4125,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480723</v>
+        <v>480665</v>
       </c>
       <c r="R28" t="n">
-        <v>7026941</v>
+        <v>7026974</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4172,11 +4163,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4188,7 +4174,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4352,10 +4338,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122880249</v>
+        <v>122891907</v>
       </c>
       <c r="B30" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4364,51 +4350,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480665</v>
+        <v>480588</v>
       </c>
       <c r="R30" t="n">
-        <v>7026974</v>
+        <v>7026921</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4432,12 +4411,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4446,12 +4425,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122891907</v>
+        <v>122880031</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4481,44 +4481,60 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480588</v>
+        <v>480624</v>
       </c>
       <c r="R31" t="n">
-        <v>7026921</v>
+        <v>7026948</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4542,12 +4558,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4556,33 +4577,12 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880031</v>
+        <v>122880539</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4659,13 +4659,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480624</v>
+        <v>480649</v>
       </c>
       <c r="R32" t="n">
-        <v>7026948</v>
+        <v>7026970</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4731,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122880539</v>
+        <v>122892032</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,57 +4743,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480649</v>
+        <v>480671</v>
       </c>
       <c r="R33" t="n">
-        <v>7026970</v>
+        <v>7026952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4820,17 +4804,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4839,12 +4823,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4862,7 +4867,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122892032</v>
+        <v>122891912</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4905,13 +4910,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480671</v>
+        <v>480572</v>
       </c>
       <c r="R34" t="n">
-        <v>7026952</v>
+        <v>7026904</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4998,7 +5003,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122891912</v>
+        <v>122891989</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5041,13 +5046,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480572</v>
+        <v>480640</v>
       </c>
       <c r="R35" t="n">
-        <v>7026904</v>
+        <v>7026997</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5134,7 +5139,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891989</v>
+        <v>122892027</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5177,13 +5182,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480640</v>
+        <v>480633</v>
       </c>
       <c r="R36" t="n">
-        <v>7026997</v>
+        <v>7026985</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5213,11 +5218,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5270,7 +5270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122892027</v>
+        <v>122891927</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480633</v>
+        <v>480619</v>
       </c>
       <c r="R37" t="n">
-        <v>7026985</v>
+        <v>7026865</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891927</v>
+        <v>122891948</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480619</v>
+        <v>480613</v>
       </c>
       <c r="R38" t="n">
-        <v>7026865</v>
+        <v>7026955</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5480,6 +5480,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5532,7 +5537,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891948</v>
+        <v>122891969</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5575,13 +5580,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480613</v>
+        <v>480602</v>
       </c>
       <c r="R39" t="n">
-        <v>7026955</v>
+        <v>7026970</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5611,11 +5616,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5668,7 +5668,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122891969</v>
+        <v>122892038</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480602</v>
+        <v>480638</v>
       </c>
       <c r="R40" t="n">
-        <v>7026970</v>
+        <v>7026959</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5747,6 +5747,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5799,7 +5804,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122892038</v>
+        <v>122892039</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480638</v>
+        <v>480657</v>
       </c>
       <c r="R41" t="n">
-        <v>7026959</v>
+        <v>7026989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5935,14 +5940,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122892039</v>
+        <v>122805210</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5951,40 +5956,56 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480657</v>
+        <v>480670</v>
       </c>
       <c r="R42" t="n">
-        <v>7026989</v>
+        <v>7026876</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6018,7 +6039,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Synobservation i skog med mycket höga livsmiljövärden för tretåig hackspett. Påtagligt med födosökspår. Detta är absolut en del av ett revir för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6027,33 +6048,12 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -3554,10 +3554,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122879519</v>
+        <v>122883150</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3566,40 +3566,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3609,17 +3600,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480673</v>
+        <v>480584</v>
       </c>
       <c r="R24" t="n">
-        <v>7026982</v>
+        <v>7026773</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3653,7 +3644,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3668,6 +3659,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3685,10 +3696,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122883150</v>
+        <v>122879519</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3697,31 +3708,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3731,17 +3751,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480584</v>
+        <v>480673</v>
       </c>
       <c r="R25" t="n">
-        <v>7026773</v>
+        <v>7026982</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3775,7 +3795,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3790,26 +3810,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805346</v>
+        <v>122805416</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480637</v>
+        <v>480631</v>
       </c>
       <c r="R2" t="n">
-        <v>7026856</v>
+        <v>7026842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,12 +793,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805416</v>
+        <v>122806407</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,40 +828,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -856,13 +870,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480631</v>
+        <v>480615</v>
       </c>
       <c r="R3" t="n">
-        <v>7026842</v>
+        <v>7026855</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,6 +908,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -905,27 +924,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,7 +942,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122802656</v>
+        <v>122805780</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -983,13 +982,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480666</v>
+        <v>480659</v>
       </c>
       <c r="R4" t="n">
-        <v>7026858</v>
+        <v>7026743</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,7 +1036,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1075,10 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122806407</v>
+        <v>122805987</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,42 +1086,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
@@ -1132,10 +1117,10 @@
         <v>480615</v>
       </c>
       <c r="R5" t="n">
-        <v>7026855</v>
+        <v>7026767</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,11 +1152,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1183,7 +1163,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122805987</v>
+        <v>122806449</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1241,13 +1241,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480615</v>
+        <v>480607</v>
       </c>
       <c r="R6" t="n">
-        <v>7026767</v>
+        <v>7026875</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1328,7 +1328,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122806449</v>
+        <v>122805346</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480607</v>
+        <v>480637</v>
       </c>
       <c r="R7" t="n">
-        <v>7026875</v>
+        <v>7026856</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805780</v>
+        <v>122802656</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480659</v>
+        <v>480666</v>
       </c>
       <c r="R8" t="n">
-        <v>7026743</v>
+        <v>7026858</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1587,7 +1587,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122805020</v>
+        <v>122802625</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480704</v>
+        <v>480667</v>
       </c>
       <c r="R9" t="n">
-        <v>7026893</v>
+        <v>7026892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,26 +1701,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,7 +1718,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1771,19 +1751,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1793,17 +1766,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R10" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1837,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,6 +1825,31 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1869,7 +1867,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815554</v>
+        <v>122805020</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1902,12 +1900,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1917,17 +1922,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480630</v>
+        <v>480704</v>
       </c>
       <c r="R11" t="n">
-        <v>7026966</v>
+        <v>7026893</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1961,7 +1966,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1978,11 +1983,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
         <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122877780</v>
+        <v>122891882</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2172,37 +2172,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480713</v>
+        <v>480710</v>
       </c>
       <c r="R13" t="n">
-        <v>7026987</v>
+        <v>7026891</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2226,17 +2238,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,27 +2262,32 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2288,10 +2305,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122880817</v>
+        <v>122879071</v>
       </c>
       <c r="B14" t="n">
-        <v>100623</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2300,31 +2317,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2333,13 +2364,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480637</v>
+        <v>480723</v>
       </c>
       <c r="R14" t="n">
-        <v>7026903</v>
+        <v>7026941</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2371,6 +2402,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2382,7 +2418,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2400,7 +2436,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880672</v>
+        <v>122880310</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2443,7 +2479,7 @@
         <v>480679</v>
       </c>
       <c r="R15" t="n">
-        <v>7026935</v>
+        <v>7026950</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2489,27 +2525,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2527,10 +2543,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122881168</v>
+        <v>122878222</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2539,41 +2555,60 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480648</v>
+        <v>480731</v>
       </c>
       <c r="R16" t="n">
-        <v>7026848</v>
+        <v>7026971</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2607,7 +2642,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2622,26 +2657,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2662,7 +2677,7 @@
         <v>122879230</v>
       </c>
       <c r="B17" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2771,10 +2786,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122880310</v>
+        <v>122880249</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2783,41 +2798,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480679</v>
+        <v>480665</v>
       </c>
       <c r="R18" t="n">
-        <v>7026950</v>
+        <v>7026974</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2878,10 +2903,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122878222</v>
+        <v>122882054</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2890,40 +2915,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2933,17 +2949,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480731</v>
+        <v>480707</v>
       </c>
       <c r="R19" t="n">
-        <v>7026971</v>
+        <v>7026891</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2977,7 +2993,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2991,7 +3007,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3009,10 +3045,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122880746</v>
+        <v>122883150</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3025,34 +3061,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480639</v>
+        <v>480584</v>
       </c>
       <c r="R20" t="n">
-        <v>7026895</v>
+        <v>7026773</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3087,6 +3133,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3098,7 +3149,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3113,12 +3164,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3136,7 +3187,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122879095</v>
+        <v>122891907</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3170,19 +3221,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480694</v>
+        <v>480588</v>
       </c>
       <c r="R21" t="n">
-        <v>7026965</v>
+        <v>7026921</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3206,12 +3260,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3220,12 +3274,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3263,10 +3318,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122891882</v>
+        <v>122877780</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,49 +3334,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480710</v>
+        <v>480713</v>
       </c>
       <c r="R22" t="n">
-        <v>7026891</v>
+        <v>7026987</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3345,17 +3388,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3369,32 +3412,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3412,10 +3450,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882054</v>
+        <v>122880539</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3424,31 +3462,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3458,17 +3505,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480707</v>
+        <v>480649</v>
       </c>
       <c r="R23" t="n">
-        <v>7026891</v>
+        <v>7026970</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3502,7 +3549,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3516,27 +3563,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3554,10 +3581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122883150</v>
+        <v>122879519</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3566,31 +3593,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3600,17 +3636,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480584</v>
+        <v>480673</v>
       </c>
       <c r="R24" t="n">
-        <v>7026773</v>
+        <v>7026982</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3644,7 +3680,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3659,26 +3695,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3696,10 +3712,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122879519</v>
+        <v>122879095</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3708,60 +3724,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480673</v>
+        <v>480694</v>
       </c>
       <c r="R25" t="n">
-        <v>7026982</v>
+        <v>7026965</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3793,11 +3790,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3810,6 +3802,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3830,7 +3842,7 @@
         <v>122880098</v>
       </c>
       <c r="B26" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3944,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122879071</v>
+        <v>122880817</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>100631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3956,45 +3968,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4003,13 +4001,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480723</v>
+        <v>480637</v>
       </c>
       <c r="R27" t="n">
-        <v>7026941</v>
+        <v>7026903</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4041,11 +4039,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4057,7 +4050,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4075,10 +4068,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880249</v>
+        <v>122881168</v>
       </c>
       <c r="B28" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4087,51 +4080,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480665</v>
+        <v>480648</v>
       </c>
       <c r="R28" t="n">
-        <v>7026974</v>
+        <v>7026848</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4163,6 +4146,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4175,6 +4163,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4192,10 +4200,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122882519</v>
+        <v>122880672</v>
       </c>
       <c r="B29" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4208,51 +4216,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480735</v>
+        <v>480679</v>
       </c>
       <c r="R29" t="n">
-        <v>7026895</v>
+        <v>7026935</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4284,11 +4278,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4315,12 +4304,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4338,10 +4327,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122891907</v>
+        <v>122882519</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4354,40 +4343,51 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480588</v>
+        <v>480735</v>
       </c>
       <c r="R30" t="n">
-        <v>7026921</v>
+        <v>7026895</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4411,12 +4411,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4425,13 +4430,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4446,12 +4450,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4472,7 +4476,7 @@
         <v>122880031</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4600,10 +4604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880539</v>
+        <v>122880746</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4612,60 +4616,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480649</v>
+        <v>480639</v>
       </c>
       <c r="R32" t="n">
-        <v>7026970</v>
+        <v>7026895</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4697,11 +4682,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4714,6 +4694,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122892032</v>
+        <v>122891912</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480671</v>
+        <v>480572</v>
       </c>
       <c r="R33" t="n">
-        <v>7026952</v>
+        <v>7026904</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891912</v>
+        <v>122891927</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480572</v>
+        <v>480619</v>
       </c>
       <c r="R34" t="n">
-        <v>7026904</v>
+        <v>7026865</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4946,11 +4946,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5003,7 +4998,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122891989</v>
+        <v>122892027</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5046,13 +5041,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480640</v>
+        <v>480633</v>
       </c>
       <c r="R35" t="n">
-        <v>7026997</v>
+        <v>7026985</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5082,11 +5077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5139,7 +5129,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122892027</v>
+        <v>122891989</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5182,13 +5172,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480633</v>
+        <v>480640</v>
       </c>
       <c r="R36" t="n">
-        <v>7026985</v>
+        <v>7026997</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5218,6 +5208,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5270,7 +5265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122891927</v>
+        <v>122892032</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5313,10 +5308,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480619</v>
+        <v>480671</v>
       </c>
       <c r="R37" t="n">
-        <v>7026865</v>
+        <v>7026952</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5349,6 +5344,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5401,7 +5401,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891948</v>
+        <v>122891969</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480613</v>
+        <v>480602</v>
       </c>
       <c r="R38" t="n">
-        <v>7026955</v>
+        <v>7026970</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5480,11 +5480,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5537,7 +5532,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891969</v>
+        <v>122892039</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5580,13 +5575,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480602</v>
+        <v>480657</v>
       </c>
       <c r="R39" t="n">
-        <v>7026970</v>
+        <v>7026989</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5616,6 +5611,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5804,7 +5804,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122892039</v>
+        <v>122891948</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480657</v>
+        <v>480613</v>
       </c>
       <c r="R41" t="n">
-        <v>7026989</v>
+        <v>7026955</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -2436,10 +2436,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880310</v>
+        <v>122878222</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2448,41 +2448,60 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480679</v>
+        <v>480731</v>
       </c>
       <c r="R15" t="n">
-        <v>7026950</v>
+        <v>7026971</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2512,6 +2531,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2543,10 +2567,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122878222</v>
+        <v>122880310</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2555,60 +2579,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480731</v>
+        <v>480679</v>
       </c>
       <c r="R16" t="n">
-        <v>7026971</v>
+        <v>7026950</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2638,11 +2643,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805416</v>
+        <v>122805987</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480631</v>
+        <v>480615</v>
       </c>
       <c r="R2" t="n">
-        <v>7026842</v>
+        <v>7026767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,7 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -793,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122806407</v>
+        <v>122802656</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,55 +814,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480615</v>
+        <v>480666</v>
       </c>
       <c r="R3" t="n">
-        <v>7026855</v>
+        <v>7026858</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +896,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805780</v>
+        <v>122805416</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,37 +950,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480659</v>
+        <v>480631</v>
       </c>
       <c r="R4" t="n">
-        <v>7026743</v>
+        <v>7026842</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,11 +1026,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1036,7 +1037,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1051,12 +1052,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1074,7 +1075,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122805987</v>
+        <v>122805346</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1114,10 +1115,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480615</v>
+        <v>480637</v>
       </c>
       <c r="R5" t="n">
-        <v>7026767</v>
+        <v>7026856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1164,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1328,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805346</v>
+        <v>122806407</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,41 +1341,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480637</v>
+        <v>480615</v>
       </c>
       <c r="R7" t="n">
-        <v>7026856</v>
+        <v>7026855</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1406,6 +1421,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1417,27 +1437,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122802656</v>
+        <v>122805780</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480666</v>
+        <v>480659</v>
       </c>
       <c r="R8" t="n">
-        <v>7026858</v>
+        <v>7026743</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1587,7 +1587,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1620,19 +1620,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1642,17 +1635,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R9" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1686,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,6 +1694,31 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,7 +1736,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815554</v>
+        <v>122802625</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1751,12 +1769,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1766,17 +1791,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480630</v>
+        <v>480667</v>
       </c>
       <c r="R10" t="n">
-        <v>7026966</v>
+        <v>7026892</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1810,7 +1835,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1825,31 +1850,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122805020</v>
+        <v>122815560</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1879,42 +1879,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1922,14 +1923,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480704</v>
+        <v>480640</v>
       </c>
       <c r="R11" t="n">
-        <v>7026893</v>
+        <v>7026997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1966,7 +1967,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1975,6 +1976,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1983,24 +1985,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2018,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815560</v>
+        <v>122805020</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2030,43 +2017,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2074,14 +2060,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480640</v>
+        <v>480704</v>
       </c>
       <c r="R12" t="n">
-        <v>7026997</v>
+        <v>7026893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2118,7 +2104,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2127,7 +2113,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2136,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122891882</v>
+        <v>122880249</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>100631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,33 +2168,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2204,17 +2202,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480710</v>
+        <v>480665</v>
       </c>
       <c r="R13" t="n">
-        <v>7026891</v>
+        <v>7026974</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2238,17 +2236,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2262,32 +2255,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2305,10 +2273,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122879071</v>
+        <v>122880310</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2317,60 +2285,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480723</v>
+        <v>480679</v>
       </c>
       <c r="R14" t="n">
-        <v>7026941</v>
+        <v>7026950</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2402,11 +2351,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2418,7 +2362,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2436,10 +2380,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122878222</v>
+        <v>122880746</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2448,60 +2392,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480731</v>
+        <v>480639</v>
       </c>
       <c r="R15" t="n">
-        <v>7026971</v>
+        <v>7026895</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2533,11 +2458,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2550,6 +2470,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2567,10 +2507,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122880310</v>
+        <v>122891882</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2583,37 +2523,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480679</v>
+        <v>480710</v>
       </c>
       <c r="R16" t="n">
-        <v>7026950</v>
+        <v>7026891</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2637,12 +2589,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2656,7 +2613,32 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2674,10 +2656,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122879230</v>
+        <v>122883150</v>
       </c>
       <c r="B17" t="n">
-        <v>100631</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,46 +2668,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480678</v>
+        <v>480584</v>
       </c>
       <c r="R17" t="n">
-        <v>7026984</v>
+        <v>7026773</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2757,6 +2744,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2769,6 +2761,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2786,10 +2798,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122880249</v>
+        <v>122879071</v>
       </c>
       <c r="B18" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2798,31 +2810,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2836,13 +2857,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480665</v>
+        <v>480723</v>
       </c>
       <c r="R18" t="n">
-        <v>7026974</v>
+        <v>7026941</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2874,6 +2895,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2885,7 +2911,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2903,10 +2929,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882054</v>
+        <v>122879230</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>100631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2915,51 +2941,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480707</v>
+        <v>480678</v>
       </c>
       <c r="R19" t="n">
-        <v>7026891</v>
+        <v>7026984</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,11 +3012,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3008,26 +3024,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3045,10 +3041,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122883150</v>
+        <v>122877780</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3061,47 +3057,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480584</v>
+        <v>480713</v>
       </c>
       <c r="R20" t="n">
-        <v>7026773</v>
+        <v>7026987</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3135,7 +3121,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3149,27 +3135,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3187,10 +3173,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122891907</v>
+        <v>122880539</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3199,41 +3185,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480588</v>
+        <v>480649</v>
       </c>
       <c r="R21" t="n">
-        <v>7026921</v>
+        <v>7026970</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3260,12 +3262,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3274,33 +3281,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3318,10 +3304,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122877780</v>
+        <v>122879519</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3330,38 +3316,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480713</v>
+        <v>480673</v>
       </c>
       <c r="R22" t="n">
-        <v>7026987</v>
+        <v>7026982</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3398,7 +3403,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3412,27 +3417,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3450,10 +3435,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122880539</v>
+        <v>122882519</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3462,45 +3447,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3509,13 +3489,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480649</v>
+        <v>480735</v>
       </c>
       <c r="R23" t="n">
-        <v>7026970</v>
+        <v>7026895</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3549,7 +3529,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3563,7 +3543,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122879519</v>
+        <v>122878222</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480673</v>
+        <v>480731</v>
       </c>
       <c r="R24" t="n">
-        <v>7026982</v>
+        <v>7026971</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122879095</v>
+        <v>122880817</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3724,41 +3724,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480694</v>
+        <v>480637</v>
       </c>
       <c r="R25" t="n">
-        <v>7026965</v>
+        <v>7026903</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3801,27 +3806,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3956,10 +3941,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122880817</v>
+        <v>122879095</v>
       </c>
       <c r="B27" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3968,46 +3953,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480637</v>
+        <v>480694</v>
       </c>
       <c r="R27" t="n">
-        <v>7026903</v>
+        <v>7026965</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4050,7 +4030,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122881168</v>
+        <v>122882054</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4084,37 +4084,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480648</v>
+        <v>480707</v>
       </c>
       <c r="R28" t="n">
-        <v>7026848</v>
+        <v>7026891</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4148,7 +4158,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4162,7 +4172,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4177,12 +4187,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4327,10 +4337,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122882519</v>
+        <v>122891907</v>
       </c>
       <c r="B30" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4343,51 +4353,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480735</v>
+        <v>480588</v>
       </c>
       <c r="R30" t="n">
-        <v>7026895</v>
+        <v>7026921</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4411,17 +4410,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4430,12 +4424,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4450,12 +4445,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4473,10 +4468,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122880031</v>
+        <v>122881168</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4485,60 +4480,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480624</v>
+        <v>480648</v>
       </c>
       <c r="R31" t="n">
-        <v>7026948</v>
+        <v>7026848</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4572,7 +4548,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4587,6 +4563,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,10 +4600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880746</v>
+        <v>122880031</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4616,41 +4612,60 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480639</v>
+        <v>480624</v>
       </c>
       <c r="R32" t="n">
-        <v>7026895</v>
+        <v>7026948</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4682,6 +4697,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4694,26 +4714,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122891912</v>
+        <v>122892039</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480572</v>
+        <v>480657</v>
       </c>
       <c r="R33" t="n">
-        <v>7026904</v>
+        <v>7026989</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891927</v>
+        <v>122892032</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480619</v>
+        <v>480671</v>
       </c>
       <c r="R34" t="n">
-        <v>7026865</v>
+        <v>7026952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4946,6 +4946,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4998,7 +5003,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122892027</v>
+        <v>122891927</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5041,13 +5046,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480633</v>
+        <v>480619</v>
       </c>
       <c r="R35" t="n">
-        <v>7026985</v>
+        <v>7026865</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5129,7 +5134,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891989</v>
+        <v>122891948</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480640</v>
+        <v>480613</v>
       </c>
       <c r="R36" t="n">
-        <v>7026997</v>
+        <v>7026955</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5265,7 +5270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122892032</v>
+        <v>122892038</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5308,10 +5313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480671</v>
+        <v>480638</v>
       </c>
       <c r="R37" t="n">
-        <v>7026952</v>
+        <v>7026959</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5401,7 +5406,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891969</v>
+        <v>122892027</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5444,10 +5449,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480602</v>
+        <v>480633</v>
       </c>
       <c r="R38" t="n">
-        <v>7026970</v>
+        <v>7026985</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5532,7 +5537,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122892039</v>
+        <v>122891969</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5575,13 +5580,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480657</v>
+        <v>480602</v>
       </c>
       <c r="R39" t="n">
-        <v>7026989</v>
+        <v>7026970</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5611,11 +5616,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5668,7 +5668,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122892038</v>
+        <v>122891912</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480638</v>
+        <v>480572</v>
       </c>
       <c r="R40" t="n">
-        <v>7026959</v>
+        <v>7026904</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122891948</v>
+        <v>122891989</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480613</v>
+        <v>480640</v>
       </c>
       <c r="R41" t="n">
-        <v>7026955</v>
+        <v>7026997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -1329,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122806407</v>
+        <v>122805780</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,55 +1341,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480615</v>
+        <v>480659</v>
       </c>
       <c r="R7" t="n">
-        <v>7026855</v>
+        <v>7026743</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1409,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,6 +1424,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1455,10 +1461,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805780</v>
+        <v>122806407</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,41 +1473,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480659</v>
+        <v>480615</v>
       </c>
       <c r="R8" t="n">
-        <v>7026743</v>
+        <v>7026855</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1535,7 +1555,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,26 +1570,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122879230</v>
+        <v>122877780</v>
       </c>
       <c r="B19" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2941,46 +2941,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480678</v>
+        <v>480713</v>
       </c>
       <c r="R19" t="n">
-        <v>7026984</v>
+        <v>7026987</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3012,6 +3007,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3023,7 +3023,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3041,10 +3061,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122877780</v>
+        <v>122880539</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3053,41 +3073,60 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480713</v>
+        <v>480649</v>
       </c>
       <c r="R20" t="n">
-        <v>7026987</v>
+        <v>7026970</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3121,7 +3160,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3136,26 +3175,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3173,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122880539</v>
+        <v>122879230</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3185,45 +3204,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3232,13 +3237,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480649</v>
+        <v>480678</v>
       </c>
       <c r="R21" t="n">
-        <v>7026970</v>
+        <v>7026984</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3270,11 +3275,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -3941,10 +3941,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122879095</v>
+        <v>122882054</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3957,34 +3957,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480694</v>
+        <v>480707</v>
       </c>
       <c r="R27" t="n">
-        <v>7026965</v>
+        <v>7026891</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -4019,6 +4029,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4045,12 +4060,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4068,10 +4083,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122882054</v>
+        <v>122879095</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4084,44 +4099,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480707</v>
+        <v>480694</v>
       </c>
       <c r="R28" t="n">
-        <v>7026891</v>
+        <v>7026965</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4156,11 +4161,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4187,12 +4187,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805987</v>
+        <v>122802656</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480615</v>
+        <v>480666</v>
       </c>
       <c r="R2" t="n">
-        <v>7026767</v>
+        <v>7026858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -802,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122802656</v>
+        <v>122805987</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -842,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480666</v>
+        <v>480615</v>
       </c>
       <c r="R3" t="n">
-        <v>7026858</v>
+        <v>7026767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +885,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805416</v>
+        <v>122805346</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,48 +950,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480631</v>
+        <v>480637</v>
       </c>
       <c r="R4" t="n">
-        <v>7026842</v>
+        <v>7026856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1052,12 +1038,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1075,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122805346</v>
+        <v>122805416</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,34 +1077,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480637</v>
+        <v>480631</v>
       </c>
       <c r="R5" t="n">
-        <v>7026856</v>
+        <v>7026842</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122806449</v>
+        <v>122805780</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1242,10 +1242,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480607</v>
+        <v>480659</v>
       </c>
       <c r="R6" t="n">
-        <v>7026875</v>
+        <v>7026743</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1278,6 +1278,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1334,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805780</v>
+        <v>122806449</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1369,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480659</v>
+        <v>480607</v>
       </c>
       <c r="R7" t="n">
-        <v>7026743</v>
+        <v>7026875</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1405,11 +1410,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1587,7 +1587,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122815554</v>
+        <v>122802625</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1620,12 +1620,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1635,17 +1642,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480630</v>
+        <v>480667</v>
       </c>
       <c r="R9" t="n">
-        <v>7026966</v>
+        <v>7026892</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,31 +1701,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1736,7 +1718,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1769,19 +1751,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1791,17 +1766,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R10" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1835,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,6 +1825,31 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815560</v>
+        <v>122805020</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1879,43 +1879,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1923,14 +1922,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480640</v>
+        <v>480704</v>
       </c>
       <c r="R11" t="n">
-        <v>7026997</v>
+        <v>7026893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,7 +1966,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,7 +1975,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1985,9 +1983,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2005,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122805020</v>
+        <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2017,42 +2030,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2060,14 +2074,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480704</v>
+        <v>480640</v>
       </c>
       <c r="R12" t="n">
-        <v>7026893</v>
+        <v>7026997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2104,7 +2118,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,6 +2127,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2121,24 +2136,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122880249</v>
+        <v>122880310</v>
       </c>
       <c r="B13" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,51 +2168,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480665</v>
+        <v>480679</v>
       </c>
       <c r="R13" t="n">
-        <v>7026974</v>
+        <v>7026950</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2273,7 +2263,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122880310</v>
+        <v>122881168</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2313,10 +2303,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480679</v>
+        <v>480648</v>
       </c>
       <c r="R14" t="n">
-        <v>7026950</v>
+        <v>7026848</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2351,6 +2341,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2363,6 +2358,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2380,10 +2395,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880746</v>
+        <v>122880098</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2392,41 +2407,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480639</v>
+        <v>480632</v>
       </c>
       <c r="R15" t="n">
-        <v>7026895</v>
+        <v>7026950</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2470,26 +2495,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2507,10 +2512,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122891882</v>
+        <v>122880539</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2519,33 +2524,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2555,17 +2567,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480710</v>
+        <v>480649</v>
       </c>
       <c r="R16" t="n">
-        <v>7026891</v>
+        <v>7026970</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2589,17 +2601,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2613,32 +2625,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2656,10 +2643,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122883150</v>
+        <v>122879095</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2672,44 +2659,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480584</v>
+        <v>480694</v>
       </c>
       <c r="R17" t="n">
-        <v>7026773</v>
+        <v>7026965</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2744,11 +2721,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2775,12 +2747,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2929,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122877780</v>
+        <v>122879230</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2941,41 +2913,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480713</v>
+        <v>480678</v>
       </c>
       <c r="R19" t="n">
-        <v>7026987</v>
+        <v>7026984</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3007,11 +2984,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3023,27 +2995,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3061,10 +3013,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122880539</v>
+        <v>122880672</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3073,57 +3025,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480649</v>
+        <v>480679</v>
       </c>
       <c r="R20" t="n">
-        <v>7026970</v>
+        <v>7026935</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3158,11 +3091,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3174,7 +3102,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3192,10 +3140,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122879230</v>
+        <v>122879519</v>
       </c>
       <c r="B21" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,31 +3152,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3237,13 +3199,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480678</v>
+        <v>480673</v>
       </c>
       <c r="R21" t="n">
-        <v>7026984</v>
+        <v>7026982</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3273,6 +3235,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3304,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122879519</v>
+        <v>122891907</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3316,60 +3283,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480673</v>
+        <v>480588</v>
       </c>
       <c r="R22" t="n">
-        <v>7026982</v>
+        <v>7026921</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3393,17 +3344,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3412,12 +3358,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3435,10 +3402,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882519</v>
+        <v>122880249</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>100631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3447,40 +3414,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3489,13 +3452,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480735</v>
+        <v>480665</v>
       </c>
       <c r="R23" t="n">
-        <v>7026895</v>
+        <v>7026974</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3527,11 +3490,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3543,27 +3501,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3581,10 +3519,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122878222</v>
+        <v>122877780</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3593,57 +3531,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480731</v>
+        <v>480713</v>
       </c>
       <c r="R24" t="n">
-        <v>7026971</v>
+        <v>7026987</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3680,7 +3599,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3695,6 +3614,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3712,10 +3651,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122880817</v>
+        <v>122882054</v>
       </c>
       <c r="B25" t="n">
-        <v>100631</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3724,46 +3663,51 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480637</v>
+        <v>480707</v>
       </c>
       <c r="R25" t="n">
-        <v>7026903</v>
+        <v>7026891</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3795,6 +3739,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3806,7 +3755,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3824,10 +3793,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122880098</v>
+        <v>122883150</v>
       </c>
       <c r="B26" t="n">
-        <v>100631</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3836,31 +3805,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3870,17 +3839,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480632</v>
+        <v>480584</v>
       </c>
       <c r="R26" t="n">
-        <v>7026950</v>
+        <v>7026773</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3912,6 +3881,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3923,7 +3897,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3941,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122882054</v>
+        <v>122880746</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3957,44 +3951,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480707</v>
+        <v>480639</v>
       </c>
       <c r="R27" t="n">
-        <v>7026891</v>
+        <v>7026895</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -4029,11 +4013,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4024,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4060,12 +4039,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4083,10 +4062,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122879095</v>
+        <v>122880817</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4095,41 +4074,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480694</v>
+        <v>480637</v>
       </c>
       <c r="R28" t="n">
-        <v>7026965</v>
+        <v>7026903</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4172,27 +4156,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4210,10 +4174,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122880672</v>
+        <v>122880031</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4222,41 +4186,60 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480679</v>
+        <v>480624</v>
       </c>
       <c r="R29" t="n">
-        <v>7026935</v>
+        <v>7026948</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4288,6 +4271,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4299,27 +4287,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4337,10 +4305,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122891907</v>
+        <v>122878222</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4349,44 +4317,60 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480588</v>
+        <v>480731</v>
       </c>
       <c r="R30" t="n">
-        <v>7026921</v>
+        <v>7026971</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4410,12 +4394,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4424,33 +4413,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4468,10 +4436,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122881168</v>
+        <v>122891882</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4484,37 +4452,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480648</v>
+        <v>480710</v>
       </c>
       <c r="R31" t="n">
-        <v>7026848</v>
+        <v>7026891</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4538,17 +4518,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4562,7 +4542,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4577,12 +4562,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4600,10 +4585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880031</v>
+        <v>122882519</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>90970</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4612,45 +4597,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4659,10 +4639,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480624</v>
+        <v>480735</v>
       </c>
       <c r="R32" t="n">
-        <v>7026948</v>
+        <v>7026895</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4699,7 +4679,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4713,7 +4693,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122892039</v>
+        <v>122892027</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480657</v>
+        <v>480633</v>
       </c>
       <c r="R33" t="n">
-        <v>7026989</v>
+        <v>7026985</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4810,11 +4810,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4867,7 +4862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122892032</v>
+        <v>122891969</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4910,13 +4905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480671</v>
+        <v>480602</v>
       </c>
       <c r="R34" t="n">
-        <v>7026952</v>
+        <v>7026970</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4946,11 +4941,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5003,7 +4993,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122891927</v>
+        <v>122892032</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5046,10 +5036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480619</v>
+        <v>480671</v>
       </c>
       <c r="R35" t="n">
-        <v>7026865</v>
+        <v>7026952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5082,6 +5072,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5134,7 +5129,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891948</v>
+        <v>122892038</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480613</v>
+        <v>480638</v>
       </c>
       <c r="R36" t="n">
-        <v>7026955</v>
+        <v>7026959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5270,7 +5265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122892038</v>
+        <v>122892039</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5313,10 +5308,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480638</v>
+        <v>480657</v>
       </c>
       <c r="R37" t="n">
-        <v>7026959</v>
+        <v>7026989</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5406,7 +5401,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122892027</v>
+        <v>122891912</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480633</v>
+        <v>480572</v>
       </c>
       <c r="R38" t="n">
-        <v>7026985</v>
+        <v>7026904</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5485,6 +5480,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5537,7 +5537,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891969</v>
+        <v>122891927</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480602</v>
+        <v>480619</v>
       </c>
       <c r="R39" t="n">
-        <v>7026970</v>
+        <v>7026865</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122891912</v>
+        <v>122891989</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480572</v>
+        <v>480640</v>
       </c>
       <c r="R40" t="n">
-        <v>7026904</v>
+        <v>7026997</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122891989</v>
+        <v>122891948</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480640</v>
+        <v>480613</v>
       </c>
       <c r="R41" t="n">
-        <v>7026997</v>
+        <v>7026955</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122802656</v>
+        <v>122805346</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480666</v>
+        <v>480637</v>
       </c>
       <c r="R2" t="n">
-        <v>7026858</v>
+        <v>7026856</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805987</v>
+        <v>122805780</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -847,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480615</v>
+        <v>480659</v>
       </c>
       <c r="R3" t="n">
-        <v>7026767</v>
+        <v>7026743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +880,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805346</v>
+        <v>122805416</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,34 +950,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480637</v>
+        <v>480631</v>
       </c>
       <c r="R4" t="n">
-        <v>7026856</v>
+        <v>7026842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,12 +1052,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122805416</v>
+        <v>122802656</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,48 +1091,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480631</v>
+        <v>480666</v>
       </c>
       <c r="R5" t="n">
-        <v>7026842</v>
+        <v>7026858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,6 +1153,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1179,12 +1184,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122805780</v>
+        <v>122806449</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1242,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480659</v>
+        <v>480607</v>
       </c>
       <c r="R6" t="n">
-        <v>7026743</v>
+        <v>7026875</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1278,11 +1283,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122806449</v>
+        <v>122806407</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,41 +1346,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480607</v>
+        <v>480615</v>
       </c>
       <c r="R7" t="n">
-        <v>7026875</v>
+        <v>7026855</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1412,6 +1426,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1424,26 +1443,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1461,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122806407</v>
+        <v>122805987</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,42 +1472,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
@@ -1518,10 +1503,10 @@
         <v>480615</v>
       </c>
       <c r="R8" t="n">
-        <v>7026855</v>
+        <v>7026767</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1553,11 +1538,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122802625</v>
+        <v>122815560</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,42 +1599,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1642,14 +1643,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480667</v>
+        <v>480640</v>
       </c>
       <c r="R9" t="n">
-        <v>7026892</v>
+        <v>7026997</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1687,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,12 +1696,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,7 +1725,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815554</v>
+        <v>122802625</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1751,12 +1758,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1766,17 +1780,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480630</v>
+        <v>480667</v>
       </c>
       <c r="R10" t="n">
-        <v>7026966</v>
+        <v>7026892</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1810,7 +1824,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1825,31 +1839,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2018,10 +2007,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815560</v>
+        <v>122815554</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2030,43 +2019,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2074,17 +2055,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480640</v>
+        <v>480630</v>
       </c>
       <c r="R12" t="n">
-        <v>7026997</v>
+        <v>7026966</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2118,7 +2099,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2127,7 +2108,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2138,7 +2118,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122880310</v>
+        <v>122880539</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,38 +2168,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480679</v>
+        <v>480649</v>
       </c>
       <c r="R13" t="n">
-        <v>7026950</v>
+        <v>7026970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,6 +2251,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2263,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122881168</v>
+        <v>122880031</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2275,41 +2299,60 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480648</v>
+        <v>480624</v>
       </c>
       <c r="R14" t="n">
-        <v>7026848</v>
+        <v>7026948</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2343,7 +2386,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2358,26 +2401,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2395,10 +2418,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880098</v>
+        <v>122883150</v>
       </c>
       <c r="B15" t="n">
-        <v>100631</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2407,31 +2430,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2441,17 +2464,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480632</v>
+        <v>480584</v>
       </c>
       <c r="R15" t="n">
-        <v>7026950</v>
+        <v>7026773</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2483,6 +2506,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2494,7 +2522,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2512,7 +2560,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122880539</v>
+        <v>122878222</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2547,7 +2595,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2571,13 +2619,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480649</v>
+        <v>480731</v>
       </c>
       <c r="R16" t="n">
-        <v>7026970</v>
+        <v>7026971</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2611,7 +2659,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2643,7 +2691,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122879095</v>
+        <v>122880310</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2683,13 +2731,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480694</v>
+        <v>480679</v>
       </c>
       <c r="R17" t="n">
-        <v>7026965</v>
+        <v>7026950</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2732,27 +2780,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2770,10 +2798,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122879071</v>
+        <v>122880817</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2782,45 +2810,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2829,13 +2843,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480723</v>
+        <v>480637</v>
       </c>
       <c r="R18" t="n">
-        <v>7026941</v>
+        <v>7026903</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2867,11 +2881,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2883,7 +2892,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122879230</v>
+        <v>122879071</v>
       </c>
       <c r="B19" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2913,31 +2922,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2946,13 +2969,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480678</v>
+        <v>480723</v>
       </c>
       <c r="R19" t="n">
-        <v>7026984</v>
+        <v>7026941</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2982,6 +3005,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3013,10 +3041,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122880672</v>
+        <v>122879519</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3025,41 +3053,60 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480679</v>
+        <v>480673</v>
       </c>
       <c r="R20" t="n">
-        <v>7026935</v>
+        <v>7026982</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3091,6 +3138,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3103,26 +3155,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3140,10 +3172,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122879519</v>
+        <v>122880746</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3152,60 +3184,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480673</v>
+        <v>480639</v>
       </c>
       <c r="R21" t="n">
-        <v>7026982</v>
+        <v>7026895</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3237,11 +3250,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3253,7 +3261,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3271,10 +3299,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122891907</v>
+        <v>122882054</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3287,40 +3315,47 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480588</v>
+        <v>480707</v>
       </c>
       <c r="R22" t="n">
-        <v>7026921</v>
+        <v>7026891</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3344,12 +3379,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3358,13 +3398,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3379,12 +3418,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3402,10 +3441,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122880249</v>
+        <v>122881168</v>
       </c>
       <c r="B23" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3414,51 +3453,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480665</v>
+        <v>480648</v>
       </c>
       <c r="R23" t="n">
-        <v>7026974</v>
+        <v>7026848</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3490,6 +3519,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3502,6 +3536,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3519,10 +3573,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122877780</v>
+        <v>122880098</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3531,41 +3585,51 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480713</v>
+        <v>480632</v>
       </c>
       <c r="R24" t="n">
-        <v>7026987</v>
+        <v>7026950</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3597,11 +3661,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3614,26 +3673,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3651,10 +3690,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122882054</v>
+        <v>122882519</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3667,47 +3706,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480707</v>
+        <v>480735</v>
       </c>
       <c r="R25" t="n">
-        <v>7026891</v>
+        <v>7026895</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3741,7 +3784,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3793,10 +3836,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122883150</v>
+        <v>122877780</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3809,47 +3852,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480584</v>
+        <v>480713</v>
       </c>
       <c r="R26" t="n">
-        <v>7026773</v>
+        <v>7026987</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3883,7 +3916,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3897,27 +3930,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3935,10 +3968,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122880746</v>
+        <v>122891882</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3951,37 +3984,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480639</v>
+        <v>480710</v>
       </c>
       <c r="R27" t="n">
-        <v>7026895</v>
+        <v>7026891</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4005,12 +4050,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4024,7 +4074,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4039,12 +4094,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4062,7 +4117,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880817</v>
+        <v>122880249</v>
       </c>
       <c r="B28" t="n">
         <v>100631</v>
@@ -4101,19 +4156,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480637</v>
+        <v>480665</v>
       </c>
       <c r="R28" t="n">
-        <v>7026903</v>
+        <v>7026974</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4174,10 +4234,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122880031</v>
+        <v>122879095</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4186,60 +4246,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480624</v>
+        <v>480694</v>
       </c>
       <c r="R29" t="n">
-        <v>7026948</v>
+        <v>7026965</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4271,11 +4312,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4287,7 +4323,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4305,10 +4361,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122878222</v>
+        <v>122891907</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4317,60 +4373,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480731</v>
+        <v>480588</v>
       </c>
       <c r="R30" t="n">
-        <v>7026971</v>
+        <v>7026921</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4394,17 +4434,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4413,12 +4448,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4436,10 +4492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122891882</v>
+        <v>122880672</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4452,49 +4508,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480710</v>
+        <v>480679</v>
       </c>
       <c r="R31" t="n">
-        <v>7026891</v>
+        <v>7026935</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4518,17 +4562,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4545,11 +4584,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4562,12 +4596,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4585,10 +4619,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122882519</v>
+        <v>122879230</v>
       </c>
       <c r="B32" t="n">
-        <v>90970</v>
+        <v>100631</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4597,40 +4631,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4639,13 +4664,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480735</v>
+        <v>480678</v>
       </c>
       <c r="R32" t="n">
-        <v>7026895</v>
+        <v>7026984</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4677,11 +4702,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4694,26 +4714,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891969</v>
+        <v>122892038</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480602</v>
+        <v>480638</v>
       </c>
       <c r="R34" t="n">
-        <v>7026970</v>
+        <v>7026959</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4941,6 +4941,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4993,7 +4998,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122892032</v>
+        <v>122891927</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5036,10 +5041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480671</v>
+        <v>480619</v>
       </c>
       <c r="R35" t="n">
-        <v>7026952</v>
+        <v>7026865</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5072,11 +5077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5129,7 +5129,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122892038</v>
+        <v>122891989</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480638</v>
+        <v>480640</v>
       </c>
       <c r="R36" t="n">
-        <v>7026959</v>
+        <v>7026997</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122892039</v>
+        <v>122891912</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5308,13 +5308,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480657</v>
+        <v>480572</v>
       </c>
       <c r="R37" t="n">
-        <v>7026989</v>
+        <v>7026904</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891912</v>
+        <v>122892039</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480572</v>
+        <v>480657</v>
       </c>
       <c r="R38" t="n">
-        <v>7026904</v>
+        <v>7026989</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891927</v>
+        <v>122892032</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480619</v>
+        <v>480671</v>
       </c>
       <c r="R39" t="n">
-        <v>7026865</v>
+        <v>7026952</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5616,6 +5616,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5668,7 +5673,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122891989</v>
+        <v>122891948</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5711,10 +5716,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480640</v>
+        <v>480613</v>
       </c>
       <c r="R40" t="n">
-        <v>7026997</v>
+        <v>7026955</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5804,7 +5809,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122891948</v>
+        <v>122891969</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5847,13 +5852,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480613</v>
+        <v>480602</v>
       </c>
       <c r="R41" t="n">
-        <v>7026955</v>
+        <v>7026970</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5883,11 +5888,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -3573,10 +3573,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122880098</v>
+        <v>122882519</v>
       </c>
       <c r="B24" t="n">
-        <v>100631</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3585,36 +3585,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3623,13 +3627,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480632</v>
+        <v>480735</v>
       </c>
       <c r="R24" t="n">
-        <v>7026950</v>
+        <v>7026895</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3661,6 +3665,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3672,7 +3681,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3690,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122882519</v>
+        <v>122880098</v>
       </c>
       <c r="B25" t="n">
-        <v>90970</v>
+        <v>100631</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3702,40 +3731,36 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3744,13 +3769,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480735</v>
+        <v>480632</v>
       </c>
       <c r="R25" t="n">
-        <v>7026895</v>
+        <v>7026950</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3782,11 +3807,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3798,27 +3818,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122880672</v>
+        <v>122879230</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4504,41 +4504,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480679</v>
+        <v>480678</v>
       </c>
       <c r="R31" t="n">
-        <v>7026935</v>
+        <v>7026984</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4582,26 +4587,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4619,10 +4604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122879230</v>
+        <v>122880672</v>
       </c>
       <c r="B32" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4631,46 +4616,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480678</v>
+        <v>480679</v>
       </c>
       <c r="R32" t="n">
-        <v>7026984</v>
+        <v>7026935</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4714,6 +4694,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -3573,10 +3573,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122882519</v>
+        <v>122880098</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>100631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3585,40 +3585,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3627,13 +3623,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480735</v>
+        <v>480632</v>
       </c>
       <c r="R24" t="n">
-        <v>7026895</v>
+        <v>7026950</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3665,11 +3661,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3681,27 +3672,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3719,10 +3690,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122880098</v>
+        <v>122882519</v>
       </c>
       <c r="B25" t="n">
-        <v>100631</v>
+        <v>90970</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,36 +3702,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3769,13 +3744,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480632</v>
+        <v>480735</v>
       </c>
       <c r="R25" t="n">
-        <v>7026950</v>
+        <v>7026895</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3807,6 +3782,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3818,7 +3798,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805346</v>
+        <v>122806449</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480637</v>
+        <v>480607</v>
       </c>
       <c r="R2" t="n">
-        <v>7026856</v>
+        <v>7026875</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -805,7 +805,7 @@
         <v>122805780</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>122805416</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122802656</v>
+        <v>122805346</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480666</v>
+        <v>480637</v>
       </c>
       <c r="R5" t="n">
-        <v>7026858</v>
+        <v>7026856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,11 +1151,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122806449</v>
+        <v>122805987</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1247,13 +1242,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480607</v>
+        <v>480615</v>
       </c>
       <c r="R6" t="n">
-        <v>7026875</v>
+        <v>7026767</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1296,7 +1291,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122806407</v>
+        <v>122802656</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,55 +1341,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480615</v>
+        <v>480666</v>
       </c>
       <c r="R7" t="n">
-        <v>7026855</v>
+        <v>7026858</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1428,7 +1409,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,7 +1423,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1460,10 +1461,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805987</v>
+        <v>122806407</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,28 +1473,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
@@ -1503,10 +1518,10 @@
         <v>480615</v>
       </c>
       <c r="R8" t="n">
-        <v>7026767</v>
+        <v>7026855</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1538,6 +1553,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1549,27 +1569,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122815560</v>
+        <v>122802625</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,43 +1599,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1643,14 +1642,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480640</v>
+        <v>480667</v>
       </c>
       <c r="R9" t="n">
-        <v>7026997</v>
+        <v>7026892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1696,18 +1695,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1725,10 +1718,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1758,19 +1751,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1780,17 +1766,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R10" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1824,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,6 +1825,31 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1859,7 +1870,7 @@
         <v>122805020</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2007,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815554</v>
+        <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2019,35 +2030,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2055,17 +2074,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480630</v>
+        <v>480640</v>
       </c>
       <c r="R12" t="n">
-        <v>7026966</v>
+        <v>7026997</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2099,7 +2118,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,6 +2127,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2118,27 +2138,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122880539</v>
+        <v>122881168</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,57 +2168,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480649</v>
+        <v>480648</v>
       </c>
       <c r="R13" t="n">
-        <v>7026970</v>
+        <v>7026848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2255,7 +2236,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2270,6 +2251,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2287,10 +2288,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122880031</v>
+        <v>122880098</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>100634</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,40 +2300,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2346,13 +2338,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480624</v>
+        <v>480632</v>
       </c>
       <c r="R14" t="n">
-        <v>7026948</v>
+        <v>7026950</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2382,11 +2374,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2418,10 +2405,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122883150</v>
+        <v>122879230</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>100634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2430,51 +2417,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480584</v>
+        <v>480678</v>
       </c>
       <c r="R15" t="n">
-        <v>7026773</v>
+        <v>7026984</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2506,11 +2488,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2523,26 +2500,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2563,7 +2520,7 @@
         <v>122878222</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2691,10 +2648,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122880310</v>
+        <v>122891907</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2725,16 +2682,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480679</v>
+        <v>480588</v>
       </c>
       <c r="R17" t="n">
-        <v>7026950</v>
+        <v>7026921</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2761,12 +2721,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2775,12 +2735,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2798,10 +2779,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122880817</v>
+        <v>122880539</v>
       </c>
       <c r="B18" t="n">
-        <v>100631</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2810,31 +2791,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2843,10 +2838,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480637</v>
+        <v>480649</v>
       </c>
       <c r="R18" t="n">
-        <v>7026903</v>
+        <v>7026970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2879,6 +2874,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2910,10 +2910,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122879071</v>
+        <v>122880746</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2922,57 +2922,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480723</v>
+        <v>480639</v>
       </c>
       <c r="R19" t="n">
-        <v>7026941</v>
+        <v>7026895</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -3007,11 +2988,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3023,7 +2999,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3041,10 +3037,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122879519</v>
+        <v>122879095</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3053,60 +3049,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480673</v>
+        <v>480694</v>
       </c>
       <c r="R20" t="n">
-        <v>7026982</v>
+        <v>7026965</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3138,11 +3115,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3155,6 +3127,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3172,10 +3164,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122880746</v>
+        <v>122879071</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3184,38 +3176,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480639</v>
+        <v>480723</v>
       </c>
       <c r="R21" t="n">
-        <v>7026895</v>
+        <v>7026941</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3250,6 +3261,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3261,27 +3277,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3299,10 +3295,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122882054</v>
+        <v>122880817</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>100634</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,51 +3307,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480707</v>
+        <v>480637</v>
       </c>
       <c r="R22" t="n">
-        <v>7026891</v>
+        <v>7026903</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3387,11 +3378,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3403,27 +3389,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3441,10 +3407,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122881168</v>
+        <v>122880249</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>100634</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3453,41 +3419,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480648</v>
+        <v>480665</v>
       </c>
       <c r="R23" t="n">
-        <v>7026848</v>
+        <v>7026974</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3519,11 +3495,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3536,26 +3507,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3573,10 +3524,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122880098</v>
+        <v>122877780</v>
       </c>
       <c r="B24" t="n">
-        <v>100631</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3585,51 +3536,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480632</v>
+        <v>480713</v>
       </c>
       <c r="R24" t="n">
-        <v>7026950</v>
+        <v>7026987</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3661,6 +3602,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3673,6 +3619,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3690,10 +3656,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122882519</v>
+        <v>122882054</v>
       </c>
       <c r="B25" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3706,51 +3672,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480735</v>
+        <v>480707</v>
       </c>
       <c r="R25" t="n">
-        <v>7026895</v>
+        <v>7026891</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3784,7 +3746,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3836,10 +3798,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122877780</v>
+        <v>122879519</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3848,38 +3810,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480713</v>
+        <v>480673</v>
       </c>
       <c r="R26" t="n">
-        <v>7026987</v>
+        <v>7026982</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3916,7 +3897,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3930,27 +3911,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3971,7 +3932,7 @@
         <v>122891882</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4117,10 +4078,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880249</v>
+        <v>122880310</v>
       </c>
       <c r="B28" t="n">
-        <v>100631</v>
+        <v>78769</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4129,51 +4090,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480665</v>
+        <v>480679</v>
       </c>
       <c r="R28" t="n">
-        <v>7026974</v>
+        <v>7026950</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4234,10 +4185,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122879095</v>
+        <v>122882519</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4250,37 +4201,51 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480694</v>
+        <v>480735</v>
       </c>
       <c r="R29" t="n">
-        <v>7026965</v>
+        <v>7026895</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4312,6 +4277,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4338,12 +4308,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4361,10 +4331,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122891907</v>
+        <v>122880031</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4373,44 +4343,60 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480588</v>
+        <v>480624</v>
       </c>
       <c r="R30" t="n">
-        <v>7026921</v>
+        <v>7026948</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4434,12 +4420,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4448,33 +4439,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4492,10 +4462,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122879230</v>
+        <v>122880672</v>
       </c>
       <c r="B31" t="n">
-        <v>100631</v>
+        <v>78769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4504,46 +4474,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480678</v>
+        <v>480679</v>
       </c>
       <c r="R31" t="n">
-        <v>7026984</v>
+        <v>7026935</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4587,6 +4552,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4604,10 +4589,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122880672</v>
+        <v>122883150</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4620,37 +4605,47 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480679</v>
+        <v>480584</v>
       </c>
       <c r="R32" t="n">
-        <v>7026935</v>
+        <v>7026773</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4682,6 +4677,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122892027</v>
+        <v>122892032</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480633</v>
+        <v>480671</v>
       </c>
       <c r="R33" t="n">
-        <v>7026985</v>
+        <v>7026952</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4810,6 +4810,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4862,10 +4867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122892038</v>
+        <v>122891989</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4905,10 +4910,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480638</v>
+        <v>480640</v>
       </c>
       <c r="R34" t="n">
-        <v>7026959</v>
+        <v>7026997</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4998,10 +5003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122891927</v>
+        <v>122892027</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5041,13 +5046,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480619</v>
+        <v>480633</v>
       </c>
       <c r="R35" t="n">
-        <v>7026865</v>
+        <v>7026985</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5129,10 +5134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891989</v>
+        <v>122891927</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480640</v>
+        <v>480619</v>
       </c>
       <c r="R36" t="n">
-        <v>7026997</v>
+        <v>7026865</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5208,11 +5213,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5265,10 +5265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122891912</v>
+        <v>122891969</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480572</v>
+        <v>480602</v>
       </c>
       <c r="R37" t="n">
-        <v>7026904</v>
+        <v>7026970</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5344,11 +5344,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5401,10 +5396,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122892039</v>
+        <v>122891912</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5444,13 +5439,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480657</v>
+        <v>480572</v>
       </c>
       <c r="R38" t="n">
-        <v>7026989</v>
+        <v>7026904</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5537,10 +5532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122892032</v>
+        <v>122891948</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5580,10 +5575,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480671</v>
+        <v>480613</v>
       </c>
       <c r="R39" t="n">
-        <v>7026952</v>
+        <v>7026955</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5673,10 +5668,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122891948</v>
+        <v>122892038</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5716,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480613</v>
+        <v>480638</v>
       </c>
       <c r="R40" t="n">
-        <v>7026955</v>
+        <v>7026959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5809,10 +5804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122891969</v>
+        <v>122892039</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5852,13 +5847,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480602</v>
+        <v>480657</v>
       </c>
       <c r="R41" t="n">
-        <v>7026970</v>
+        <v>7026989</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5888,6 +5883,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5943,7 +5943,7 @@
         <v>122805210</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122806449</v>
+        <v>122802656</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480607</v>
+        <v>480666</v>
       </c>
       <c r="R2" t="n">
-        <v>7026875</v>
+        <v>7026858</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +753,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -805,7 +810,7 @@
         <v>122805780</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122805416</v>
+        <v>122806407</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,40 +951,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -988,13 +993,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480631</v>
+        <v>480615</v>
       </c>
       <c r="R4" t="n">
-        <v>7026842</v>
+        <v>7026855</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,6 +1031,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1037,27 +1047,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1075,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122805346</v>
+        <v>122805416</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,34 +1081,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480637</v>
+        <v>480631</v>
       </c>
       <c r="R5" t="n">
-        <v>7026856</v>
+        <v>7026842</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122805987</v>
+        <v>122806449</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,13 +1246,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480615</v>
+        <v>480607</v>
       </c>
       <c r="R6" t="n">
-        <v>7026767</v>
+        <v>7026875</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1329,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122802656</v>
+        <v>122805987</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480666</v>
+        <v>480615</v>
       </c>
       <c r="R7" t="n">
-        <v>7026858</v>
+        <v>7026767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,11 +1411,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1423,7 +1422,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1461,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122806407</v>
+        <v>122805346</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,55 +1472,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480615</v>
+        <v>480637</v>
       </c>
       <c r="R8" t="n">
-        <v>7026855</v>
+        <v>7026856</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1553,11 +1538,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1620,19 +1620,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1642,17 +1635,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R9" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1686,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,6 +1694,31 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815554</v>
+        <v>122815560</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1730,35 +1748,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1766,17 +1792,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480630</v>
+        <v>480640</v>
       </c>
       <c r="R10" t="n">
-        <v>7026966</v>
+        <v>7026997</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1810,7 +1836,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1819,6 +1845,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1829,27 +1856,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1867,7 +1874,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122805020</v>
+        <v>122802625</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1907,7 +1914,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1926,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480704</v>
+        <v>480667</v>
       </c>
       <c r="R11" t="n">
-        <v>7026893</v>
+        <v>7026892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1966,7 +1973,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,26 +1988,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2018,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815560</v>
+        <v>122805020</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2030,43 +2017,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2074,14 +2060,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480640</v>
+        <v>480704</v>
       </c>
       <c r="R12" t="n">
-        <v>7026997</v>
+        <v>7026893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2118,7 +2104,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2127,7 +2113,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2136,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122881168</v>
+        <v>122880539</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,38 +2168,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480648</v>
+        <v>480649</v>
       </c>
       <c r="R13" t="n">
-        <v>7026848</v>
+        <v>7026970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2236,7 +2255,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2251,26 +2270,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2288,10 +2287,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122880098</v>
+        <v>122878222</v>
       </c>
       <c r="B14" t="n">
-        <v>100634</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2300,31 +2299,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2338,13 +2346,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480632</v>
+        <v>480731</v>
       </c>
       <c r="R14" t="n">
-        <v>7026950</v>
+        <v>7026971</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2374,6 +2382,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2405,10 +2418,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122879230</v>
+        <v>122882519</v>
       </c>
       <c r="B15" t="n">
-        <v>100634</v>
+        <v>90975</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2417,31 +2430,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2450,13 +2472,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480678</v>
+        <v>480735</v>
       </c>
       <c r="R15" t="n">
-        <v>7026984</v>
+        <v>7026895</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2488,6 +2510,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2500,6 +2527,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2517,10 +2564,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122878222</v>
+        <v>122879230</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>100636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2529,45 +2576,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2576,13 +2609,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480731</v>
+        <v>480678</v>
       </c>
       <c r="R16" t="n">
-        <v>7026971</v>
+        <v>7026984</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2614,11 +2647,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2630,7 +2658,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2648,10 +2676,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122891907</v>
+        <v>122880249</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>100636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2660,44 +2688,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480588</v>
+        <v>480665</v>
       </c>
       <c r="R17" t="n">
-        <v>7026921</v>
+        <v>7026974</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2721,12 +2756,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2735,33 +2770,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2779,10 +2793,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122880539</v>
+        <v>122880310</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2791,57 +2805,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480649</v>
+        <v>480679</v>
       </c>
       <c r="R18" t="n">
-        <v>7026970</v>
+        <v>7026950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2874,11 +2869,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2910,10 +2900,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122880746</v>
+        <v>122879095</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2950,10 +2940,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480639</v>
+        <v>480694</v>
       </c>
       <c r="R19" t="n">
-        <v>7026895</v>
+        <v>7026965</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2999,7 +2989,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3037,10 +3027,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122879095</v>
+        <v>122882054</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3053,34 +3043,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480694</v>
+        <v>480707</v>
       </c>
       <c r="R20" t="n">
-        <v>7026965</v>
+        <v>7026891</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3115,6 +3115,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3141,12 +3146,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3164,10 +3169,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122879071</v>
+        <v>122879519</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3199,7 +3204,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3223,13 +3228,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480723</v>
+        <v>480673</v>
       </c>
       <c r="R21" t="n">
-        <v>7026941</v>
+        <v>7026982</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3263,7 +3268,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3295,10 +3300,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122880817</v>
+        <v>122883150</v>
       </c>
       <c r="B22" t="n">
-        <v>100634</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3307,46 +3312,51 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480637</v>
+        <v>480584</v>
       </c>
       <c r="R22" t="n">
-        <v>7026903</v>
+        <v>7026773</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3378,6 +3388,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3389,7 +3404,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3407,10 +3442,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122880249</v>
+        <v>122880031</v>
       </c>
       <c r="B23" t="n">
-        <v>100634</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3419,31 +3454,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3457,13 +3501,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480665</v>
+        <v>480624</v>
       </c>
       <c r="R23" t="n">
-        <v>7026974</v>
+        <v>7026948</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3493,6 +3537,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3524,10 +3573,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122877780</v>
+        <v>122891882</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3540,37 +3589,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480713</v>
+        <v>480710</v>
       </c>
       <c r="R24" t="n">
-        <v>7026987</v>
+        <v>7026891</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3594,17 +3655,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3618,27 +3679,32 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3656,10 +3722,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122882054</v>
+        <v>122881168</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3672,47 +3738,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480707</v>
+        <v>480648</v>
       </c>
       <c r="R25" t="n">
-        <v>7026891</v>
+        <v>7026848</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3746,7 +3802,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3760,7 +3816,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3775,12 +3831,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3798,10 +3854,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122879519</v>
+        <v>122880672</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3810,60 +3866,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480673</v>
+        <v>480679</v>
       </c>
       <c r="R26" t="n">
-        <v>7026982</v>
+        <v>7026935</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3895,11 +3932,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3912,6 +3944,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3929,10 +3981,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122891882</v>
+        <v>122880098</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>100636</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3941,33 +3993,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3977,17 +4027,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480710</v>
+        <v>480632</v>
       </c>
       <c r="R27" t="n">
-        <v>7026891</v>
+        <v>7026950</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4011,17 +4061,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4035,32 +4080,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4078,10 +4098,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880310</v>
+        <v>122877780</v>
       </c>
       <c r="B28" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4118,13 +4138,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480679</v>
+        <v>480713</v>
       </c>
       <c r="R28" t="n">
-        <v>7026950</v>
+        <v>7026987</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4156,6 +4176,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4168,6 +4193,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,10 +4230,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122882519</v>
+        <v>122879071</v>
       </c>
       <c r="B29" t="n">
-        <v>90973</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4197,25 +4242,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4225,12 +4270,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4239,13 +4289,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480735</v>
+        <v>480723</v>
       </c>
       <c r="R29" t="n">
-        <v>7026895</v>
+        <v>7026941</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4279,7 +4329,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4294,26 +4344,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4331,10 +4361,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122880031</v>
+        <v>122880817</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>100636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4343,45 +4373,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4390,13 +4406,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480624</v>
+        <v>480637</v>
       </c>
       <c r="R30" t="n">
-        <v>7026948</v>
+        <v>7026903</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4426,11 +4442,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4462,10 +4473,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122880672</v>
+        <v>122880746</v>
       </c>
       <c r="B31" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4502,13 +4513,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480679</v>
+        <v>480639</v>
       </c>
       <c r="R31" t="n">
-        <v>7026935</v>
+        <v>7026895</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4551,7 +4562,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4589,10 +4600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122883150</v>
+        <v>122891907</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4605,47 +4616,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480584</v>
+        <v>480588</v>
       </c>
       <c r="R32" t="n">
-        <v>7026773</v>
+        <v>7026921</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4669,17 +4673,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4688,12 +4687,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122892032</v>
+        <v>122892027</v>
       </c>
       <c r="B33" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480671</v>
+        <v>480633</v>
       </c>
       <c r="R33" t="n">
-        <v>7026952</v>
+        <v>7026985</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4810,11 +4810,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4867,10 +4862,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891989</v>
+        <v>122892039</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4910,10 +4905,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480640</v>
+        <v>480657</v>
       </c>
       <c r="R34" t="n">
-        <v>7026997</v>
+        <v>7026989</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5003,10 +4998,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122892027</v>
+        <v>122892032</v>
       </c>
       <c r="B35" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5046,13 +5041,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480633</v>
+        <v>480671</v>
       </c>
       <c r="R35" t="n">
-        <v>7026985</v>
+        <v>7026952</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5082,6 +5077,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891927</v>
+        <v>122891948</v>
       </c>
       <c r="B36" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480619</v>
+        <v>480613</v>
       </c>
       <c r="R36" t="n">
-        <v>7026865</v>
+        <v>7026955</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5213,6 +5213,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5265,10 +5270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122891969</v>
+        <v>122892038</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5308,13 +5313,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480602</v>
+        <v>480638</v>
       </c>
       <c r="R37" t="n">
-        <v>7026970</v>
+        <v>7026959</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5344,6 +5349,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5396,10 +5406,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891912</v>
+        <v>122891969</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5439,10 +5449,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480572</v>
+        <v>480602</v>
       </c>
       <c r="R38" t="n">
-        <v>7026904</v>
+        <v>7026970</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5475,11 +5485,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5532,10 +5537,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891948</v>
+        <v>122891912</v>
       </c>
       <c r="B39" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5575,13 +5580,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480613</v>
+        <v>480572</v>
       </c>
       <c r="R39" t="n">
-        <v>7026955</v>
+        <v>7026904</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5668,10 +5673,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122892038</v>
+        <v>122891927</v>
       </c>
       <c r="B40" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5711,10 +5716,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480638</v>
+        <v>480619</v>
       </c>
       <c r="R40" t="n">
-        <v>7026959</v>
+        <v>7026865</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5747,11 +5752,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5804,10 +5804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122892039</v>
+        <v>122891989</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480657</v>
+        <v>480640</v>
       </c>
       <c r="R41" t="n">
-        <v>7026989</v>
+        <v>7026997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -2418,10 +2418,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122882519</v>
+        <v>122879230</v>
       </c>
       <c r="B15" t="n">
-        <v>90975</v>
+        <v>100636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2430,40 +2430,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2472,13 +2463,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480735</v>
+        <v>480678</v>
       </c>
       <c r="R15" t="n">
-        <v>7026895</v>
+        <v>7026984</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2510,11 +2501,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2527,26 +2513,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2564,7 +2530,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122879230</v>
+        <v>122880249</v>
       </c>
       <c r="B16" t="n">
         <v>100636</v>
@@ -2603,16 +2569,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480678</v>
+        <v>480665</v>
       </c>
       <c r="R16" t="n">
-        <v>7026984</v>
+        <v>7026974</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -2658,7 +2629,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2676,10 +2647,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122880249</v>
+        <v>122882519</v>
       </c>
       <c r="B17" t="n">
-        <v>100636</v>
+        <v>90975</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2688,36 +2659,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2726,13 +2701,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480665</v>
+        <v>480735</v>
       </c>
       <c r="R17" t="n">
-        <v>7026974</v>
+        <v>7026895</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2764,6 +2739,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2775,7 +2755,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122879095</v>
+        <v>122882054</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2916,34 +2916,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480694</v>
+        <v>480707</v>
       </c>
       <c r="R19" t="n">
-        <v>7026965</v>
+        <v>7026891</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2978,6 +2988,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3004,12 +3019,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3027,10 +3042,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882054</v>
+        <v>122879095</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3043,44 +3058,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480707</v>
+        <v>480694</v>
       </c>
       <c r="R20" t="n">
-        <v>7026891</v>
+        <v>7026965</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3115,11 +3120,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122802656</v>
+        <v>122805780</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480666</v>
+        <v>480659</v>
       </c>
       <c r="R2" t="n">
-        <v>7026858</v>
+        <v>7026743</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122805780</v>
+        <v>122806407</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,41 +819,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480659</v>
+        <v>480615</v>
       </c>
       <c r="R3" t="n">
-        <v>7026743</v>
+        <v>7026855</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,26 +916,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122806407</v>
+        <v>122805987</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,42 +945,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
@@ -996,10 +976,10 @@
         <v>480615</v>
       </c>
       <c r="R4" t="n">
-        <v>7026855</v>
+        <v>7026767</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,11 +1011,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1047,7 +1022,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122805416</v>
+        <v>122806449</v>
       </c>
       <c r="B5" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,51 +1076,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480631</v>
+        <v>480607</v>
       </c>
       <c r="R5" t="n">
-        <v>7026842</v>
+        <v>7026875</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,7 +1149,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1183,12 +1164,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1206,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122806449</v>
+        <v>122802656</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1246,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480607</v>
+        <v>480666</v>
       </c>
       <c r="R6" t="n">
-        <v>7026875</v>
+        <v>7026858</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,6 +1265,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1295,7 +1281,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1333,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805987</v>
+        <v>122805346</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480615</v>
+        <v>480637</v>
       </c>
       <c r="R7" t="n">
-        <v>7026767</v>
+        <v>7026856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,7 +1408,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1460,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805346</v>
+        <v>122805416</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,34 +1462,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480637</v>
+        <v>480631</v>
       </c>
       <c r="R8" t="n">
-        <v>7026856</v>
+        <v>7026842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122815554</v>
+        <v>122815560</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,35 +1599,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1635,17 +1643,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480630</v>
+        <v>480640</v>
       </c>
       <c r="R9" t="n">
-        <v>7026966</v>
+        <v>7026997</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1687,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,6 +1696,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1698,27 +1707,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1736,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815560</v>
+        <v>122802625</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1748,43 +1737,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1792,14 +1780,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480640</v>
+        <v>480667</v>
       </c>
       <c r="R10" t="n">
-        <v>7026997</v>
+        <v>7026892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1836,7 +1824,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,18 +1833,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1874,7 +1856,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1907,19 +1889,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1929,17 +1904,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R11" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1973,7 +1948,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1988,6 +1963,31 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122880539</v>
+        <v>122891882</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,40 +2168,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2211,17 +2204,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480649</v>
+        <v>480710</v>
       </c>
       <c r="R13" t="n">
-        <v>7026970</v>
+        <v>7026891</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2245,17 +2238,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2269,7 +2262,32 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2287,10 +2305,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122878222</v>
+        <v>122879095</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,60 +2317,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480731</v>
+        <v>480694</v>
       </c>
       <c r="R14" t="n">
-        <v>7026971</v>
+        <v>7026965</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2384,11 +2383,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2400,7 +2394,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2418,10 +2432,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122879230</v>
+        <v>122880746</v>
       </c>
       <c r="B15" t="n">
-        <v>100636</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2430,46 +2444,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480678</v>
+        <v>480639</v>
       </c>
       <c r="R15" t="n">
-        <v>7026984</v>
+        <v>7026895</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2512,7 +2521,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2530,10 +2559,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122880249</v>
+        <v>122891907</v>
       </c>
       <c r="B16" t="n">
-        <v>100636</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2542,51 +2571,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480665</v>
+        <v>480588</v>
       </c>
       <c r="R16" t="n">
-        <v>7026974</v>
+        <v>7026921</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2610,12 +2632,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2624,12 +2646,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2647,10 +2690,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122882519</v>
+        <v>122877780</v>
       </c>
       <c r="B17" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2663,48 +2706,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480735</v>
+        <v>480713</v>
       </c>
       <c r="R17" t="n">
-        <v>7026895</v>
+        <v>7026987</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2741,7 +2770,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2755,27 +2784,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2793,10 +2822,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122880310</v>
+        <v>122880098</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>100642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2805,35 +2834,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480679</v>
+        <v>480632</v>
       </c>
       <c r="R18" t="n">
         <v>7026950</v>
@@ -2900,10 +2939,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122882054</v>
+        <v>122880817</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>100642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2912,51 +2951,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480707</v>
+        <v>480637</v>
       </c>
       <c r="R19" t="n">
-        <v>7026891</v>
+        <v>7026903</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2988,11 +3022,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3004,27 +3033,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3042,10 +3051,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122879095</v>
+        <v>122882054</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3058,34 +3067,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480694</v>
+        <v>480707</v>
       </c>
       <c r="R20" t="n">
-        <v>7026965</v>
+        <v>7026891</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3120,6 +3139,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3146,12 +3170,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3169,10 +3193,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122879519</v>
+        <v>122883150</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3181,40 +3205,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3224,17 +3239,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480673</v>
+        <v>480584</v>
       </c>
       <c r="R21" t="n">
-        <v>7026982</v>
+        <v>7026773</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3268,7 +3283,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3283,6 +3298,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3300,10 +3335,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122883150</v>
+        <v>122878222</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3312,31 +3347,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3346,17 +3390,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480584</v>
+        <v>480731</v>
       </c>
       <c r="R22" t="n">
-        <v>7026773</v>
+        <v>7026971</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3390,7 +3434,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3404,27 +3448,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3442,10 +3466,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122880031</v>
+        <v>122881168</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3454,60 +3478,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480624</v>
+        <v>480648</v>
       </c>
       <c r="R23" t="n">
-        <v>7026948</v>
+        <v>7026848</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3541,7 +3546,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3556,6 +3561,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3573,10 +3598,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122891882</v>
+        <v>122879071</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3585,33 +3610,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3621,17 +3653,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480710</v>
+        <v>480723</v>
       </c>
       <c r="R24" t="n">
-        <v>7026891</v>
+        <v>7026941</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3655,17 +3687,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3680,31 +3712,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3722,10 +3729,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122881168</v>
+        <v>122880031</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3734,41 +3741,60 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480648</v>
+        <v>480624</v>
       </c>
       <c r="R25" t="n">
-        <v>7026848</v>
+        <v>7026948</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3802,7 +3828,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3817,26 +3843,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3854,10 +3860,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122880672</v>
+        <v>122880249</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>100642</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3866,41 +3872,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480679</v>
+        <v>480665</v>
       </c>
       <c r="R26" t="n">
-        <v>7026935</v>
+        <v>7026974</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3943,27 +3959,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3981,10 +3977,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122880098</v>
+        <v>122880310</v>
       </c>
       <c r="B27" t="n">
-        <v>100636</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3993,45 +3989,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480632</v>
+        <v>480679</v>
       </c>
       <c r="R27" t="n">
         <v>7026950</v>
@@ -4098,10 +4084,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122877780</v>
+        <v>122880672</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4138,13 +4124,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480713</v>
+        <v>480679</v>
       </c>
       <c r="R28" t="n">
-        <v>7026987</v>
+        <v>7026935</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4176,11 +4162,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4192,27 +4173,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4230,10 +4211,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122879071</v>
+        <v>122882519</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>90981</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4242,25 +4223,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4270,17 +4251,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4289,13 +4265,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480723</v>
+        <v>480735</v>
       </c>
       <c r="R29" t="n">
-        <v>7026941</v>
+        <v>7026895</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4329,7 +4305,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4344,6 +4320,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4361,10 +4357,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122880817</v>
+        <v>122879230</v>
       </c>
       <c r="B30" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4406,13 +4402,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480637</v>
+        <v>480678</v>
       </c>
       <c r="R30" t="n">
-        <v>7026903</v>
+        <v>7026984</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4455,7 +4451,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4473,10 +4469,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122880746</v>
+        <v>122880539</v>
       </c>
       <c r="B31" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4485,41 +4481,60 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480639</v>
+        <v>480649</v>
       </c>
       <c r="R31" t="n">
-        <v>7026895</v>
+        <v>7026970</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4551,6 +4566,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4563,26 +4583,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122891907</v>
+        <v>122879519</v>
       </c>
       <c r="B32" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4612,44 +4612,60 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480588</v>
+        <v>480673</v>
       </c>
       <c r="R32" t="n">
-        <v>7026921</v>
+        <v>7026982</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4673,12 +4689,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4687,33 +4708,12 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122892027</v>
+        <v>122892039</v>
       </c>
       <c r="B33" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4774,13 +4774,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480633</v>
+        <v>480657</v>
       </c>
       <c r="R33" t="n">
-        <v>7026985</v>
+        <v>7026989</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4810,6 +4810,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4862,10 +4867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122892039</v>
+        <v>122891912</v>
       </c>
       <c r="B34" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4905,13 +4910,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480657</v>
+        <v>480572</v>
       </c>
       <c r="R34" t="n">
-        <v>7026989</v>
+        <v>7026904</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4998,10 +5003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122892032</v>
+        <v>122891948</v>
       </c>
       <c r="B35" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5041,10 +5046,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480671</v>
+        <v>480613</v>
       </c>
       <c r="R35" t="n">
-        <v>7026952</v>
+        <v>7026955</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5134,10 +5139,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122891948</v>
+        <v>122892038</v>
       </c>
       <c r="B36" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5177,10 +5182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480613</v>
+        <v>480638</v>
       </c>
       <c r="R36" t="n">
-        <v>7026955</v>
+        <v>7026959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5270,10 +5275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122892038</v>
+        <v>122892027</v>
       </c>
       <c r="B37" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5313,13 +5318,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480638</v>
+        <v>480633</v>
       </c>
       <c r="R37" t="n">
-        <v>7026959</v>
+        <v>7026985</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5349,11 +5354,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5406,10 +5406,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891969</v>
+        <v>122892032</v>
       </c>
       <c r="B38" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480602</v>
+        <v>480671</v>
       </c>
       <c r="R38" t="n">
-        <v>7026970</v>
+        <v>7026952</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5485,6 +5485,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5537,10 +5542,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891912</v>
+        <v>122891989</v>
       </c>
       <c r="B39" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5580,13 +5585,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480572</v>
+        <v>480640</v>
       </c>
       <c r="R39" t="n">
-        <v>7026904</v>
+        <v>7026997</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5676,7 +5681,7 @@
         <v>122891927</v>
       </c>
       <c r="B40" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5804,10 +5809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122891989</v>
+        <v>122891969</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5847,13 +5852,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480640</v>
+        <v>480602</v>
       </c>
       <c r="R41" t="n">
-        <v>7026997</v>
+        <v>7026970</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5883,11 +5888,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122805780</v>
+        <v>122806449</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480659</v>
+        <v>480607</v>
       </c>
       <c r="R2" t="n">
-        <v>7026743</v>
+        <v>7026875</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122806407</v>
+        <v>122805780</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,55 +814,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480615</v>
+        <v>480659</v>
       </c>
       <c r="R3" t="n">
-        <v>7026855</v>
+        <v>7026743</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,7 +937,7 @@
         <v>122805987</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122806449</v>
+        <v>122806407</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,41 +1073,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480607</v>
+        <v>480615</v>
       </c>
       <c r="R5" t="n">
-        <v>7026875</v>
+        <v>7026855</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,6 +1153,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 20 st skott/stjälkar och 2 st. vinterståndare. Snötäckt fyndplats vid besökstillfället, finns sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1150,26 +1170,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122802656</v>
+        <v>122805416</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>90984</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,34 +1203,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480666</v>
+        <v>480631</v>
       </c>
       <c r="R6" t="n">
-        <v>7026858</v>
+        <v>7026842</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,11 +1279,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1296,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122805346</v>
+        <v>122802656</v>
       </c>
       <c r="B7" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1359,10 +1368,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480637</v>
+        <v>480666</v>
       </c>
       <c r="R7" t="n">
-        <v>7026856</v>
+        <v>7026858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,6 +1404,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122805416</v>
+        <v>122805346</v>
       </c>
       <c r="B8" t="n">
-        <v>90981</v>
+        <v>78775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,48 +1476,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480631</v>
+        <v>480637</v>
       </c>
       <c r="R8" t="n">
-        <v>7026842</v>
+        <v>7026856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122815560</v>
+        <v>122802625</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,43 +1599,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1643,14 +1642,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480640</v>
+        <v>480667</v>
       </c>
       <c r="R9" t="n">
-        <v>7026997</v>
+        <v>7026892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
+          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1696,18 +1695,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1725,7 +1718,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122802625</v>
+        <v>122815554</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1758,19 +1751,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1780,17 +1766,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480667</v>
+        <v>480630</v>
       </c>
       <c r="R10" t="n">
-        <v>7026892</v>
+        <v>7026966</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1824,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Synobservation av en hona i skog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,6 +1825,31 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1856,7 +1867,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815554</v>
+        <v>122805020</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1889,12 +1900,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1904,17 +1922,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480630</v>
+        <v>480704</v>
       </c>
       <c r="R11" t="n">
-        <v>7026966</v>
+        <v>7026893</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1948,7 +1966,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran.</t>
+          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1965,11 +1983,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog till stor del dominerad av gran.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1982,12 +1995,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2005,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122805020</v>
+        <v>122815560</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2017,42 +2030,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2060,14 +2074,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480704</v>
+        <v>480640</v>
       </c>
       <c r="R12" t="n">
-        <v>7026893</v>
+        <v>7026997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2104,7 +2118,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av en hane som födosökte en lång stund på en liggande upplyft död gran. I skog med höga till mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Minst 6 st skott/stjälkar varav 5 st med vinterståndare. Vid besöket på fyndplatsen doldes stor del av bottenskiktet av snötäcket. Vid barmark kan sannolikt fler knärotsskott observeras här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,6 +2127,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2121,24 +2136,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122891882</v>
+        <v>122879095</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2172,49 +2172,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480710</v>
+        <v>480694</v>
       </c>
       <c r="R13" t="n">
-        <v>7026891</v>
+        <v>7026965</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2238,17 +2226,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2265,11 +2248,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2282,12 +2260,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2305,10 +2283,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122879095</v>
+        <v>122881168</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2345,13 +2323,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480694</v>
+        <v>480648</v>
       </c>
       <c r="R14" t="n">
-        <v>7026965</v>
+        <v>7026848</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2383,6 +2361,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2394,7 +2377,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2409,12 +2392,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2432,10 +2415,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122880746</v>
+        <v>122880539</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2444,41 +2427,60 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480639</v>
+        <v>480649</v>
       </c>
       <c r="R15" t="n">
-        <v>7026895</v>
+        <v>7026970</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2510,6 +2512,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2522,26 +2529,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2559,10 +2546,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122891907</v>
+        <v>122879230</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>100645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2571,44 +2558,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480588</v>
+        <v>480678</v>
       </c>
       <c r="R16" t="n">
-        <v>7026921</v>
+        <v>7026984</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2632,12 +2621,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2646,33 +2635,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2690,10 +2658,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122877780</v>
+        <v>122878222</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>98379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2702,38 +2670,57 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480713</v>
+        <v>480731</v>
       </c>
       <c r="R17" t="n">
-        <v>7026987</v>
+        <v>7026971</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2770,7 +2757,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2785,26 +2772,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2822,10 +2789,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122880098</v>
+        <v>122879071</v>
       </c>
       <c r="B18" t="n">
-        <v>100642</v>
+        <v>98379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2834,31 +2801,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2872,13 +2848,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480632</v>
+        <v>480723</v>
       </c>
       <c r="R18" t="n">
-        <v>7026950</v>
+        <v>7026941</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2910,6 +2886,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2921,7 +2902,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2939,10 +2920,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122880817</v>
+        <v>122877780</v>
       </c>
       <c r="B19" t="n">
-        <v>100642</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2951,46 +2932,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480637</v>
+        <v>480713</v>
       </c>
       <c r="R19" t="n">
-        <v>7026903</v>
+        <v>7026987</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3022,6 +2998,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3034,6 +3015,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3051,7 +3052,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122882054</v>
+        <v>122891882</v>
       </c>
       <c r="B20" t="n">
         <v>57481</v>
@@ -3085,6 +3086,8 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3101,13 +3104,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480707</v>
+        <v>480710</v>
       </c>
       <c r="R20" t="n">
         <v>7026891</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3131,17 +3134,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3161,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3170,12 +3178,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3193,10 +3201,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122883150</v>
+        <v>122880098</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>100645</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3205,31 +3213,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3239,17 +3247,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480584</v>
+        <v>480632</v>
       </c>
       <c r="R21" t="n">
-        <v>7026773</v>
+        <v>7026950</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3281,11 +3289,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3297,27 +3300,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3335,10 +3318,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122878222</v>
+        <v>122880031</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3370,7 +3353,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3394,10 +3377,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480731</v>
+        <v>480624</v>
       </c>
       <c r="R22" t="n">
-        <v>7026971</v>
+        <v>7026948</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3434,7 +3417,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 4 st skott och 7 vinterståndare. Snötäckt mark med islager i botten vid besöket på fyndplatsen. Med tanke på hyfsat stor mängd fröställningar/vinterståndare uppenbaras här sannolikt betydligt fler knärotsskott under barmarkssäsongen.</t>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3466,10 +3449,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122881168</v>
+        <v>122882519</v>
       </c>
       <c r="B23" t="n">
-        <v>78772</v>
+        <v>90984</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3482,37 +3465,51 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480648</v>
+        <v>480735</v>
       </c>
       <c r="R23" t="n">
-        <v>7026848</v>
+        <v>7026895</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3546,7 +3543,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en död stående gran i gammal barrblandskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3560,7 +3557,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3575,12 +3572,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3598,10 +3595,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122879071</v>
+        <v>122880817</v>
       </c>
       <c r="B24" t="n">
-        <v>98376</v>
+        <v>100645</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3610,45 +3607,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3657,13 +3640,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480723</v>
+        <v>480637</v>
       </c>
       <c r="R24" t="n">
-        <v>7026941</v>
+        <v>7026903</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3695,11 +3678,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 5 st skott och 2 st vinterståndare inom ca 1 m2. Marken var snö- och istäckt vid besöket på fyndplatsen. Sannolikt uppenbarar sig här betydligt fler knärotsskott under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3711,7 +3689,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3729,10 +3707,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122880031</v>
+        <v>122882054</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3741,40 +3719,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3784,17 +3753,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480624</v>
+        <v>480707</v>
       </c>
       <c r="R25" t="n">
-        <v>7026948</v>
+        <v>7026891</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3828,7 +3797,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym av stående död ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3842,7 +3811,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3860,10 +3849,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122880249</v>
+        <v>122880746</v>
       </c>
       <c r="B26" t="n">
-        <v>100642</v>
+        <v>78775</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3872,51 +3861,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480665</v>
+        <v>480639</v>
       </c>
       <c r="R26" t="n">
-        <v>7026974</v>
+        <v>7026895</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3960,6 +3939,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3977,10 +3976,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122880310</v>
+        <v>122891907</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4011,16 +4010,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480679</v>
+        <v>480588</v>
       </c>
       <c r="R27" t="n">
-        <v>7026950</v>
+        <v>7026921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4047,12 +4049,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4061,12 +4063,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4084,10 +4107,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122880672</v>
+        <v>122883150</v>
       </c>
       <c r="B28" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4100,37 +4123,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480679</v>
+        <v>480584</v>
       </c>
       <c r="R28" t="n">
-        <v>7026935</v>
+        <v>7026773</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4162,6 +4195,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4188,12 +4226,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4211,10 +4249,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122882519</v>
+        <v>122879519</v>
       </c>
       <c r="B29" t="n">
-        <v>90981</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4223,40 +4261,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4265,10 +4308,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480735</v>
+        <v>480673</v>
       </c>
       <c r="R29" t="n">
-        <v>7026895</v>
+        <v>7026982</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4305,7 +4348,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4320,26 +4363,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4357,10 +4380,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122879230</v>
+        <v>122880672</v>
       </c>
       <c r="B30" t="n">
-        <v>100642</v>
+        <v>78775</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4369,46 +4392,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480678</v>
+        <v>480679</v>
       </c>
       <c r="R30" t="n">
-        <v>7026984</v>
+        <v>7026935</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4452,6 +4470,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4469,10 +4507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122880539</v>
+        <v>122880249</v>
       </c>
       <c r="B31" t="n">
-        <v>98376</v>
+        <v>100645</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4481,40 +4519,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4528,13 +4557,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480649</v>
+        <v>480665</v>
       </c>
       <c r="R31" t="n">
-        <v>7026970</v>
+        <v>7026974</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4564,11 +4593,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 33 st skott och 4 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4600,10 +4624,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122879519</v>
+        <v>122880310</v>
       </c>
       <c r="B32" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4612,60 +4636,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480673</v>
+        <v>480679</v>
       </c>
       <c r="R32" t="n">
-        <v>7026982</v>
+        <v>7026950</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4697,11 +4702,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 16 st skott och 6 st vinterståndare inom ca 2 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
         <v>122892039</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122891912</v>
+        <v>122891969</v>
       </c>
       <c r="B34" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480572</v>
+        <v>480602</v>
       </c>
       <c r="R34" t="n">
-        <v>7026904</v>
+        <v>7026970</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4946,11 +4946,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5003,10 +4998,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122891948</v>
+        <v>122892027</v>
       </c>
       <c r="B35" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5046,13 +5041,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480613</v>
+        <v>480633</v>
       </c>
       <c r="R35" t="n">
-        <v>7026955</v>
+        <v>7026985</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5082,11 +5077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5139,10 +5129,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122892038</v>
+        <v>122892032</v>
       </c>
       <c r="B36" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5182,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480638</v>
+        <v>480671</v>
       </c>
       <c r="R36" t="n">
-        <v>7026959</v>
+        <v>7026952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5275,10 +5265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122892027</v>
+        <v>122891927</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5318,13 +5308,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480633</v>
+        <v>480619</v>
       </c>
       <c r="R37" t="n">
-        <v>7026985</v>
+        <v>7026865</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5406,10 +5396,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122892032</v>
+        <v>122891912</v>
       </c>
       <c r="B38" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5449,13 +5439,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480671</v>
+        <v>480572</v>
       </c>
       <c r="R38" t="n">
-        <v>7026952</v>
+        <v>7026904</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5545,7 +5535,7 @@
         <v>122891989</v>
       </c>
       <c r="B39" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5678,10 +5668,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122891927</v>
+        <v>122891948</v>
       </c>
       <c r="B40" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480619</v>
+        <v>480613</v>
       </c>
       <c r="R40" t="n">
-        <v>7026865</v>
+        <v>7026955</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5757,6 +5747,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5809,10 +5804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122891969</v>
+        <v>122892038</v>
       </c>
       <c r="B41" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5852,13 +5847,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480602</v>
+        <v>480638</v>
       </c>
       <c r="R41" t="n">
-        <v>7026970</v>
+        <v>7026959</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5888,6 +5883,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -2920,10 +2920,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122877780</v>
+        <v>122891882</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2936,37 +2936,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480713</v>
+        <v>480710</v>
       </c>
       <c r="R19" t="n">
-        <v>7026987</v>
+        <v>7026891</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2990,17 +3002,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3014,27 +3026,32 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3052,10 +3069,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122891882</v>
+        <v>122880098</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>100645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3064,33 +3081,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3100,17 +3115,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480710</v>
+        <v>480632</v>
       </c>
       <c r="R20" t="n">
-        <v>7026891</v>
+        <v>7026950</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3134,17 +3149,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Riktigt färska hackspår efter en hane av tretåig hackspett i en liggande upplyft död gran. Hackspåren bearbetades fram av tretå-hanen i realtid när observationen skedde på fyndplatsen. Det handlar om flera hackspår med ca 2 - 3 cm djup i den döda granstammen.</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,32 +3168,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gammal kontinuitetsskog med mest gran på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3201,10 +3186,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122880098</v>
+        <v>122877780</v>
       </c>
       <c r="B21" t="n">
-        <v>100645</v>
+        <v>78775</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3213,51 +3198,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480632</v>
+        <v>480713</v>
       </c>
       <c r="R21" t="n">
-        <v>7026950</v>
+        <v>7026987</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3289,6 +3264,11 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en tallstam i gammal barrbkandskog.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3301,6 +3281,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122880031</v>
+        <v>122882519</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>90984</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3330,45 +3330,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3377,10 +3372,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480624</v>
+        <v>480735</v>
       </c>
       <c r="R22" t="n">
-        <v>7026948</v>
+        <v>7026895</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3417,7 +3412,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3431,7 +3426,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3449,10 +3464,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122882519</v>
+        <v>122880031</v>
       </c>
       <c r="B23" t="n">
-        <v>90984</v>
+        <v>98379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3461,40 +3476,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3503,10 +3523,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480735</v>
+        <v>480624</v>
       </c>
       <c r="R23" t="n">
-        <v>7026895</v>
+        <v>7026948</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3543,7 +3563,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Minst 11 st skott och 2 st vinterståndare inom ca 1 m2 yta. Snö- och istäckt mark vid besöket på fyndplatsen. Under barmarkssäsongen uppenbarar sig sannolikt fler knärotsskott här.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3557,27 +3577,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122891912</v>
+        <v>122891989</v>
       </c>
       <c r="B38" t="n">
         <v>78775</v>
@@ -5439,13 +5439,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480572</v>
+        <v>480640</v>
       </c>
       <c r="R38" t="n">
-        <v>7026904</v>
+        <v>7026997</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122891989</v>
+        <v>122891912</v>
       </c>
       <c r="B39" t="n">
         <v>78775</v>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480640</v>
+        <v>480572</v>
       </c>
       <c r="R39" t="n">
-        <v>7026997</v>
+        <v>7026904</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>122805210</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>122805210</v>
       </c>
       <c r="B42" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>122805210</v>
       </c>
       <c r="B42" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,7 +6075,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124589389</v>
+        <v>124591111</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480597</v>
+        <v>480594</v>
       </c>
       <c r="R43" t="n">
-        <v>7026837</v>
+        <v>7026755</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6216,10 +6216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124591947</v>
+        <v>124589949</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6228,31 +6228,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6266,13 +6266,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480629</v>
+        <v>480553</v>
       </c>
       <c r="R44" t="n">
-        <v>7026719</v>
+        <v>7026841</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6311,12 +6311,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6331,26 +6326,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6368,10 +6343,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124587436</v>
+        <v>124591424</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6384,27 +6359,32 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6413,13 +6393,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480669</v>
+        <v>480520</v>
       </c>
       <c r="R45" t="n">
-        <v>7026780</v>
+        <v>7026793</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6448,7 +6428,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6458,12 +6438,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6492,12 +6472,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6515,10 +6495,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124583865</v>
+        <v>124589882</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6527,31 +6507,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6560,13 +6554,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480592</v>
+        <v>480585</v>
       </c>
       <c r="R46" t="n">
-        <v>7026811</v>
+        <v>7026859</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6595,7 +6589,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6605,7 +6599,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6637,7 +6636,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124581847</v>
+        <v>124585231</v>
       </c>
       <c r="B47" t="n">
         <v>100279</v>
@@ -6687,10 +6686,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480610</v>
+        <v>480686</v>
       </c>
       <c r="R47" t="n">
-        <v>7026917</v>
+        <v>7026765</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -6722,7 +6721,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6732,7 +6731,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6764,10 +6763,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124582374</v>
+        <v>124582437</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79919</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6776,60 +6775,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480614</v>
+        <v>480564</v>
       </c>
       <c r="R48" t="n">
-        <v>7026910</v>
+        <v>7026877</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6858,7 +6838,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6868,12 +6848,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6905,10 +6880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124585658</v>
+        <v>124586809</v>
       </c>
       <c r="B49" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6917,31 +6892,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6951,17 +6935,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480707</v>
+        <v>480678</v>
       </c>
       <c r="R49" t="n">
-        <v>7026812</v>
+        <v>7026830</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6990,7 +6974,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7000,7 +6984,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7032,10 +7021,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124582915</v>
+        <v>124580257</v>
       </c>
       <c r="B50" t="n">
-        <v>58055</v>
+        <v>56714</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7044,20 +7033,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102990</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7070,6 +7059,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>hane</t>
@@ -7087,17 +7081,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480596</v>
+        <v>480661</v>
       </c>
       <c r="R50" t="n">
-        <v>7026957</v>
+        <v>7026890</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7126,7 +7120,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7136,7 +7130,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7168,10 +7167,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124585231</v>
+        <v>124586736</v>
       </c>
       <c r="B51" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7180,31 +7179,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7218,10 +7226,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480686</v>
+        <v>480710</v>
       </c>
       <c r="R51" t="n">
-        <v>7026765</v>
+        <v>7026857</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -7253,7 +7261,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7263,7 +7271,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7295,10 +7308,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124582437</v>
+        <v>124580022</v>
       </c>
       <c r="B52" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7307,41 +7320,60 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480564</v>
+        <v>480658</v>
       </c>
       <c r="R52" t="n">
-        <v>7026877</v>
+        <v>7026927</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7370,7 +7402,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7380,7 +7412,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7412,10 +7449,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124583310</v>
+        <v>124584501</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7424,31 +7461,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7462,13 +7508,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480524</v>
+        <v>480613</v>
       </c>
       <c r="R53" t="n">
-        <v>7026808</v>
+        <v>7026805</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7497,7 +7543,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7507,12 +7553,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7527,26 +7573,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7564,7 +7590,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124585037</v>
+        <v>124581805</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -7599,7 +7625,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>109</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7623,13 +7649,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480624</v>
+        <v>480633</v>
       </c>
       <c r="R54" t="n">
-        <v>7026760</v>
+        <v>7026927</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7658,7 +7684,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7668,12 +7694,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7705,10 +7731,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124588640</v>
+        <v>124582743</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7717,40 +7743,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7764,10 +7781,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480649</v>
+        <v>480571</v>
       </c>
       <c r="R55" t="n">
-        <v>7026845</v>
+        <v>7026896</v>
       </c>
       <c r="S55" t="n">
         <v>8</v>
@@ -7799,7 +7816,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7809,12 +7826,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7829,6 +7846,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7846,10 +7883,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124589882</v>
+        <v>124583745</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7858,40 +7895,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7905,13 +7933,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480585</v>
+        <v>480563</v>
       </c>
       <c r="R56" t="n">
-        <v>7026859</v>
+        <v>7026812</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7940,7 +7968,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7950,12 +7978,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7970,6 +7998,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7987,10 +8035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124581805</v>
+        <v>124578750</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7999,45 +8047,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8046,13 +8080,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480633</v>
+        <v>480662</v>
       </c>
       <c r="R57" t="n">
-        <v>7026927</v>
+        <v>7026990</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8081,7 +8115,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8091,12 +8125,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8128,7 +8157,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124580705</v>
+        <v>124579158</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8163,7 +8192,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8187,13 +8216,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480654</v>
+        <v>480668</v>
       </c>
       <c r="R58" t="n">
-        <v>7026946</v>
+        <v>7026971</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8222,7 +8251,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8232,12 +8261,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8269,10 +8298,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124590712</v>
+        <v>124588640</v>
       </c>
       <c r="B59" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8281,31 +8310,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8319,10 +8357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480584</v>
+        <v>480649</v>
       </c>
       <c r="R59" t="n">
-        <v>7026737</v>
+        <v>7026845</v>
       </c>
       <c r="S59" t="n">
         <v>8</v>
@@ -8354,7 +8392,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8364,7 +8402,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8396,10 +8439,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124591241</v>
+        <v>124582915</v>
       </c>
       <c r="B60" t="n">
-        <v>105102</v>
+        <v>58055</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8412,24 +8455,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>102990</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8441,10 +8498,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480551</v>
+        <v>480596</v>
       </c>
       <c r="R60" t="n">
-        <v>7026795</v>
+        <v>7026957</v>
       </c>
       <c r="S60" t="n">
         <v>11</v>
@@ -8476,7 +8533,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8486,7 +8543,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8518,10 +8575,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124580257</v>
+        <v>124580705</v>
       </c>
       <c r="B61" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8530,45 +8587,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8578,17 +8630,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480661</v>
+        <v>480654</v>
       </c>
       <c r="R61" t="n">
-        <v>7026890</v>
+        <v>7026946</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8617,7 +8669,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8627,12 +8679,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8664,10 +8716,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124583745</v>
+        <v>124587258</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8676,31 +8728,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8714,13 +8766,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480563</v>
+        <v>480668</v>
       </c>
       <c r="R62" t="n">
-        <v>7026812</v>
+        <v>7026796</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8749,7 +8801,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8759,12 +8811,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8779,26 +8826,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8816,10 +8843,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124591533</v>
+        <v>124583310</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8832,37 +8859,47 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480527</v>
+        <v>480524</v>
       </c>
       <c r="R63" t="n">
-        <v>7026752</v>
+        <v>7026808</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8891,7 +8928,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8901,7 +8938,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8930,12 +8972,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8953,7 +8995,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124582743</v>
+        <v>124591947</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -9003,13 +9045,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480571</v>
+        <v>480629</v>
       </c>
       <c r="R64" t="n">
-        <v>7026896</v>
+        <v>7026719</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9038,7 +9080,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9048,12 +9090,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9105,7 +9147,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124587258</v>
+        <v>124590712</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -9155,13 +9197,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480668</v>
+        <v>480584</v>
       </c>
       <c r="R65" t="n">
-        <v>7026796</v>
+        <v>7026737</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9190,7 +9232,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9200,7 +9242,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9232,10 +9274,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124585986</v>
+        <v>124586281</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9244,37 +9286,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -9291,13 +9324,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480716</v>
+        <v>480719</v>
       </c>
       <c r="R66" t="n">
-        <v>7026818</v>
+        <v>7026862</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9326,7 +9359,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9336,12 +9369,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9373,7 +9401,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124591111</v>
+        <v>124588170</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9408,7 +9436,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9432,13 +9460,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480594</v>
+        <v>480634</v>
       </c>
       <c r="R67" t="n">
-        <v>7026755</v>
+        <v>7026772</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9467,7 +9495,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9477,12 +9505,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9514,10 +9542,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124588170</v>
+        <v>124585658</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9526,37 +9554,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -9573,13 +9592,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480634</v>
+        <v>480707</v>
       </c>
       <c r="R68" t="n">
-        <v>7026772</v>
+        <v>7026812</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9608,7 +9627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9618,12 +9637,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9655,10 +9669,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124587192</v>
+        <v>124591533</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9667,57 +9681,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480662</v>
+        <v>480527</v>
       </c>
       <c r="R69" t="n">
-        <v>7026812</v>
+        <v>7026752</v>
       </c>
       <c r="S69" t="n">
         <v>8</v>
@@ -9749,7 +9744,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9759,12 +9754,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9779,6 +9769,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9796,10 +9806,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124586736</v>
+        <v>124583865</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9808,45 +9818,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9855,13 +9851,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480710</v>
+        <v>480592</v>
       </c>
       <c r="R70" t="n">
-        <v>7026857</v>
+        <v>7026811</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9890,7 +9886,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9900,12 +9896,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9937,10 +9928,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124580022</v>
+        <v>124583496</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9949,40 +9940,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9996,13 +9978,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480658</v>
+        <v>480565</v>
       </c>
       <c r="R71" t="n">
-        <v>7026927</v>
+        <v>7026797</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10031,7 +10013,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10041,12 +10023,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10078,10 +10055,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124584890</v>
+        <v>124581847</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10094,41 +10071,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10142,13 +10105,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480617</v>
+        <v>480610</v>
       </c>
       <c r="R72" t="n">
-        <v>7026780</v>
+        <v>7026917</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10177,7 +10140,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10187,12 +10150,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10224,10 +10182,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124593040</v>
+        <v>124585037</v>
       </c>
       <c r="B73" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10236,45 +10194,40 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10288,13 +10241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480614</v>
+        <v>480624</v>
       </c>
       <c r="R73" t="n">
-        <v>7026982</v>
+        <v>7026760</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10323,7 +10276,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10333,12 +10286,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10370,7 +10323,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124579158</v>
+        <v>124585986</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -10405,7 +10358,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10429,10 +10382,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480668</v>
+        <v>480716</v>
       </c>
       <c r="R74" t="n">
-        <v>7026971</v>
+        <v>7026818</v>
       </c>
       <c r="S74" t="n">
         <v>9</v>
@@ -10464,7 +10417,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10474,12 +10427,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10511,10 +10464,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124589949</v>
+        <v>124589389</v>
       </c>
       <c r="B75" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10523,31 +10476,40 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10561,13 +10523,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480553</v>
+        <v>480597</v>
       </c>
       <c r="R75" t="n">
-        <v>7026841</v>
+        <v>7026837</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10596,7 +10558,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10606,7 +10568,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10638,10 +10605,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124586281</v>
+        <v>124593040</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>56722</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10654,27 +10621,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10688,13 +10669,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480719</v>
+        <v>480614</v>
       </c>
       <c r="R76" t="n">
-        <v>7026862</v>
+        <v>7026982</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10723,7 +10704,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10733,7 +10714,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10765,10 +10751,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124578750</v>
+        <v>124587436</v>
       </c>
       <c r="B77" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10777,31 +10763,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10810,10 +10796,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480662</v>
+        <v>480669</v>
       </c>
       <c r="R77" t="n">
-        <v>7026990</v>
+        <v>7026780</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -10845,7 +10831,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10855,7 +10841,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10870,6 +10861,26 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10887,7 +10898,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124584501</v>
+        <v>124587192</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -10922,7 +10933,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10946,10 +10957,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480613</v>
+        <v>480662</v>
       </c>
       <c r="R78" t="n">
-        <v>7026805</v>
+        <v>7026812</v>
       </c>
       <c r="S78" t="n">
         <v>8</v>
@@ -10981,7 +10992,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10991,12 +11002,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11028,10 +11039,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124586809</v>
+        <v>124582374</v>
       </c>
       <c r="B79" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11040,40 +11051,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11083,17 +11094,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480678</v>
+        <v>480614</v>
       </c>
       <c r="R79" t="n">
-        <v>7026830</v>
+        <v>7026910</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11122,7 +11133,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11132,12 +11143,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11310,10 +11321,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124591424</v>
+        <v>124591241</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>105102</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11322,33 +11333,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11360,13 +11366,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480520</v>
+        <v>480551</v>
       </c>
       <c r="R81" t="n">
-        <v>7026793</v>
+        <v>7026795</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11395,7 +11401,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11405,12 +11411,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11425,26 +11426,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11462,10 +11443,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124583496</v>
+        <v>124584890</v>
       </c>
       <c r="B82" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11478,27 +11459,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11512,13 +11507,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480565</v>
+        <v>480617</v>
       </c>
       <c r="R82" t="n">
-        <v>7026797</v>
+        <v>7026780</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11547,7 +11542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11557,7 +11552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124583407</v>
+        <v>124591844</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11625,7 +11625,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480522</v>
+        <v>480608</v>
       </c>
       <c r="R83" t="n">
-        <v>7026804</v>
+        <v>7026725</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124592046</v>
+        <v>124583407</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480633</v>
+        <v>480522</v>
       </c>
       <c r="R84" t="n">
-        <v>7026727</v>
+        <v>7026804</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124591844</v>
+        <v>124592046</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11929,7 +11929,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480608</v>
+        <v>480633</v>
       </c>
       <c r="R85" t="n">
-        <v>7026725</v>
+        <v>7026727</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124591111</v>
+        <v>124582743</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,40 +6087,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6134,10 +6125,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480594</v>
+        <v>480571</v>
       </c>
       <c r="R43" t="n">
-        <v>7026755</v>
+        <v>7026896</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -6169,7 +6160,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6179,12 +6170,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6199,6 +6190,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6216,10 +6227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124589949</v>
+        <v>124586809</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6228,31 +6239,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6262,17 +6282,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480553</v>
+        <v>480678</v>
       </c>
       <c r="R44" t="n">
-        <v>7026841</v>
+        <v>7026830</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6301,7 +6321,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6311,7 +6331,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6343,10 +6368,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124591424</v>
+        <v>124583865</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6355,36 +6380,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6393,13 +6413,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480520</v>
+        <v>480592</v>
       </c>
       <c r="R45" t="n">
-        <v>7026793</v>
+        <v>7026811</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6428,7 +6448,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6438,12 +6458,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6458,26 +6473,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6495,7 +6490,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124589882</v>
+        <v>124591111</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -6530,7 +6525,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6554,10 +6549,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480585</v>
+        <v>480594</v>
       </c>
       <c r="R46" t="n">
-        <v>7026859</v>
+        <v>7026755</v>
       </c>
       <c r="S46" t="n">
         <v>8</v>
@@ -6589,7 +6584,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6599,12 +6594,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6636,10 +6631,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124585231</v>
+        <v>124585986</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6648,31 +6643,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6686,10 +6690,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480686</v>
+        <v>480716</v>
       </c>
       <c r="R47" t="n">
-        <v>7026765</v>
+        <v>7026818</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -6721,7 +6725,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6731,7 +6735,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6763,10 +6772,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124582437</v>
+        <v>124580705</v>
       </c>
       <c r="B48" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6775,41 +6784,60 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480564</v>
+        <v>480654</v>
       </c>
       <c r="R48" t="n">
-        <v>7026877</v>
+        <v>7026946</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6838,7 +6866,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6848,7 +6876,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6880,10 +6913,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124586809</v>
+        <v>124579158</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6892,40 +6925,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6935,17 +6968,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480678</v>
+        <v>480668</v>
       </c>
       <c r="R49" t="n">
-        <v>7026830</v>
+        <v>7026971</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6974,7 +7007,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6984,12 +7017,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7021,10 +7054,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124580257</v>
+        <v>124591424</v>
       </c>
       <c r="B50" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7037,16 +7070,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7054,24 +7087,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7081,17 +7100,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480661</v>
+        <v>480520</v>
       </c>
       <c r="R50" t="n">
-        <v>7026890</v>
+        <v>7026793</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7120,7 +7139,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7130,12 +7149,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7150,6 +7169,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7167,10 +7206,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124586736</v>
+        <v>124586281</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7179,37 +7218,28 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7226,13 +7256,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480710</v>
+        <v>480719</v>
       </c>
       <c r="R51" t="n">
-        <v>7026857</v>
+        <v>7026862</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7261,7 +7291,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7271,12 +7301,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7308,10 +7333,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124580022</v>
+        <v>124580257</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7320,40 +7345,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7363,17 +7393,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480658</v>
+        <v>480661</v>
       </c>
       <c r="R52" t="n">
-        <v>7026927</v>
+        <v>7026890</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7402,7 +7432,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7412,12 +7442,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7449,7 +7479,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124584501</v>
+        <v>124587192</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7484,7 +7514,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7508,10 +7538,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480613</v>
+        <v>480662</v>
       </c>
       <c r="R53" t="n">
-        <v>7026805</v>
+        <v>7026812</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7543,7 +7573,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7553,12 +7583,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7590,7 +7620,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124581805</v>
+        <v>124588640</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -7625,7 +7655,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7649,13 +7679,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480633</v>
+        <v>480649</v>
       </c>
       <c r="R54" t="n">
-        <v>7026927</v>
+        <v>7026845</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7684,7 +7714,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7694,12 +7724,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7731,10 +7761,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124582743</v>
+        <v>124581847</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7743,31 +7773,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7781,13 +7811,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480571</v>
+        <v>480610</v>
       </c>
       <c r="R55" t="n">
-        <v>7026896</v>
+        <v>7026917</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7816,7 +7846,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7826,12 +7856,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7846,26 +7871,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7883,10 +7888,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124583745</v>
+        <v>124589389</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7895,31 +7900,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7933,13 +7947,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480563</v>
+        <v>480597</v>
       </c>
       <c r="R56" t="n">
-        <v>7026812</v>
+        <v>7026837</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7968,7 +7982,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7978,12 +7992,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7998,26 +8012,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8035,10 +8029,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124578750</v>
+        <v>124588170</v>
       </c>
       <c r="B57" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8047,31 +8041,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8080,13 +8088,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480662</v>
+        <v>480634</v>
       </c>
       <c r="R57" t="n">
-        <v>7026990</v>
+        <v>7026772</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8115,7 +8123,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8125,7 +8133,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8157,7 +8170,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124579158</v>
+        <v>124582374</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8192,7 +8205,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8216,13 +8229,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480668</v>
+        <v>480614</v>
       </c>
       <c r="R58" t="n">
-        <v>7026971</v>
+        <v>7026910</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8251,7 +8264,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8261,12 +8274,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8298,10 +8311,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124588640</v>
+        <v>124590712</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8310,40 +8323,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8357,10 +8361,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480649</v>
+        <v>480584</v>
       </c>
       <c r="R59" t="n">
-        <v>7026845</v>
+        <v>7026737</v>
       </c>
       <c r="S59" t="n">
         <v>8</v>
@@ -8392,7 +8396,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8402,12 +8406,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8439,10 +8438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124582915</v>
+        <v>124583496</v>
       </c>
       <c r="B60" t="n">
-        <v>58055</v>
+        <v>100279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8455,36 +8454,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102990</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8498,13 +8488,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480596</v>
+        <v>480565</v>
       </c>
       <c r="R60" t="n">
-        <v>7026957</v>
+        <v>7026797</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8533,7 +8523,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8543,7 +8533,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8575,10 +8565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124580705</v>
+        <v>124591533</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8587,60 +8577,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480654</v>
+        <v>480527</v>
       </c>
       <c r="R61" t="n">
-        <v>7026946</v>
+        <v>7026752</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8669,7 +8640,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8679,12 +8650,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8699,6 +8665,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8716,10 +8702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124587258</v>
+        <v>124584501</v>
       </c>
       <c r="B62" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8728,31 +8714,40 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8766,13 +8761,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480668</v>
+        <v>480613</v>
       </c>
       <c r="R62" t="n">
-        <v>7026796</v>
+        <v>7026805</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8801,7 +8796,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8811,7 +8806,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8843,10 +8843,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124583310</v>
+        <v>124586736</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8855,31 +8855,40 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8893,13 +8902,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480524</v>
+        <v>480710</v>
       </c>
       <c r="R63" t="n">
-        <v>7026808</v>
+        <v>7026857</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8928,7 +8937,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8938,12 +8947,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8958,26 +8967,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8995,10 +8984,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124591947</v>
+        <v>124582915</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>58055</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9007,20 +8996,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>102990</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9028,10 +9017,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9045,13 +9043,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480629</v>
+        <v>480596</v>
       </c>
       <c r="R64" t="n">
-        <v>7026719</v>
+        <v>7026957</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9080,7 +9078,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9090,12 +9088,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9110,26 +9103,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9147,10 +9120,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124590712</v>
+        <v>124587436</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9159,36 +9132,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9197,10 +9165,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480584</v>
+        <v>480669</v>
       </c>
       <c r="R65" t="n">
-        <v>7026737</v>
+        <v>7026780</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -9232,7 +9200,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9242,7 +9210,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9257,6 +9230,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9274,10 +9267,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124586281</v>
+        <v>124583310</v>
       </c>
       <c r="B66" t="n">
-        <v>105102</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9286,31 +9279,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9324,13 +9317,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480719</v>
+        <v>480524</v>
       </c>
       <c r="R66" t="n">
-        <v>7026862</v>
+        <v>7026808</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9359,7 +9352,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9369,7 +9362,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9384,6 +9382,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9401,10 +9419,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124588170</v>
+        <v>124587258</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9413,40 +9431,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9460,13 +9469,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480634</v>
+        <v>480668</v>
       </c>
       <c r="R67" t="n">
-        <v>7026772</v>
+        <v>7026796</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9495,7 +9504,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9505,12 +9514,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9542,10 +9546,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124585658</v>
+        <v>124591241</v>
       </c>
       <c r="B68" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9558,29 +9562,24 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9592,13 +9591,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480707</v>
+        <v>480551</v>
       </c>
       <c r="R68" t="n">
-        <v>7026812</v>
+        <v>7026795</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9627,7 +9626,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9637,7 +9636,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9669,10 +9668,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124591533</v>
+        <v>124582437</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9681,25 +9680,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9709,13 +9708,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480527</v>
+        <v>480564</v>
       </c>
       <c r="R69" t="n">
-        <v>7026752</v>
+        <v>7026877</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9744,7 +9743,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9754,7 +9753,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9769,26 +9768,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9806,10 +9785,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124583865</v>
+        <v>124589882</v>
       </c>
       <c r="B70" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9818,31 +9797,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9851,13 +9844,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480592</v>
+        <v>480585</v>
       </c>
       <c r="R70" t="n">
-        <v>7026811</v>
+        <v>7026859</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9886,7 +9879,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9896,7 +9889,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9928,10 +9926,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124583496</v>
+        <v>124585037</v>
       </c>
       <c r="B71" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9940,31 +9938,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9978,13 +9985,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480565</v>
+        <v>480624</v>
       </c>
       <c r="R71" t="n">
-        <v>7026797</v>
+        <v>7026760</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10013,7 +10020,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10023,7 +10030,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10055,7 +10067,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124581847</v>
+        <v>124589949</v>
       </c>
       <c r="B72" t="n">
         <v>100279</v>
@@ -10105,13 +10117,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480610</v>
+        <v>480553</v>
       </c>
       <c r="R72" t="n">
-        <v>7026917</v>
+        <v>7026841</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10140,7 +10152,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10150,7 +10162,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10182,10 +10194,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124585037</v>
+        <v>124585658</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10194,37 +10206,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -10241,13 +10244,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480624</v>
+        <v>480707</v>
       </c>
       <c r="R73" t="n">
-        <v>7026760</v>
+        <v>7026812</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10276,7 +10279,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10286,12 +10289,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10323,10 +10321,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124585986</v>
+        <v>124591947</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10335,40 +10333,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10382,13 +10371,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480716</v>
+        <v>480629</v>
       </c>
       <c r="R74" t="n">
-        <v>7026818</v>
+        <v>7026719</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10417,7 +10406,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10427,12 +10416,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10447,6 +10436,26 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10464,10 +10473,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124589389</v>
+        <v>124593040</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10476,40 +10485,45 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10523,10 +10537,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480597</v>
+        <v>480614</v>
       </c>
       <c r="R75" t="n">
-        <v>7026837</v>
+        <v>7026982</v>
       </c>
       <c r="S75" t="n">
         <v>8</v>
@@ -10558,7 +10572,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10568,12 +10582,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10605,10 +10619,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124593040</v>
+        <v>124585231</v>
       </c>
       <c r="B76" t="n">
-        <v>56722</v>
+        <v>100279</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10621,41 +10635,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10669,13 +10669,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480614</v>
+        <v>480686</v>
       </c>
       <c r="R76" t="n">
-        <v>7026982</v>
+        <v>7026765</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10714,12 +10714,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10751,10 +10746,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124587436</v>
+        <v>124578750</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10763,31 +10758,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10796,10 +10791,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480669</v>
+        <v>480662</v>
       </c>
       <c r="R77" t="n">
-        <v>7026780</v>
+        <v>7026990</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -10831,7 +10826,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10841,12 +10836,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10861,26 +10851,6 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10898,10 +10868,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124587192</v>
+        <v>124584890</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10910,40 +10880,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10957,13 +10932,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480662</v>
+        <v>480617</v>
       </c>
       <c r="R78" t="n">
-        <v>7026812</v>
+        <v>7026780</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10992,7 +10967,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11002,12 +10977,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11039,7 +11014,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124582374</v>
+        <v>124585555</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -11074,7 +11049,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -11098,13 +11073,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480614</v>
+        <v>480684</v>
       </c>
       <c r="R79" t="n">
-        <v>7026910</v>
+        <v>7026753</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11133,7 +11108,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11143,12 +11118,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11180,7 +11155,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124585555</v>
+        <v>124581805</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -11215,7 +11190,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>109</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11239,13 +11214,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480684</v>
+        <v>480633</v>
       </c>
       <c r="R80" t="n">
-        <v>7026753</v>
+        <v>7026927</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11274,7 +11249,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11284,12 +11259,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11321,10 +11296,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124591241</v>
+        <v>124583745</v>
       </c>
       <c r="B81" t="n">
-        <v>105102</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11333,28 +11308,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11366,13 +11346,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480551</v>
+        <v>480563</v>
       </c>
       <c r="R81" t="n">
-        <v>7026795</v>
+        <v>7026812</v>
       </c>
       <c r="S81" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11401,7 +11381,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11411,7 +11391,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11426,6 +11411,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11443,10 +11448,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124584890</v>
+        <v>124580022</v>
       </c>
       <c r="B82" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11455,45 +11460,40 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11507,13 +11507,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480617</v>
+        <v>480658</v>
       </c>
       <c r="R82" t="n">
-        <v>7026780</v>
+        <v>7026927</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124591844</v>
+        <v>124583407</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11625,7 +11625,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480608</v>
+        <v>480522</v>
       </c>
       <c r="R83" t="n">
-        <v>7026725</v>
+        <v>7026804</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124583407</v>
+        <v>124592046</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480522</v>
+        <v>480633</v>
       </c>
       <c r="R84" t="n">
-        <v>7026804</v>
+        <v>7026727</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124592046</v>
+        <v>124591844</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11929,7 +11929,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480633</v>
+        <v>480608</v>
       </c>
       <c r="R85" t="n">
-        <v>7026727</v>
+        <v>7026725</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124582743</v>
+        <v>124587192</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,31 +6087,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6125,10 +6134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480571</v>
+        <v>480662</v>
       </c>
       <c r="R43" t="n">
-        <v>7026896</v>
+        <v>7026812</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -6160,7 +6169,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6170,12 +6179,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6190,26 +6199,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6227,10 +6216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124586809</v>
+        <v>124581847</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6239,40 +6228,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6282,17 +6262,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480678</v>
+        <v>480610</v>
       </c>
       <c r="R44" t="n">
-        <v>7026830</v>
+        <v>7026917</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6321,7 +6301,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6331,12 +6311,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6368,10 +6343,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124583865</v>
+        <v>124582915</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>58055</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6384,27 +6359,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>102990</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6413,13 +6402,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480592</v>
+        <v>480596</v>
       </c>
       <c r="R45" t="n">
-        <v>7026811</v>
+        <v>7026957</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6448,7 +6437,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6458,7 +6447,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6490,10 +6479,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124591111</v>
+        <v>124583865</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6502,45 +6491,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6549,13 +6524,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480594</v>
+        <v>480592</v>
       </c>
       <c r="R46" t="n">
-        <v>7026755</v>
+        <v>7026811</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6584,7 +6559,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6594,12 +6569,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6631,10 +6601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124585986</v>
+        <v>124585231</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6643,40 +6613,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6690,10 +6651,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480716</v>
+        <v>480686</v>
       </c>
       <c r="R47" t="n">
-        <v>7026818</v>
+        <v>7026765</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -6725,7 +6686,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6735,12 +6696,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6772,7 +6728,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124580705</v>
+        <v>124589882</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6807,7 +6763,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6831,13 +6787,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480654</v>
+        <v>480585</v>
       </c>
       <c r="R48" t="n">
-        <v>7026946</v>
+        <v>7026859</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6866,7 +6822,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6876,12 +6832,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6913,7 +6869,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124579158</v>
+        <v>124580022</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6948,7 +6904,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6972,10 +6928,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480668</v>
+        <v>480658</v>
       </c>
       <c r="R49" t="n">
-        <v>7026971</v>
+        <v>7026927</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -7007,7 +6963,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7017,12 +6973,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7054,10 +7010,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124591424</v>
+        <v>124589949</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7066,31 +7022,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7104,13 +7060,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480520</v>
+        <v>480553</v>
       </c>
       <c r="R50" t="n">
-        <v>7026793</v>
+        <v>7026841</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7139,7 +7095,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7149,12 +7105,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7169,26 +7120,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7206,10 +7137,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124586281</v>
+        <v>124587436</v>
       </c>
       <c r="B51" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7218,36 +7149,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7256,13 +7182,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480719</v>
+        <v>480669</v>
       </c>
       <c r="R51" t="n">
-        <v>7026862</v>
+        <v>7026780</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7291,7 +7217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7301,7 +7227,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7316,6 +7247,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7333,10 +7284,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124580257</v>
+        <v>124586736</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7345,45 +7296,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7393,17 +7339,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480661</v>
+        <v>480710</v>
       </c>
       <c r="R52" t="n">
-        <v>7026890</v>
+        <v>7026857</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7432,7 +7378,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7442,12 +7388,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7479,10 +7425,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124587192</v>
+        <v>124590712</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7491,40 +7437,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7538,10 +7475,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480662</v>
+        <v>480584</v>
       </c>
       <c r="R53" t="n">
-        <v>7026812</v>
+        <v>7026737</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7573,7 +7510,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7583,12 +7520,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7620,10 +7552,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124588640</v>
+        <v>124586281</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7632,37 +7564,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7679,13 +7602,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480649</v>
+        <v>480719</v>
       </c>
       <c r="R54" t="n">
-        <v>7026845</v>
+        <v>7026862</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7714,7 +7637,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7724,12 +7647,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7761,10 +7679,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124581847</v>
+        <v>124585986</v>
       </c>
       <c r="B55" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7773,31 +7691,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7811,10 +7738,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480610</v>
+        <v>480716</v>
       </c>
       <c r="R55" t="n">
-        <v>7026917</v>
+        <v>7026818</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -7846,7 +7773,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7856,7 +7783,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8029,10 +7961,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124588170</v>
+        <v>124583745</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8041,40 +7973,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8088,10 +8011,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480634</v>
+        <v>480563</v>
       </c>
       <c r="R57" t="n">
-        <v>7026772</v>
+        <v>7026812</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -8123,7 +8046,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8133,12 +8056,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8153,6 +8076,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8170,7 +8113,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124582374</v>
+        <v>124585037</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8205,7 +8148,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8229,13 +8172,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480614</v>
+        <v>480624</v>
       </c>
       <c r="R58" t="n">
-        <v>7026910</v>
+        <v>7026760</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8264,7 +8207,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8274,12 +8217,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8311,10 +8254,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124590712</v>
+        <v>124579158</v>
       </c>
       <c r="B59" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8323,31 +8266,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8361,13 +8313,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480584</v>
+        <v>480668</v>
       </c>
       <c r="R59" t="n">
-        <v>7026737</v>
+        <v>7026971</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8396,7 +8348,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8406,7 +8358,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8438,10 +8395,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124583496</v>
+        <v>124588170</v>
       </c>
       <c r="B60" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8450,31 +8407,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8488,13 +8454,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480565</v>
+        <v>480634</v>
       </c>
       <c r="R60" t="n">
-        <v>7026797</v>
+        <v>7026772</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8523,7 +8489,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8533,7 +8499,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8565,10 +8536,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124591533</v>
+        <v>124585658</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8577,41 +8548,51 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480527</v>
+        <v>480707</v>
       </c>
       <c r="R61" t="n">
-        <v>7026752</v>
+        <v>7026812</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8640,7 +8621,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8650,7 +8631,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8665,26 +8646,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8702,7 +8663,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124584501</v>
+        <v>124582374</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -8737,7 +8698,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8761,13 +8722,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480613</v>
+        <v>480614</v>
       </c>
       <c r="R62" t="n">
-        <v>7026805</v>
+        <v>7026910</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8796,7 +8757,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8806,12 +8767,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8843,7 +8804,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124586736</v>
+        <v>124588640</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -8878,7 +8839,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8902,13 +8863,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480710</v>
+        <v>480649</v>
       </c>
       <c r="R63" t="n">
-        <v>7026857</v>
+        <v>7026845</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8937,7 +8898,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8947,12 +8908,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8984,10 +8945,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124582915</v>
+        <v>124580705</v>
       </c>
       <c r="B64" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8996,40 +8957,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9043,13 +9004,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480596</v>
+        <v>480654</v>
       </c>
       <c r="R64" t="n">
-        <v>7026957</v>
+        <v>7026946</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9078,7 +9039,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9088,7 +9049,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9120,10 +9086,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124587436</v>
+        <v>124583496</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9132,31 +9098,36 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9165,10 +9136,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480669</v>
+        <v>480565</v>
       </c>
       <c r="R65" t="n">
-        <v>7026780</v>
+        <v>7026797</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -9200,7 +9171,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9210,12 +9181,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9230,26 +9196,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9267,10 +9213,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124583310</v>
+        <v>124584890</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9279,20 +9225,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9300,10 +9246,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9317,13 +9277,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480524</v>
+        <v>480617</v>
       </c>
       <c r="R66" t="n">
-        <v>7026808</v>
+        <v>7026780</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9352,7 +9312,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9362,12 +9322,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9382,26 +9342,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9419,10 +9359,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124587258</v>
+        <v>124582437</v>
       </c>
       <c r="B67" t="n">
-        <v>100279</v>
+        <v>79919</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9435,44 +9375,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480668</v>
+        <v>480564</v>
       </c>
       <c r="R67" t="n">
-        <v>7026796</v>
+        <v>7026877</v>
       </c>
       <c r="S67" t="n">
         <v>11</v>
@@ -9504,7 +9434,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9514,7 +9444,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9546,10 +9476,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124591241</v>
+        <v>124593040</v>
       </c>
       <c r="B68" t="n">
-        <v>105102</v>
+        <v>56722</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9562,24 +9492,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9591,13 +9540,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480551</v>
+        <v>480614</v>
       </c>
       <c r="R68" t="n">
-        <v>7026795</v>
+        <v>7026982</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9626,7 +9575,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9636,7 +9585,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9668,10 +9622,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124582437</v>
+        <v>124584501</v>
       </c>
       <c r="B69" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9680,41 +9634,60 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480564</v>
+        <v>480613</v>
       </c>
       <c r="R69" t="n">
-        <v>7026877</v>
+        <v>7026805</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9743,7 +9716,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9753,7 +9726,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9785,7 +9763,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124589882</v>
+        <v>124591111</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9820,7 +9798,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9844,10 +9822,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480585</v>
+        <v>480594</v>
       </c>
       <c r="R70" t="n">
-        <v>7026859</v>
+        <v>7026755</v>
       </c>
       <c r="S70" t="n">
         <v>8</v>
@@ -9879,7 +9857,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9889,12 +9867,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9926,10 +9904,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124585037</v>
+        <v>124591947</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9938,40 +9916,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9985,13 +9954,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480624</v>
+        <v>480629</v>
       </c>
       <c r="R71" t="n">
-        <v>7026760</v>
+        <v>7026719</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10020,7 +9989,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10030,12 +9999,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10050,6 +10019,26 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10067,10 +10056,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124589949</v>
+        <v>124581805</v>
       </c>
       <c r="B72" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10079,31 +10068,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10117,13 +10115,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480553</v>
+        <v>480633</v>
       </c>
       <c r="R72" t="n">
-        <v>7026841</v>
+        <v>7026927</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10152,7 +10150,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10162,7 +10160,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10194,10 +10197,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124585658</v>
+        <v>124591424</v>
       </c>
       <c r="B73" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10206,31 +10209,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10244,13 +10247,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480707</v>
+        <v>480520</v>
       </c>
       <c r="R73" t="n">
-        <v>7026812</v>
+        <v>7026793</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10279,7 +10282,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10289,7 +10292,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10304,6 +10312,26 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10321,10 +10349,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124591947</v>
+        <v>124580257</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10337,16 +10365,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10354,10 +10382,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10367,17 +10409,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480629</v>
+        <v>480661</v>
       </c>
       <c r="R74" t="n">
-        <v>7026719</v>
+        <v>7026890</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10406,7 +10448,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10416,12 +10458,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10436,26 +10478,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10473,10 +10495,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124593040</v>
+        <v>124578750</v>
       </c>
       <c r="B75" t="n">
-        <v>56722</v>
+        <v>100279</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10489,46 +10511,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10537,10 +10540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480614</v>
+        <v>480662</v>
       </c>
       <c r="R75" t="n">
-        <v>7026982</v>
+        <v>7026990</v>
       </c>
       <c r="S75" t="n">
         <v>8</v>
@@ -10572,7 +10575,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10582,12 +10585,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10619,10 +10617,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124585231</v>
+        <v>124591241</v>
       </c>
       <c r="B76" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10635,29 +10633,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -10669,13 +10662,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480686</v>
+        <v>480551</v>
       </c>
       <c r="R76" t="n">
-        <v>7026765</v>
+        <v>7026795</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10704,7 +10697,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10714,7 +10707,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10746,7 +10739,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124578750</v>
+        <v>124587258</v>
       </c>
       <c r="B77" t="n">
         <v>100279</v>
@@ -10785,19 +10778,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480662</v>
+        <v>480668</v>
       </c>
       <c r="R77" t="n">
-        <v>7026990</v>
+        <v>7026796</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10826,7 +10824,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10836,7 +10834,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10868,10 +10866,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124584890</v>
+        <v>124582743</v>
       </c>
       <c r="B78" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10880,20 +10878,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10901,24 +10899,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10932,13 +10916,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480617</v>
+        <v>480571</v>
       </c>
       <c r="R78" t="n">
-        <v>7026780</v>
+        <v>7026896</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10967,7 +10951,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10977,12 +10961,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10997,6 +10981,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11014,10 +11018,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124585555</v>
+        <v>124586809</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11026,40 +11030,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11069,17 +11073,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480684</v>
+        <v>480678</v>
       </c>
       <c r="R79" t="n">
-        <v>7026753</v>
+        <v>7026830</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11108,7 +11112,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11118,12 +11122,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11155,7 +11159,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124581805</v>
+        <v>124585555</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -11190,7 +11194,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11214,13 +11218,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480633</v>
+        <v>480684</v>
       </c>
       <c r="R80" t="n">
-        <v>7026927</v>
+        <v>7026753</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11249,7 +11253,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11259,12 +11263,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11296,10 +11300,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124583745</v>
+        <v>124591533</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11312,47 +11316,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480563</v>
+        <v>480527</v>
       </c>
       <c r="R81" t="n">
-        <v>7026812</v>
+        <v>7026752</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11381,7 +11375,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11391,12 +11385,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11425,12 +11414,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11448,10 +11437,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124580022</v>
+        <v>124583310</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11460,40 +11449,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11507,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480658</v>
+        <v>480524</v>
       </c>
       <c r="R82" t="n">
-        <v>7026927</v>
+        <v>7026808</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11542,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11552,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11572,6 +11552,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124583407</v>
+        <v>124592046</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480522</v>
+        <v>480633</v>
       </c>
       <c r="R83" t="n">
-        <v>7026804</v>
+        <v>7026727</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124592046</v>
+        <v>124583407</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480633</v>
+        <v>480522</v>
       </c>
       <c r="R84" t="n">
-        <v>7026727</v>
+        <v>7026804</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124587192</v>
+        <v>124586809</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,40 +6087,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6130,17 +6130,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480662</v>
+        <v>480678</v>
       </c>
       <c r="R43" t="n">
-        <v>7026812</v>
+        <v>7026830</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6216,10 +6216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124581847</v>
+        <v>124586281</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6232,27 +6232,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6266,13 +6266,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480610</v>
+        <v>480719</v>
       </c>
       <c r="R44" t="n">
-        <v>7026917</v>
+        <v>7026862</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6343,10 +6343,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124582915</v>
+        <v>124591111</v>
       </c>
       <c r="B45" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6355,40 +6355,40 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6402,13 +6402,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480596</v>
+        <v>480594</v>
       </c>
       <c r="R45" t="n">
-        <v>7026957</v>
+        <v>7026755</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6447,7 +6447,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6479,7 +6484,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124583865</v>
+        <v>124590712</v>
       </c>
       <c r="B46" t="n">
         <v>100279</v>
@@ -6518,19 +6523,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480592</v>
+        <v>480584</v>
       </c>
       <c r="R46" t="n">
-        <v>7026811</v>
+        <v>7026737</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6559,7 +6569,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6569,7 +6579,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6601,7 +6611,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124585231</v>
+        <v>124587258</v>
       </c>
       <c r="B47" t="n">
         <v>100279</v>
@@ -6651,13 +6661,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480686</v>
+        <v>480668</v>
       </c>
       <c r="R47" t="n">
-        <v>7026765</v>
+        <v>7026796</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6686,7 +6696,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6696,7 +6706,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6728,10 +6738,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124589882</v>
+        <v>124583496</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6740,40 +6750,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6787,10 +6788,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480585</v>
+        <v>480565</v>
       </c>
       <c r="R48" t="n">
-        <v>7026859</v>
+        <v>7026797</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6822,7 +6823,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6832,12 +6833,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6869,10 +6865,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124580022</v>
+        <v>124583745</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6881,40 +6877,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6928,13 +6915,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480658</v>
+        <v>480563</v>
       </c>
       <c r="R49" t="n">
-        <v>7026927</v>
+        <v>7026812</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6963,7 +6950,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6973,12 +6960,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6993,6 +6980,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7010,10 +7017,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124589949</v>
+        <v>124591533</v>
       </c>
       <c r="B50" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7022,51 +7029,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480553</v>
+        <v>480527</v>
       </c>
       <c r="R50" t="n">
-        <v>7026841</v>
+        <v>7026752</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7095,7 +7092,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7105,7 +7102,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7120,6 +7117,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7137,10 +7154,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124587436</v>
+        <v>124585231</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7149,31 +7166,36 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7182,13 +7204,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480669</v>
+        <v>480686</v>
       </c>
       <c r="R51" t="n">
-        <v>7026780</v>
+        <v>7026765</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7217,7 +7239,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7227,12 +7249,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7247,26 +7264,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7284,7 +7281,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124586736</v>
+        <v>124585986</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7319,7 +7316,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7343,10 +7340,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480710</v>
+        <v>480716</v>
       </c>
       <c r="R52" t="n">
-        <v>7026857</v>
+        <v>7026818</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -7378,7 +7375,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7388,12 +7385,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7425,10 +7422,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124590712</v>
+        <v>124585555</v>
       </c>
       <c r="B53" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7437,31 +7434,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7475,10 +7481,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480584</v>
+        <v>480684</v>
       </c>
       <c r="R53" t="n">
-        <v>7026737</v>
+        <v>7026753</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7510,7 +7516,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7520,7 +7526,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7552,10 +7563,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124586281</v>
+        <v>124580705</v>
       </c>
       <c r="B54" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7564,28 +7575,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7602,13 +7622,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480719</v>
+        <v>480654</v>
       </c>
       <c r="R54" t="n">
-        <v>7026862</v>
+        <v>7026946</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7637,7 +7657,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7647,7 +7667,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7679,10 +7704,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124585986</v>
+        <v>124593040</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7691,40 +7716,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7738,13 +7768,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480716</v>
+        <v>480614</v>
       </c>
       <c r="R55" t="n">
-        <v>7026818</v>
+        <v>7026982</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7773,7 +7803,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7783,12 +7813,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7820,7 +7850,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124589389</v>
+        <v>124589882</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -7855,7 +7885,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7879,10 +7909,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480597</v>
+        <v>480585</v>
       </c>
       <c r="R56" t="n">
-        <v>7026837</v>
+        <v>7026859</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -7914,7 +7944,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7924,12 +7954,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7961,10 +7991,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124583745</v>
+        <v>124591241</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>105102</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7973,33 +8003,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8011,13 +8036,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480563</v>
+        <v>480551</v>
       </c>
       <c r="R57" t="n">
-        <v>7026812</v>
+        <v>7026795</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8046,7 +8071,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8056,12 +8081,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8076,26 +8096,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124585037</v>
+        <v>124581847</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8125,40 +8125,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8172,13 +8163,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480624</v>
+        <v>480610</v>
       </c>
       <c r="R58" t="n">
-        <v>7026760</v>
+        <v>7026917</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8207,7 +8198,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8217,12 +8208,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8254,10 +8240,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124579158</v>
+        <v>124578750</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8266,45 +8252,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8313,13 +8285,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480668</v>
+        <v>480662</v>
       </c>
       <c r="R59" t="n">
-        <v>7026971</v>
+        <v>7026990</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8348,7 +8320,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8358,12 +8330,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8395,10 +8362,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124588170</v>
+        <v>124591424</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8407,40 +8374,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8454,10 +8412,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480634</v>
+        <v>480520</v>
       </c>
       <c r="R60" t="n">
-        <v>7026772</v>
+        <v>7026793</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -8489,7 +8447,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8499,12 +8457,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8519,6 +8477,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8536,10 +8514,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124585658</v>
+        <v>124589389</v>
       </c>
       <c r="B61" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8548,28 +8526,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8586,13 +8573,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480707</v>
+        <v>480597</v>
       </c>
       <c r="R61" t="n">
-        <v>7026812</v>
+        <v>7026837</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8621,7 +8608,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8631,7 +8618,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8663,10 +8655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124582374</v>
+        <v>124583865</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8675,45 +8667,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8722,10 +8700,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480614</v>
+        <v>480592</v>
       </c>
       <c r="R62" t="n">
-        <v>7026910</v>
+        <v>7026811</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8757,7 +8735,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8767,12 +8745,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8804,10 +8777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124588640</v>
+        <v>124589949</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8816,40 +8789,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8863,13 +8827,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480649</v>
+        <v>480553</v>
       </c>
       <c r="R63" t="n">
-        <v>7026845</v>
+        <v>7026841</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8898,7 +8862,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8908,12 +8872,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8945,7 +8904,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124580705</v>
+        <v>124588640</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -8980,7 +8939,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9004,13 +8963,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480654</v>
+        <v>480649</v>
       </c>
       <c r="R64" t="n">
-        <v>7026946</v>
+        <v>7026845</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9039,7 +8998,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9049,12 +9008,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9086,10 +9045,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124583496</v>
+        <v>124582437</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>79919</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9102,47 +9061,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480565</v>
+        <v>480564</v>
       </c>
       <c r="R65" t="n">
-        <v>7026797</v>
+        <v>7026877</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9171,7 +9120,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9181,7 +9130,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9213,10 +9162,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124584890</v>
+        <v>124586736</v>
       </c>
       <c r="B66" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9225,45 +9174,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9277,13 +9221,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480617</v>
+        <v>480710</v>
       </c>
       <c r="R66" t="n">
-        <v>7026780</v>
+        <v>7026857</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9312,7 +9256,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9322,12 +9266,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9359,10 +9303,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124582437</v>
+        <v>124582915</v>
       </c>
       <c r="B67" t="n">
-        <v>79919</v>
+        <v>58055</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9375,34 +9319,53 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>102990</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480564</v>
+        <v>480596</v>
       </c>
       <c r="R67" t="n">
-        <v>7026877</v>
+        <v>7026957</v>
       </c>
       <c r="S67" t="n">
         <v>11</v>
@@ -9434,7 +9397,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9444,7 +9407,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9476,10 +9439,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124593040</v>
+        <v>124582743</v>
       </c>
       <c r="B68" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9488,45 +9451,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9540,10 +9489,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480614</v>
+        <v>480571</v>
       </c>
       <c r="R68" t="n">
-        <v>7026982</v>
+        <v>7026896</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -9575,7 +9524,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9585,12 +9534,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9605,6 +9554,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9622,7 +9591,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124584501</v>
+        <v>124582374</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9657,7 +9626,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9681,13 +9650,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480613</v>
+        <v>480614</v>
       </c>
       <c r="R69" t="n">
-        <v>7026805</v>
+        <v>7026910</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9716,7 +9685,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9726,12 +9695,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9763,7 +9732,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124591111</v>
+        <v>124580022</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9798,7 +9767,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9822,13 +9791,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480594</v>
+        <v>480658</v>
       </c>
       <c r="R70" t="n">
-        <v>7026755</v>
+        <v>7026927</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9857,7 +9826,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9867,12 +9836,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9904,7 +9873,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124591947</v>
+        <v>124583310</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -9940,7 +9909,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9954,13 +9923,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480629</v>
+        <v>480524</v>
       </c>
       <c r="R71" t="n">
-        <v>7026719</v>
+        <v>7026808</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9989,7 +9958,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9999,12 +9968,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10056,10 +10025,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124581805</v>
+        <v>124591947</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10068,40 +10037,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10115,10 +10075,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480633</v>
+        <v>480629</v>
       </c>
       <c r="R72" t="n">
-        <v>7026927</v>
+        <v>7026719</v>
       </c>
       <c r="S72" t="n">
         <v>7</v>
@@ -10150,7 +10110,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10160,12 +10120,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10180,6 +10140,26 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10197,10 +10177,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124591424</v>
+        <v>124580257</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10213,16 +10193,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10230,10 +10210,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10243,17 +10237,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480520</v>
+        <v>480661</v>
       </c>
       <c r="R73" t="n">
-        <v>7026793</v>
+        <v>7026890</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10282,7 +10276,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10292,12 +10286,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10312,26 +10306,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10349,10 +10323,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124580257</v>
+        <v>124579158</v>
       </c>
       <c r="B74" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10361,45 +10335,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10409,17 +10378,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480661</v>
+        <v>480668</v>
       </c>
       <c r="R74" t="n">
-        <v>7026890</v>
+        <v>7026971</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10448,7 +10417,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10458,12 +10427,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10495,7 +10464,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124578750</v>
+        <v>124585658</v>
       </c>
       <c r="B75" t="n">
         <v>100279</v>
@@ -10531,7 +10500,12 @@
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10540,13 +10514,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480662</v>
+        <v>480707</v>
       </c>
       <c r="R75" t="n">
-        <v>7026990</v>
+        <v>7026812</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10575,7 +10549,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10585,7 +10559,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10617,10 +10591,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124591241</v>
+        <v>124584890</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>57883</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10633,24 +10607,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -10662,13 +10655,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480551</v>
+        <v>480617</v>
       </c>
       <c r="R76" t="n">
-        <v>7026795</v>
+        <v>7026780</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10697,7 +10690,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10707,7 +10700,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10739,10 +10737,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124587258</v>
+        <v>124585037</v>
       </c>
       <c r="B77" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10751,31 +10749,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10789,13 +10796,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480668</v>
+        <v>480624</v>
       </c>
       <c r="R77" t="n">
-        <v>7026796</v>
+        <v>7026760</v>
       </c>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10824,7 +10831,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10834,7 +10841,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10866,10 +10878,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124582743</v>
+        <v>124584501</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10878,31 +10890,40 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10916,10 +10937,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480571</v>
+        <v>480613</v>
       </c>
       <c r="R78" t="n">
-        <v>7026896</v>
+        <v>7026805</v>
       </c>
       <c r="S78" t="n">
         <v>8</v>
@@ -10951,7 +10972,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10961,12 +10982,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10981,26 +11002,6 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11018,10 +11019,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124586809</v>
+        <v>124587436</v>
       </c>
       <c r="B79" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11034,56 +11035,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480678</v>
+        <v>480669</v>
       </c>
       <c r="R79" t="n">
-        <v>7026830</v>
+        <v>7026780</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11112,7 +11099,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11122,12 +11109,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11142,6 +11129,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11159,7 +11166,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124585555</v>
+        <v>124587192</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -11194,7 +11201,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11218,10 +11225,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480684</v>
+        <v>480662</v>
       </c>
       <c r="R80" t="n">
-        <v>7026753</v>
+        <v>7026812</v>
       </c>
       <c r="S80" t="n">
         <v>8</v>
@@ -11253,7 +11260,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11263,12 +11270,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11300,10 +11307,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124591533</v>
+        <v>124588170</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11312,41 +11319,60 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480527</v>
+        <v>480634</v>
       </c>
       <c r="R81" t="n">
-        <v>7026752</v>
+        <v>7026772</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11375,7 +11401,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11385,7 +11411,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11400,26 +11431,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11437,10 +11448,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124583310</v>
+        <v>124581805</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11449,31 +11460,40 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11487,13 +11507,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480524</v>
+        <v>480633</v>
       </c>
       <c r="R82" t="n">
-        <v>7026808</v>
+        <v>7026927</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11522,7 +11542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11532,12 +11552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11552,26 +11572,6 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124592046</v>
+        <v>124583407</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480633</v>
+        <v>480522</v>
       </c>
       <c r="R83" t="n">
-        <v>7026727</v>
+        <v>7026804</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124583407</v>
+        <v>124591844</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11777,7 +11777,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480522</v>
+        <v>480608</v>
       </c>
       <c r="R84" t="n">
-        <v>7026804</v>
+        <v>7026725</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124591844</v>
+        <v>124592046</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11929,7 +11929,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480608</v>
+        <v>480633</v>
       </c>
       <c r="R85" t="n">
-        <v>7026725</v>
+        <v>7026727</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124586809</v>
+        <v>124586281</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,40 +6087,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6130,17 +6121,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480678</v>
+        <v>480719</v>
       </c>
       <c r="R43" t="n">
-        <v>7026830</v>
+        <v>7026862</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6169,7 +6160,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6179,12 +6170,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6216,10 +6202,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124586281</v>
+        <v>124586809</v>
       </c>
       <c r="B44" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6228,31 +6214,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6262,17 +6257,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480719</v>
+        <v>480678</v>
       </c>
       <c r="R44" t="n">
-        <v>7026862</v>
+        <v>7026830</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6301,7 +6296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6311,7 +6306,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6865,10 +6865,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124583745</v>
+        <v>124591533</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6881,47 +6881,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480563</v>
+        <v>480527</v>
       </c>
       <c r="R49" t="n">
-        <v>7026812</v>
+        <v>7026752</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6950,7 +6940,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6960,12 +6950,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6994,12 +6979,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7017,10 +7002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124591533</v>
+        <v>124585231</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7029,41 +7014,51 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480527</v>
+        <v>480686</v>
       </c>
       <c r="R50" t="n">
-        <v>7026752</v>
+        <v>7026765</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7092,7 +7087,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7102,7 +7097,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7117,26 +7112,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7154,10 +7129,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124585231</v>
+        <v>124583745</v>
       </c>
       <c r="B51" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7166,31 +7141,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7204,13 +7179,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480686</v>
+        <v>480563</v>
       </c>
       <c r="R51" t="n">
-        <v>7026765</v>
+        <v>7026812</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7239,7 +7214,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7249,7 +7224,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7264,6 +7244,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124580705</v>
+        <v>124593040</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7575,40 +7575,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7622,13 +7627,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480654</v>
+        <v>480614</v>
       </c>
       <c r="R54" t="n">
-        <v>7026946</v>
+        <v>7026982</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7657,7 +7662,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7667,12 +7672,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7704,10 +7709,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124593040</v>
+        <v>124580705</v>
       </c>
       <c r="B55" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7716,45 +7721,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7768,13 +7768,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480614</v>
+        <v>480654</v>
       </c>
       <c r="R55" t="n">
-        <v>7026982</v>
+        <v>7026946</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8362,10 +8362,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124591424</v>
+        <v>124589389</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8374,31 +8374,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8412,13 +8421,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480520</v>
+        <v>480597</v>
       </c>
       <c r="R60" t="n">
-        <v>7026793</v>
+        <v>7026837</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8447,7 +8456,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8457,12 +8466,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8477,26 +8486,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8514,10 +8503,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124589389</v>
+        <v>124583865</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8526,45 +8515,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8573,13 +8548,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480597</v>
+        <v>480592</v>
       </c>
       <c r="R61" t="n">
-        <v>7026837</v>
+        <v>7026811</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8608,7 +8583,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8618,12 +8593,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8655,7 +8625,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124583865</v>
+        <v>124589949</v>
       </c>
       <c r="B62" t="n">
         <v>100279</v>
@@ -8694,19 +8664,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480592</v>
+        <v>480553</v>
       </c>
       <c r="R62" t="n">
-        <v>7026811</v>
+        <v>7026841</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8735,7 +8710,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8745,7 +8720,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8777,10 +8752,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124589949</v>
+        <v>124591424</v>
       </c>
       <c r="B63" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8789,31 +8764,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8827,13 +8802,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480553</v>
+        <v>480520</v>
       </c>
       <c r="R63" t="n">
-        <v>7026841</v>
+        <v>7026793</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8862,7 +8837,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8872,7 +8847,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8887,6 +8867,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -10464,10 +10464,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124585658</v>
+        <v>124584890</v>
       </c>
       <c r="B75" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10480,27 +10480,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10514,13 +10528,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480707</v>
+        <v>480617</v>
       </c>
       <c r="R75" t="n">
-        <v>7026812</v>
+        <v>7026780</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10549,7 +10563,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10559,7 +10573,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10591,10 +10610,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124584890</v>
+        <v>124585658</v>
       </c>
       <c r="B76" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10607,41 +10626,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10655,13 +10660,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480617</v>
+        <v>480707</v>
       </c>
       <c r="R76" t="n">
-        <v>7026780</v>
+        <v>7026812</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10690,7 +10695,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10700,12 +10705,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6202,10 +6202,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124586809</v>
+        <v>124583745</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6218,16 +6218,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6235,19 +6235,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6257,17 +6248,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480678</v>
+        <v>480563</v>
       </c>
       <c r="R44" t="n">
-        <v>7026830</v>
+        <v>7026812</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6296,7 +6287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6306,12 +6297,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6326,6 +6317,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6343,10 +6354,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124591111</v>
+        <v>124593040</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6355,40 +6366,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6402,10 +6418,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480594</v>
+        <v>480614</v>
       </c>
       <c r="R45" t="n">
-        <v>7026755</v>
+        <v>7026982</v>
       </c>
       <c r="S45" t="n">
         <v>8</v>
@@ -6437,7 +6453,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6447,12 +6463,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6484,10 +6500,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124590712</v>
+        <v>124585037</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6496,31 +6512,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6534,13 +6559,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480584</v>
+        <v>480624</v>
       </c>
       <c r="R46" t="n">
-        <v>7026737</v>
+        <v>7026760</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6569,7 +6594,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6579,7 +6604,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6611,10 +6641,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124587258</v>
+        <v>124586809</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6623,31 +6653,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6657,17 +6696,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480668</v>
+        <v>480678</v>
       </c>
       <c r="R47" t="n">
-        <v>7026796</v>
+        <v>7026830</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6696,7 +6735,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6706,7 +6745,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6738,10 +6782,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124583496</v>
+        <v>124589389</v>
       </c>
       <c r="B48" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6750,31 +6794,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6788,10 +6841,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480565</v>
+        <v>480597</v>
       </c>
       <c r="R48" t="n">
-        <v>7026797</v>
+        <v>7026837</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6823,7 +6876,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6833,7 +6886,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6865,10 +6923,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124591533</v>
+        <v>124579158</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6877,41 +6935,60 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480527</v>
+        <v>480668</v>
       </c>
       <c r="R49" t="n">
-        <v>7026752</v>
+        <v>7026971</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6940,7 +7017,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6950,7 +7027,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6965,26 +7047,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7002,10 +7064,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124585231</v>
+        <v>124582374</v>
       </c>
       <c r="B50" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7014,31 +7076,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7052,13 +7123,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480686</v>
+        <v>480614</v>
       </c>
       <c r="R50" t="n">
-        <v>7026765</v>
+        <v>7026910</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7087,7 +7158,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7097,7 +7168,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7129,10 +7205,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124583745</v>
+        <v>124587192</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7141,31 +7217,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7179,13 +7264,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480563</v>
+        <v>480662</v>
       </c>
       <c r="R51" t="n">
         <v>7026812</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7214,7 +7299,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7224,12 +7309,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7244,26 +7329,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7281,10 +7346,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124585986</v>
+        <v>124582915</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>58055</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7293,40 +7358,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7340,13 +7405,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480716</v>
+        <v>480596</v>
       </c>
       <c r="R52" t="n">
-        <v>7026818</v>
+        <v>7026957</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7375,7 +7440,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7385,12 +7450,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7422,7 +7482,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124585555</v>
+        <v>124591111</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7457,7 +7517,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7481,10 +7541,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480684</v>
+        <v>480594</v>
       </c>
       <c r="R53" t="n">
-        <v>7026753</v>
+        <v>7026755</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -7516,7 +7576,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7526,12 +7586,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7563,10 +7623,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124593040</v>
+        <v>124581847</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>100279</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7579,41 +7639,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7627,13 +7673,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480614</v>
+        <v>480610</v>
       </c>
       <c r="R54" t="n">
-        <v>7026982</v>
+        <v>7026917</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7662,7 +7708,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7672,12 +7718,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7709,10 +7750,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124580705</v>
+        <v>124587258</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7721,40 +7762,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7768,13 +7800,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480654</v>
+        <v>480668</v>
       </c>
       <c r="R55" t="n">
-        <v>7026946</v>
+        <v>7026796</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7803,7 +7835,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7813,12 +7845,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7850,10 +7877,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124589882</v>
+        <v>124580257</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7862,40 +7889,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7905,17 +7937,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480585</v>
+        <v>480661</v>
       </c>
       <c r="R56" t="n">
-        <v>7026859</v>
+        <v>7026890</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7944,7 +7976,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7954,12 +7986,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7991,10 +8023,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124591241</v>
+        <v>124582437</v>
       </c>
       <c r="B57" t="n">
-        <v>105102</v>
+        <v>79919</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8007,39 +8039,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480551</v>
+        <v>480564</v>
       </c>
       <c r="R57" t="n">
-        <v>7026795</v>
+        <v>7026877</v>
       </c>
       <c r="S57" t="n">
         <v>11</v>
@@ -8071,7 +8098,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8081,7 +8108,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8113,10 +8140,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124581847</v>
+        <v>124591947</v>
       </c>
       <c r="B58" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8125,31 +8152,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8163,13 +8190,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480610</v>
+        <v>480629</v>
       </c>
       <c r="R58" t="n">
-        <v>7026917</v>
+        <v>7026719</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8198,7 +8225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8208,7 +8235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8223,6 +8255,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8240,10 +8292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124578750</v>
+        <v>124587436</v>
       </c>
       <c r="B59" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8252,31 +8304,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8285,10 +8337,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480662</v>
+        <v>480669</v>
       </c>
       <c r="R59" t="n">
-        <v>7026990</v>
+        <v>7026780</v>
       </c>
       <c r="S59" t="n">
         <v>8</v>
@@ -8320,7 +8372,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8330,7 +8382,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8345,6 +8402,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8362,10 +8439,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124589389</v>
+        <v>124591241</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8374,42 +8451,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8421,13 +8484,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480597</v>
+        <v>480551</v>
       </c>
       <c r="R60" t="n">
-        <v>7026837</v>
+        <v>7026795</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8456,7 +8519,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8466,12 +8529,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8503,10 +8561,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124583865</v>
+        <v>124584890</v>
       </c>
       <c r="B61" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8519,27 +8577,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8548,13 +8625,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480592</v>
+        <v>480617</v>
       </c>
       <c r="R61" t="n">
-        <v>7026811</v>
+        <v>7026780</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8583,7 +8660,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8593,7 +8670,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8625,10 +8707,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124589949</v>
+        <v>124580705</v>
       </c>
       <c r="B62" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8637,31 +8719,40 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8675,13 +8766,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480553</v>
+        <v>480654</v>
       </c>
       <c r="R62" t="n">
-        <v>7026841</v>
+        <v>7026946</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8710,7 +8801,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8720,7 +8811,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8752,10 +8848,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124591424</v>
+        <v>124588640</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8764,31 +8860,40 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8802,13 +8907,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480520</v>
+        <v>480649</v>
       </c>
       <c r="R63" t="n">
-        <v>7026793</v>
+        <v>7026845</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8837,7 +8942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8847,12 +8952,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8867,26 +8972,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8904,10 +8989,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124588640</v>
+        <v>124585231</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8916,40 +9001,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8963,13 +9039,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480649</v>
+        <v>480686</v>
       </c>
       <c r="R64" t="n">
-        <v>7026845</v>
+        <v>7026765</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8998,7 +9074,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9008,12 +9084,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9045,10 +9116,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124582437</v>
+        <v>124584501</v>
       </c>
       <c r="B65" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9057,41 +9128,60 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480564</v>
+        <v>480613</v>
       </c>
       <c r="R65" t="n">
-        <v>7026877</v>
+        <v>7026805</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9120,7 +9210,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9130,7 +9220,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9162,10 +9257,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124586736</v>
+        <v>124589949</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9174,40 +9269,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9221,13 +9307,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480710</v>
+        <v>480553</v>
       </c>
       <c r="R66" t="n">
-        <v>7026857</v>
+        <v>7026841</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9256,7 +9342,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9266,12 +9352,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9303,10 +9384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124582915</v>
+        <v>124586736</v>
       </c>
       <c r="B67" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9315,40 +9396,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9362,13 +9443,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480596</v>
+        <v>480710</v>
       </c>
       <c r="R67" t="n">
-        <v>7026957</v>
+        <v>7026857</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9397,7 +9478,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9407,7 +9488,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9439,10 +9525,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124582743</v>
+        <v>124589882</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9451,31 +9537,40 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9489,10 +9584,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480571</v>
+        <v>480585</v>
       </c>
       <c r="R68" t="n">
-        <v>7026896</v>
+        <v>7026859</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -9524,7 +9619,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9534,12 +9629,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9554,26 +9649,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9591,7 +9666,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124582374</v>
+        <v>124588170</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9626,7 +9701,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9650,13 +9725,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480614</v>
+        <v>480634</v>
       </c>
       <c r="R69" t="n">
-        <v>7026910</v>
+        <v>7026772</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9685,7 +9760,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9695,12 +9770,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9732,10 +9807,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124580022</v>
+        <v>124591533</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9744,60 +9819,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480658</v>
+        <v>480527</v>
       </c>
       <c r="R70" t="n">
-        <v>7026927</v>
+        <v>7026752</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9826,7 +9882,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9836,12 +9892,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9856,6 +9907,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -10025,10 +10096,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124591947</v>
+        <v>124581805</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10037,31 +10108,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10075,10 +10155,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480629</v>
+        <v>480633</v>
       </c>
       <c r="R72" t="n">
-        <v>7026719</v>
+        <v>7026927</v>
       </c>
       <c r="S72" t="n">
         <v>7</v>
@@ -10110,7 +10190,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10120,12 +10200,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10140,26 +10220,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10177,10 +10237,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124580257</v>
+        <v>124591424</v>
       </c>
       <c r="B73" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10193,16 +10253,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10210,24 +10270,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10237,17 +10283,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480661</v>
+        <v>480520</v>
       </c>
       <c r="R73" t="n">
-        <v>7026890</v>
+        <v>7026793</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10276,7 +10322,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10286,12 +10332,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10306,6 +10352,26 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10323,10 +10389,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124579158</v>
+        <v>124585658</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10335,37 +10401,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -10382,10 +10439,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480668</v>
+        <v>480707</v>
       </c>
       <c r="R74" t="n">
-        <v>7026971</v>
+        <v>7026812</v>
       </c>
       <c r="S74" t="n">
         <v>9</v>
@@ -10417,7 +10474,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10427,12 +10484,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10464,10 +10516,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124584890</v>
+        <v>124580022</v>
       </c>
       <c r="B75" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10476,45 +10528,40 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10528,13 +10575,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480617</v>
+        <v>480658</v>
       </c>
       <c r="R75" t="n">
-        <v>7026780</v>
+        <v>7026927</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10563,7 +10610,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10573,12 +10620,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10610,7 +10657,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124585658</v>
+        <v>124578750</v>
       </c>
       <c r="B76" t="n">
         <v>100279</v>
@@ -10646,12 +10693,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -10660,13 +10702,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480707</v>
+        <v>480662</v>
       </c>
       <c r="R76" t="n">
-        <v>7026812</v>
+        <v>7026990</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10695,7 +10737,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10705,7 +10747,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10737,7 +10779,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124585037</v>
+        <v>124585555</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -10772,7 +10814,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10796,13 +10838,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480624</v>
+        <v>480684</v>
       </c>
       <c r="R77" t="n">
-        <v>7026760</v>
+        <v>7026753</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10831,7 +10873,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10841,12 +10883,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10878,10 +10920,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124584501</v>
+        <v>124583865</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10890,45 +10932,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10937,13 +10965,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480613</v>
+        <v>480592</v>
       </c>
       <c r="R78" t="n">
-        <v>7026805</v>
+        <v>7026811</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10972,7 +11000,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10982,12 +11010,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11019,10 +11042,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124587436</v>
+        <v>124583496</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11031,31 +11054,36 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -11064,10 +11092,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480669</v>
+        <v>480565</v>
       </c>
       <c r="R79" t="n">
-        <v>7026780</v>
+        <v>7026797</v>
       </c>
       <c r="S79" t="n">
         <v>8</v>
@@ -11099,7 +11127,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11109,12 +11137,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11129,26 +11152,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11166,7 +11169,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124587192</v>
+        <v>124585986</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -11201,7 +11204,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11225,13 +11228,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480662</v>
+        <v>480716</v>
       </c>
       <c r="R80" t="n">
-        <v>7026812</v>
+        <v>7026818</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11260,7 +11263,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11270,12 +11273,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11307,10 +11310,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124588170</v>
+        <v>124590712</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11319,40 +11322,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11366,13 +11360,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480634</v>
+        <v>480584</v>
       </c>
       <c r="R81" t="n">
-        <v>7026772</v>
+        <v>7026737</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11401,7 +11395,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11411,12 +11405,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11448,10 +11437,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124581805</v>
+        <v>124582743</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11460,40 +11449,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11507,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480633</v>
+        <v>480571</v>
       </c>
       <c r="R82" t="n">
-        <v>7026927</v>
+        <v>7026896</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11542,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11552,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11572,6 +11552,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124583407</v>
+        <v>124592046</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480522</v>
+        <v>480633</v>
       </c>
       <c r="R83" t="n">
-        <v>7026804</v>
+        <v>7026727</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124591844</v>
+        <v>124583407</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11777,7 +11777,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480608</v>
+        <v>480522</v>
       </c>
       <c r="R84" t="n">
-        <v>7026725</v>
+        <v>7026804</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124592046</v>
+        <v>124591844</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11929,7 +11929,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480633</v>
+        <v>480608</v>
       </c>
       <c r="R85" t="n">
-        <v>7026727</v>
+        <v>7026725</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124586281</v>
+        <v>124593040</v>
       </c>
       <c r="B43" t="n">
-        <v>105102</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6091,27 +6091,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6125,13 +6139,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480719</v>
+        <v>480614</v>
       </c>
       <c r="R43" t="n">
-        <v>7026862</v>
+        <v>7026982</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6160,7 +6174,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6170,7 +6184,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6354,10 +6373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124593040</v>
+        <v>124586281</v>
       </c>
       <c r="B45" t="n">
-        <v>56722</v>
+        <v>105102</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6370,41 +6389,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6418,13 +6423,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480614</v>
+        <v>480719</v>
       </c>
       <c r="R45" t="n">
-        <v>7026982</v>
+        <v>7026862</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6453,7 +6458,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6463,12 +6468,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7346,10 +7346,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124582915</v>
+        <v>124591111</v>
       </c>
       <c r="B52" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7358,40 +7358,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480596</v>
+        <v>480594</v>
       </c>
       <c r="R52" t="n">
-        <v>7026957</v>
+        <v>7026755</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7450,7 +7450,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7482,10 +7487,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124591111</v>
+        <v>124581847</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7494,40 +7499,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7541,13 +7537,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480594</v>
+        <v>480610</v>
       </c>
       <c r="R53" t="n">
-        <v>7026755</v>
+        <v>7026917</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7576,7 +7572,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7586,12 +7582,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7623,7 +7614,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124581847</v>
+        <v>124587258</v>
       </c>
       <c r="B54" t="n">
         <v>100279</v>
@@ -7673,13 +7664,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480610</v>
+        <v>480668</v>
       </c>
       <c r="R54" t="n">
-        <v>7026917</v>
+        <v>7026796</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7708,7 +7699,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7718,7 +7709,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7750,10 +7741,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124587258</v>
+        <v>124582915</v>
       </c>
       <c r="B55" t="n">
-        <v>100279</v>
+        <v>58055</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7766,27 +7757,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>102990</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480668</v>
+        <v>480596</v>
       </c>
       <c r="R55" t="n">
-        <v>7026796</v>
+        <v>7026957</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -10096,10 +10096,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124581805</v>
+        <v>124591424</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10108,40 +10108,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10155,10 +10146,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480633</v>
+        <v>480520</v>
       </c>
       <c r="R72" t="n">
-        <v>7026927</v>
+        <v>7026793</v>
       </c>
       <c r="S72" t="n">
         <v>7</v>
@@ -10190,7 +10181,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10200,12 +10191,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10220,6 +10211,26 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10237,10 +10248,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124591424</v>
+        <v>124585658</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10249,31 +10260,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10287,13 +10298,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480520</v>
+        <v>480707</v>
       </c>
       <c r="R73" t="n">
-        <v>7026793</v>
+        <v>7026812</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10322,7 +10333,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10332,12 +10343,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10352,26 +10358,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10389,10 +10375,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124585658</v>
+        <v>124581805</v>
       </c>
       <c r="B74" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10401,28 +10387,37 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -10439,13 +10434,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480707</v>
+        <v>480633</v>
       </c>
       <c r="R74" t="n">
-        <v>7026812</v>
+        <v>7026927</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10474,7 +10469,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10484,7 +10479,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6228,7 +6228,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7346,10 +7346,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124591111</v>
+        <v>124582915</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>58055</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7358,40 +7358,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480594</v>
+        <v>480596</v>
       </c>
       <c r="R52" t="n">
-        <v>7026755</v>
+        <v>7026957</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7450,12 +7450,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7487,10 +7482,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124581847</v>
+        <v>124591111</v>
       </c>
       <c r="B53" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7499,31 +7494,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7537,13 +7541,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480610</v>
+        <v>480594</v>
       </c>
       <c r="R53" t="n">
-        <v>7026917</v>
+        <v>7026755</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7572,7 +7576,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7582,7 +7586,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7614,7 +7623,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124587258</v>
+        <v>124581847</v>
       </c>
       <c r="B54" t="n">
         <v>100279</v>
@@ -7664,13 +7673,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480668</v>
+        <v>480610</v>
       </c>
       <c r="R54" t="n">
-        <v>7026796</v>
+        <v>7026917</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7699,7 +7708,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7709,7 +7718,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7741,10 +7750,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124582915</v>
+        <v>124587258</v>
       </c>
       <c r="B55" t="n">
-        <v>58055</v>
+        <v>100279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7757,36 +7766,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102990</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480596</v>
+        <v>480668</v>
       </c>
       <c r="R55" t="n">
-        <v>7026957</v>
+        <v>7026796</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8292,10 +8292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124587436</v>
+        <v>124591241</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8304,31 +8304,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8337,13 +8337,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480669</v>
+        <v>480551</v>
       </c>
       <c r="R59" t="n">
-        <v>7026780</v>
+        <v>7026795</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8382,12 +8382,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8402,26 +8397,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8439,10 +8414,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124591241</v>
+        <v>124587436</v>
       </c>
       <c r="B60" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8451,31 +8426,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8484,13 +8459,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480551</v>
+        <v>480669</v>
       </c>
       <c r="R60" t="n">
-        <v>7026795</v>
+        <v>7026780</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8519,7 +8494,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8529,7 +8504,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8544,6 +8524,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124593040</v>
+        <v>124582437</v>
       </c>
       <c r="B43" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6091,61 +6091,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480614</v>
+        <v>480564</v>
       </c>
       <c r="R43" t="n">
-        <v>7026982</v>
+        <v>7026877</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6174,7 +6150,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6184,12 +6160,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6221,43 +6192,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124583745</v>
+        <v>124585986</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6271,13 +6251,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480563</v>
+        <v>480716</v>
       </c>
       <c r="R44" t="n">
-        <v>7026812</v>
+        <v>7026818</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6306,7 +6286,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6316,12 +6296,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6336,26 +6316,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6373,10 +6333,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124586281</v>
+        <v>124588640</v>
       </c>
       <c r="B45" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6385,28 +6345,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6423,13 +6392,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480719</v>
+        <v>480649</v>
       </c>
       <c r="R45" t="n">
-        <v>7026862</v>
+        <v>7026845</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6458,7 +6427,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6468,7 +6437,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6500,7 +6474,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124585037</v>
+        <v>124582374</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -6535,7 +6509,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6559,13 +6533,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480624</v>
+        <v>480614</v>
       </c>
       <c r="R46" t="n">
-        <v>7026760</v>
+        <v>7026910</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6594,7 +6568,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6604,12 +6578,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6641,10 +6615,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124586809</v>
+        <v>124591533</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6657,56 +6631,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480678</v>
+        <v>480527</v>
       </c>
       <c r="R47" t="n">
-        <v>7026830</v>
+        <v>7026752</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6735,7 +6690,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6745,12 +6700,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6765,6 +6715,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6782,10 +6752,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124589389</v>
+        <v>124591241</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6794,42 +6764,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6841,13 +6797,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480597</v>
+        <v>480551</v>
       </c>
       <c r="R48" t="n">
-        <v>7026837</v>
+        <v>7026795</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6876,7 +6832,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6886,12 +6842,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6923,10 +6874,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124579158</v>
+        <v>124582915</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>58055</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6935,40 +6886,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6982,13 +6933,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480668</v>
+        <v>480596</v>
       </c>
       <c r="R49" t="n">
-        <v>7026971</v>
+        <v>7026957</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7017,7 +6968,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7027,12 +6978,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7064,10 +7010,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124582374</v>
+        <v>124589949</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7076,40 +7022,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7123,13 +7060,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480614</v>
+        <v>480553</v>
       </c>
       <c r="R50" t="n">
-        <v>7026910</v>
+        <v>7026841</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7158,7 +7095,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7168,12 +7105,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7205,10 +7137,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124587192</v>
+        <v>124578750</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7217,45 +7149,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7267,7 +7185,7 @@
         <v>480662</v>
       </c>
       <c r="R51" t="n">
-        <v>7026812</v>
+        <v>7026990</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -7299,7 +7217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7309,12 +7227,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7346,10 +7259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124582915</v>
+        <v>124585037</v>
       </c>
       <c r="B52" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7358,40 +7271,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7405,13 +7318,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480596</v>
+        <v>480624</v>
       </c>
       <c r="R52" t="n">
-        <v>7026957</v>
+        <v>7026760</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7440,7 +7353,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7450,7 +7363,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7623,7 +7541,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124581847</v>
+        <v>124590712</v>
       </c>
       <c r="B54" t="n">
         <v>100279</v>
@@ -7673,13 +7591,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480610</v>
+        <v>480584</v>
       </c>
       <c r="R54" t="n">
-        <v>7026917</v>
+        <v>7026737</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7708,7 +7626,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7718,7 +7636,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7877,10 +7795,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124580257</v>
+        <v>124589882</v>
       </c>
       <c r="B56" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7889,45 +7807,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7937,17 +7850,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480661</v>
+        <v>480585</v>
       </c>
       <c r="R56" t="n">
-        <v>7026890</v>
+        <v>7026859</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7976,7 +7889,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7986,12 +7899,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8023,10 +7936,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124582437</v>
+        <v>124589389</v>
       </c>
       <c r="B57" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8035,41 +7948,60 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480564</v>
+        <v>480597</v>
       </c>
       <c r="R57" t="n">
-        <v>7026877</v>
+        <v>7026837</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8098,7 +8030,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8108,7 +8040,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8140,43 +8077,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124591947</v>
+        <v>124584501</v>
       </c>
       <c r="B58" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8190,13 +8136,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480629</v>
+        <v>480613</v>
       </c>
       <c r="R58" t="n">
-        <v>7026719</v>
+        <v>7026805</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8225,7 +8171,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8235,12 +8181,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8255,26 +8201,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8292,7 +8218,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124591241</v>
+        <v>124586281</v>
       </c>
       <c r="B59" t="n">
         <v>105102</v>
@@ -8326,6 +8252,11 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8337,13 +8268,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480551</v>
+        <v>480719</v>
       </c>
       <c r="R59" t="n">
-        <v>7026795</v>
+        <v>7026862</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8372,7 +8303,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8382,7 +8313,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8561,10 +8492,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124584890</v>
+        <v>124580022</v>
       </c>
       <c r="B61" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8573,45 +8504,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8625,13 +8551,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480617</v>
+        <v>480658</v>
       </c>
       <c r="R61" t="n">
-        <v>7026780</v>
+        <v>7026927</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8660,7 +8586,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8670,12 +8596,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8707,10 +8633,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124580705</v>
+        <v>124583865</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8719,45 +8645,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8766,13 +8678,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480654</v>
+        <v>480592</v>
       </c>
       <c r="R62" t="n">
-        <v>7026946</v>
+        <v>7026811</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8801,7 +8713,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8811,12 +8723,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8848,7 +8755,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124588640</v>
+        <v>124588170</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -8883,7 +8790,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8907,13 +8814,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480649</v>
+        <v>480634</v>
       </c>
       <c r="R63" t="n">
-        <v>7026845</v>
+        <v>7026772</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8942,7 +8849,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8952,12 +8859,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8989,10 +8896,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124585231</v>
+        <v>124579158</v>
       </c>
       <c r="B64" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9001,31 +8908,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9039,10 +8955,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480686</v>
+        <v>480668</v>
       </c>
       <c r="R64" t="n">
-        <v>7026765</v>
+        <v>7026971</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -9074,7 +8990,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9084,7 +9000,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9116,10 +9037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124584501</v>
+        <v>124585231</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9128,40 +9049,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9175,13 +9087,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480613</v>
+        <v>480686</v>
       </c>
       <c r="R65" t="n">
-        <v>7026805</v>
+        <v>7026765</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9210,7 +9122,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9220,12 +9132,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9257,10 +9164,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124589949</v>
+        <v>124587192</v>
       </c>
       <c r="B66" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9269,31 +9176,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9307,13 +9223,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480553</v>
+        <v>480662</v>
       </c>
       <c r="R66" t="n">
-        <v>7026841</v>
+        <v>7026812</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9342,7 +9258,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9352,7 +9268,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9384,10 +9305,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124586736</v>
+        <v>124584890</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9396,40 +9317,45 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9443,13 +9369,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480710</v>
+        <v>480617</v>
       </c>
       <c r="R67" t="n">
-        <v>7026857</v>
+        <v>7026780</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9478,7 +9404,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9488,12 +9414,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9525,10 +9451,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124589882</v>
+        <v>124583496</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9537,40 +9463,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9584,10 +9501,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480585</v>
+        <v>480565</v>
       </c>
       <c r="R68" t="n">
-        <v>7026859</v>
+        <v>7026797</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -9619,7 +9536,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9629,12 +9546,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9666,7 +9578,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124588170</v>
+        <v>124586736</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9701,7 +9613,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9725,13 +9637,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480634</v>
+        <v>480710</v>
       </c>
       <c r="R69" t="n">
-        <v>7026772</v>
+        <v>7026857</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9760,7 +9672,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9770,12 +9682,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9807,10 +9719,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124591533</v>
+        <v>124585658</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9819,41 +9731,51 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480527</v>
+        <v>480707</v>
       </c>
       <c r="R70" t="n">
-        <v>7026752</v>
+        <v>7026812</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9882,7 +9804,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9892,7 +9814,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9907,26 +9829,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9944,43 +9846,43 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124583310</v>
+        <v>124581847</v>
       </c>
       <c r="B71" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9994,13 +9896,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480524</v>
+        <v>480610</v>
       </c>
       <c r="R71" t="n">
-        <v>7026808</v>
+        <v>7026917</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10029,7 +9931,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10039,12 +9941,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10059,26 +9956,6 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10096,43 +9973,52 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124591424</v>
+        <v>124581805</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10146,10 +10032,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480520</v>
+        <v>480633</v>
       </c>
       <c r="R72" t="n">
-        <v>7026793</v>
+        <v>7026927</v>
       </c>
       <c r="S72" t="n">
         <v>7</v>
@@ -10181,7 +10067,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10191,12 +10077,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10211,26 +10097,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10248,10 +10114,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124585658</v>
+        <v>124580705</v>
       </c>
       <c r="B73" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10260,28 +10126,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -10298,13 +10173,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480707</v>
+        <v>480654</v>
       </c>
       <c r="R73" t="n">
-        <v>7026812</v>
+        <v>7026946</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10333,7 +10208,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10343,7 +10218,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10375,10 +10255,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124581805</v>
+        <v>124586809</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10387,40 +10267,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10430,17 +10310,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480633</v>
+        <v>480678</v>
       </c>
       <c r="R74" t="n">
-        <v>7026927</v>
+        <v>7026830</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10469,7 +10349,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10479,12 +10359,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10516,10 +10396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124580022</v>
+        <v>124580257</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10528,40 +10408,45 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10571,17 +10456,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480658</v>
+        <v>480661</v>
       </c>
       <c r="R75" t="n">
-        <v>7026927</v>
+        <v>7026890</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10610,7 +10495,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10620,12 +10505,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10657,10 +10542,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124578750</v>
+        <v>124593040</v>
       </c>
       <c r="B76" t="n">
-        <v>100279</v>
+        <v>56722</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10673,27 +10558,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -10702,10 +10606,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480662</v>
+        <v>480614</v>
       </c>
       <c r="R76" t="n">
-        <v>7026990</v>
+        <v>7026982</v>
       </c>
       <c r="S76" t="n">
         <v>8</v>
@@ -10737,7 +10641,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10747,7 +10651,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10920,43 +10829,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124583865</v>
+        <v>124583407</v>
       </c>
       <c r="B78" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10965,13 +10879,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480592</v>
+        <v>480522</v>
       </c>
       <c r="R78" t="n">
-        <v>7026811</v>
+        <v>7026804</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -11000,7 +10914,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11010,7 +10924,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11025,6 +10944,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11042,43 +10981,43 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124583496</v>
+        <v>124583310</v>
       </c>
       <c r="B79" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11092,13 +11031,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480565</v>
+        <v>480524</v>
       </c>
       <c r="R79" t="n">
-        <v>7026797</v>
+        <v>7026808</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11127,7 +11066,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11137,7 +11076,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11152,6 +11096,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11169,52 +11133,43 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124585986</v>
+        <v>124582743</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11228,13 +11183,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480716</v>
+        <v>480571</v>
       </c>
       <c r="R80" t="n">
-        <v>7026818</v>
+        <v>7026896</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11263,7 +11218,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11273,12 +11228,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11293,6 +11248,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11310,43 +11285,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124590712</v>
+        <v>124592046</v>
       </c>
       <c r="B81" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11360,13 +11335,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480584</v>
+        <v>480633</v>
       </c>
       <c r="R81" t="n">
-        <v>7026737</v>
+        <v>7026727</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11395,7 +11370,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11405,7 +11380,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11420,6 +11400,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124582743</v>
+        <v>124591947</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11487,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480571</v>
+        <v>480629</v>
       </c>
       <c r="R82" t="n">
-        <v>7026896</v>
+        <v>7026719</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124592046</v>
+        <v>124591844</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11625,7 +11625,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480633</v>
+        <v>480608</v>
       </c>
       <c r="R83" t="n">
-        <v>7026727</v>
+        <v>7026725</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124583407</v>
+        <v>124591424</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11777,7 +11777,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480522</v>
+        <v>480520</v>
       </c>
       <c r="R84" t="n">
-        <v>7026804</v>
+        <v>7026793</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124591844</v>
+        <v>124583745</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480608</v>
+        <v>480563</v>
       </c>
       <c r="R85" t="n">
-        <v>7026725</v>
+        <v>7026812</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124582437</v>
+        <v>124582915</v>
       </c>
       <c r="B43" t="n">
-        <v>79919</v>
+        <v>58055</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6091,34 +6091,53 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>102990</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480564</v>
+        <v>480596</v>
       </c>
       <c r="R43" t="n">
-        <v>7026877</v>
+        <v>7026957</v>
       </c>
       <c r="S43" t="n">
         <v>11</v>
@@ -6150,7 +6169,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6160,7 +6179,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6192,7 +6211,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124585986</v>
+        <v>124589882</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -6227,7 +6246,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6251,13 +6270,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480716</v>
+        <v>480585</v>
       </c>
       <c r="R44" t="n">
-        <v>7026818</v>
+        <v>7026859</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6286,7 +6305,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6296,12 +6315,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6333,10 +6352,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124588640</v>
+        <v>124582437</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79919</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6345,60 +6364,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480649</v>
+        <v>480564</v>
       </c>
       <c r="R45" t="n">
-        <v>7026845</v>
+        <v>7026877</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6437,12 +6437,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6474,7 +6469,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124582374</v>
+        <v>124579158</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -6509,7 +6504,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6533,13 +6528,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480614</v>
+        <v>480668</v>
       </c>
       <c r="R46" t="n">
-        <v>7026910</v>
+        <v>7026971</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6568,7 +6563,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6578,12 +6573,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6615,10 +6610,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124591533</v>
+        <v>124593040</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6627,38 +6622,62 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480527</v>
+        <v>480614</v>
       </c>
       <c r="R47" t="n">
-        <v>7026752</v>
+        <v>7026982</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6690,7 +6709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6700,7 +6719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6715,26 +6739,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6752,10 +6756,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124591241</v>
+        <v>124587436</v>
       </c>
       <c r="B48" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6764,31 +6768,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6797,13 +6801,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480551</v>
+        <v>480669</v>
       </c>
       <c r="R48" t="n">
-        <v>7026795</v>
+        <v>7026780</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6832,7 +6836,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6842,7 +6846,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6857,6 +6866,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6874,10 +6903,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124582915</v>
+        <v>124586736</v>
       </c>
       <c r="B49" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6886,40 +6915,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6933,13 +6962,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480596</v>
+        <v>480710</v>
       </c>
       <c r="R49" t="n">
-        <v>7026957</v>
+        <v>7026857</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6968,7 +6997,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6978,7 +7007,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7010,7 +7044,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124589949</v>
+        <v>124590712</v>
       </c>
       <c r="B50" t="n">
         <v>100279</v>
@@ -7060,13 +7094,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480553</v>
+        <v>480584</v>
       </c>
       <c r="R50" t="n">
-        <v>7026841</v>
+        <v>7026737</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7095,7 +7129,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7105,7 +7139,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7137,10 +7171,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124578750</v>
+        <v>124580257</v>
       </c>
       <c r="B51" t="n">
-        <v>100279</v>
+        <v>56714</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7149,46 +7183,65 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480662</v>
+        <v>480661</v>
       </c>
       <c r="R51" t="n">
-        <v>7026990</v>
+        <v>7026890</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7217,7 +7270,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7227,7 +7280,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7259,7 +7317,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124585037</v>
+        <v>124582374</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7294,7 +7352,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7318,13 +7376,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480624</v>
+        <v>480614</v>
       </c>
       <c r="R52" t="n">
-        <v>7026760</v>
+        <v>7026910</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7353,7 +7411,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7363,12 +7421,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7400,7 +7458,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124591111</v>
+        <v>124580022</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7435,7 +7493,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7459,13 +7517,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480594</v>
+        <v>480658</v>
       </c>
       <c r="R53" t="n">
-        <v>7026755</v>
+        <v>7026927</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7494,7 +7552,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7504,12 +7562,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7541,10 +7599,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124590712</v>
+        <v>124587192</v>
       </c>
       <c r="B54" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7553,31 +7611,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7591,10 +7658,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480584</v>
+        <v>480662</v>
       </c>
       <c r="R54" t="n">
-        <v>7026737</v>
+        <v>7026812</v>
       </c>
       <c r="S54" t="n">
         <v>8</v>
@@ -7626,7 +7693,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7636,7 +7703,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7668,10 +7740,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124587258</v>
+        <v>124585986</v>
       </c>
       <c r="B55" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7680,31 +7752,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7718,13 +7799,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480668</v>
+        <v>480716</v>
       </c>
       <c r="R55" t="n">
-        <v>7026796</v>
+        <v>7026818</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7753,7 +7834,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7763,7 +7844,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7795,10 +7881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124589882</v>
+        <v>124591241</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7807,42 +7893,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7854,13 +7926,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480585</v>
+        <v>480551</v>
       </c>
       <c r="R56" t="n">
-        <v>7026859</v>
+        <v>7026795</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7889,7 +7961,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7899,12 +7971,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7936,7 +8003,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124589389</v>
+        <v>124588640</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7971,7 +8038,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7995,10 +8062,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480597</v>
+        <v>480649</v>
       </c>
       <c r="R57" t="n">
-        <v>7026837</v>
+        <v>7026845</v>
       </c>
       <c r="S57" t="n">
         <v>8</v>
@@ -8030,7 +8097,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8040,12 +8107,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8077,10 +8144,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124584501</v>
+        <v>124585658</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8089,37 +8156,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8136,13 +8194,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480613</v>
+        <v>480707</v>
       </c>
       <c r="R58" t="n">
-        <v>7026805</v>
+        <v>7026812</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8171,7 +8229,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8181,12 +8239,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8218,10 +8271,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124586281</v>
+        <v>124589949</v>
       </c>
       <c r="B59" t="n">
-        <v>105102</v>
+        <v>100279</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8234,27 +8287,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8268,10 +8321,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480719</v>
+        <v>480553</v>
       </c>
       <c r="R59" t="n">
-        <v>7026862</v>
+        <v>7026841</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8303,7 +8356,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8313,7 +8366,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8345,7 +8398,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124587436</v>
+        <v>124591533</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -8379,21 +8432,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480669</v>
+        <v>480527</v>
       </c>
       <c r="R60" t="n">
-        <v>7026780</v>
+        <v>7026752</v>
       </c>
       <c r="S60" t="n">
         <v>8</v>
@@ -8425,7 +8473,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8435,12 +8483,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8469,12 +8512,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8492,10 +8535,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124580022</v>
+        <v>124585231</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8504,40 +8547,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8551,10 +8585,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480658</v>
+        <v>480686</v>
       </c>
       <c r="R61" t="n">
-        <v>7026927</v>
+        <v>7026765</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -8586,7 +8620,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8596,12 +8630,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8633,7 +8662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124583865</v>
+        <v>124587258</v>
       </c>
       <c r="B62" t="n">
         <v>100279</v>
@@ -8672,19 +8701,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480592</v>
+        <v>480668</v>
       </c>
       <c r="R62" t="n">
-        <v>7026811</v>
+        <v>7026796</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8713,7 +8747,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8723,7 +8757,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8755,7 +8789,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124588170</v>
+        <v>124589389</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -8790,7 +8824,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8814,13 +8848,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480634</v>
+        <v>480597</v>
       </c>
       <c r="R63" t="n">
-        <v>7026772</v>
+        <v>7026837</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8849,7 +8883,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8859,12 +8893,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8896,10 +8930,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124579158</v>
+        <v>124584890</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8908,40 +8942,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8955,13 +8994,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480668</v>
+        <v>480617</v>
       </c>
       <c r="R64" t="n">
-        <v>7026971</v>
+        <v>7026780</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8990,7 +9029,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9000,12 +9039,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9037,10 +9076,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124585231</v>
+        <v>124581805</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9049,31 +9088,40 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9087,13 +9135,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480686</v>
+        <v>480633</v>
       </c>
       <c r="R65" t="n">
-        <v>7026765</v>
+        <v>7026927</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9122,7 +9170,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9132,7 +9180,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9164,7 +9217,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124587192</v>
+        <v>124585037</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -9199,7 +9252,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9223,13 +9276,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480662</v>
+        <v>480624</v>
       </c>
       <c r="R66" t="n">
-        <v>7026812</v>
+        <v>7026760</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9258,7 +9311,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9268,12 +9321,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9305,10 +9358,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124584890</v>
+        <v>124588170</v>
       </c>
       <c r="B67" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9317,45 +9370,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9369,13 +9417,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480617</v>
+        <v>480634</v>
       </c>
       <c r="R67" t="n">
-        <v>7026780</v>
+        <v>7026772</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9404,7 +9452,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9414,12 +9462,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9451,7 +9499,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124583496</v>
+        <v>124583865</v>
       </c>
       <c r="B68" t="n">
         <v>100279</v>
@@ -9490,24 +9538,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480565</v>
+        <v>480592</v>
       </c>
       <c r="R68" t="n">
-        <v>7026797</v>
+        <v>7026811</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9536,7 +9579,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9546,7 +9589,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9578,7 +9621,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124586736</v>
+        <v>124580705</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9613,7 +9656,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9637,13 +9680,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480710</v>
+        <v>480654</v>
       </c>
       <c r="R69" t="n">
-        <v>7026857</v>
+        <v>7026946</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9672,7 +9715,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9682,12 +9725,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9719,10 +9762,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124585658</v>
+        <v>124591111</v>
       </c>
       <c r="B70" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9731,28 +9774,37 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -9769,13 +9821,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480707</v>
+        <v>480594</v>
       </c>
       <c r="R70" t="n">
-        <v>7026812</v>
+        <v>7026755</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9804,7 +9856,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9814,7 +9866,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9846,10 +9903,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124581847</v>
+        <v>124585555</v>
       </c>
       <c r="B71" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9858,31 +9915,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9896,13 +9962,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480610</v>
+        <v>480684</v>
       </c>
       <c r="R71" t="n">
-        <v>7026917</v>
+        <v>7026753</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9931,7 +9997,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9941,7 +10007,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9973,10 +10044,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124581805</v>
+        <v>124578750</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9985,45 +10056,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10032,13 +10089,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480633</v>
+        <v>480662</v>
       </c>
       <c r="R72" t="n">
-        <v>7026927</v>
+        <v>7026990</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10067,7 +10124,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10077,12 +10134,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10114,10 +10166,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124580705</v>
+        <v>124581847</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10126,40 +10178,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10173,13 +10216,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480654</v>
+        <v>480610</v>
       </c>
       <c r="R73" t="n">
-        <v>7026946</v>
+        <v>7026917</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10208,7 +10251,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10218,12 +10261,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10255,10 +10293,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124586809</v>
+        <v>124584501</v>
       </c>
       <c r="B74" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10267,40 +10305,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10310,17 +10348,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480678</v>
+        <v>480613</v>
       </c>
       <c r="R74" t="n">
-        <v>7026830</v>
+        <v>7026805</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10349,7 +10387,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10359,12 +10397,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10396,10 +10434,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124580257</v>
+        <v>124583496</v>
       </c>
       <c r="B75" t="n">
-        <v>56714</v>
+        <v>100279</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10408,45 +10446,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10456,17 +10480,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480661</v>
+        <v>480565</v>
       </c>
       <c r="R75" t="n">
-        <v>7026890</v>
+        <v>7026797</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10495,7 +10519,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10505,12 +10529,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10542,10 +10561,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124593040</v>
+        <v>124586281</v>
       </c>
       <c r="B76" t="n">
-        <v>56722</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10558,41 +10577,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10606,13 +10611,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480614</v>
+        <v>480719</v>
       </c>
       <c r="R76" t="n">
-        <v>7026982</v>
+        <v>7026862</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10641,7 +10646,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10651,12 +10656,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10688,10 +10688,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124585555</v>
+        <v>124586809</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10700,40 +10700,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10743,17 +10743,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480684</v>
+        <v>480678</v>
       </c>
       <c r="R77" t="n">
-        <v>7026753</v>
+        <v>7026830</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10829,7 +10829,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124583407</v>
+        <v>124591424</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10865,7 +10865,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10879,13 +10879,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480522</v>
+        <v>480520</v>
       </c>
       <c r="R78" t="n">
-        <v>7026804</v>
+        <v>7026793</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10981,7 +10981,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124583310</v>
+        <v>124591947</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -11017,7 +11017,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11031,13 +11031,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480524</v>
+        <v>480629</v>
       </c>
       <c r="R79" t="n">
-        <v>7026808</v>
+        <v>7026719</v>
       </c>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11133,7 +11133,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124582743</v>
+        <v>124583745</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -11169,7 +11169,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480571</v>
+        <v>480563</v>
       </c>
       <c r="R80" t="n">
-        <v>7026896</v>
+        <v>7026812</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11285,7 +11285,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124592046</v>
+        <v>124591844</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -11321,7 +11321,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11335,13 +11335,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480633</v>
+        <v>480608</v>
       </c>
       <c r="R81" t="n">
-        <v>7026727</v>
+        <v>7026725</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11437,7 +11437,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124591947</v>
+        <v>124583407</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11487,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480629</v>
+        <v>480522</v>
       </c>
       <c r="R82" t="n">
-        <v>7026719</v>
+        <v>7026804</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124591844</v>
+        <v>124582743</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11625,7 +11625,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480608</v>
+        <v>480571</v>
       </c>
       <c r="R83" t="n">
-        <v>7026725</v>
+        <v>7026896</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124591424</v>
+        <v>124592046</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11777,7 +11777,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480520</v>
+        <v>480633</v>
       </c>
       <c r="R84" t="n">
-        <v>7026793</v>
+        <v>7026727</v>
       </c>
       <c r="S84" t="n">
         <v>7</v>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124583745</v>
+        <v>124583310</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480563</v>
+        <v>480524</v>
       </c>
       <c r="R85" t="n">
-        <v>7026812</v>
+        <v>7026808</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -9076,10 +9076,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124581805</v>
+        <v>124583865</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9088,45 +9088,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9135,13 +9121,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480633</v>
+        <v>480592</v>
       </c>
       <c r="R65" t="n">
-        <v>7026927</v>
+        <v>7026811</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9170,7 +9156,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9180,12 +9166,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9499,10 +9480,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124583865</v>
+        <v>124581805</v>
       </c>
       <c r="B68" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9511,31 +9492,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9544,13 +9539,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480592</v>
+        <v>480633</v>
       </c>
       <c r="R68" t="n">
-        <v>7026811</v>
+        <v>7026927</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9579,7 +9574,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9589,7 +9584,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124582915</v>
+        <v>124585037</v>
       </c>
       <c r="B43" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,40 +6087,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6134,13 +6134,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480596</v>
+        <v>480624</v>
       </c>
       <c r="R43" t="n">
-        <v>7026957</v>
+        <v>7026760</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6179,7 +6179,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6211,7 +6216,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124589882</v>
+        <v>124579158</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -6246,7 +6251,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6270,13 +6275,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480585</v>
+        <v>480668</v>
       </c>
       <c r="R44" t="n">
-        <v>7026859</v>
+        <v>7026971</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6305,7 +6310,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6315,12 +6320,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6352,10 +6357,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124582437</v>
+        <v>124589882</v>
       </c>
       <c r="B45" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6364,41 +6369,60 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480564</v>
+        <v>480585</v>
       </c>
       <c r="R45" t="n">
-        <v>7026877</v>
+        <v>7026859</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6427,7 +6451,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6437,7 +6461,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6469,7 +6498,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124579158</v>
+        <v>124586736</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -6504,7 +6533,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6528,10 +6557,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480668</v>
+        <v>480710</v>
       </c>
       <c r="R46" t="n">
-        <v>7026971</v>
+        <v>7026857</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -6563,7 +6592,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6573,12 +6602,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6610,10 +6639,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124593040</v>
+        <v>124586281</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>105102</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6626,41 +6655,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6674,13 +6689,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480614</v>
+        <v>480719</v>
       </c>
       <c r="R47" t="n">
-        <v>7026982</v>
+        <v>7026862</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6709,7 +6724,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6719,12 +6734,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:52</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6756,10 +6766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124587436</v>
+        <v>124582915</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>58055</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6768,31 +6778,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6801,13 +6825,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480669</v>
+        <v>480596</v>
       </c>
       <c r="R48" t="n">
-        <v>7026780</v>
+        <v>7026957</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6836,7 +6860,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6846,12 +6870,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6866,26 +6885,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6903,7 +6902,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124586736</v>
+        <v>124580705</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6938,7 +6937,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6962,13 +6961,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480710</v>
+        <v>480654</v>
       </c>
       <c r="R49" t="n">
-        <v>7026857</v>
+        <v>7026946</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6997,7 +6996,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7007,12 +7006,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7044,7 +7043,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124590712</v>
+        <v>124587258</v>
       </c>
       <c r="B50" t="n">
         <v>100279</v>
@@ -7094,13 +7093,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480584</v>
+        <v>480668</v>
       </c>
       <c r="R50" t="n">
-        <v>7026737</v>
+        <v>7026796</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7129,7 +7128,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7139,7 +7138,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7171,10 +7170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124580257</v>
+        <v>124589389</v>
       </c>
       <c r="B51" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7183,45 +7182,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7231,17 +7225,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480661</v>
+        <v>480597</v>
       </c>
       <c r="R51" t="n">
-        <v>7026890</v>
+        <v>7026837</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7270,7 +7264,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7280,12 +7274,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7317,7 +7311,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124582374</v>
+        <v>124587192</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7352,7 +7346,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7376,13 +7370,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480614</v>
+        <v>480662</v>
       </c>
       <c r="R52" t="n">
-        <v>7026910</v>
+        <v>7026812</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7411,7 +7405,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7421,12 +7415,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7458,7 +7452,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124580022</v>
+        <v>124581805</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -7493,7 +7487,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>109</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7517,13 +7511,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480658</v>
+        <v>480633</v>
       </c>
       <c r="R53" t="n">
         <v>7026927</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7552,7 +7546,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7562,12 +7556,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7599,7 +7593,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124587192</v>
+        <v>124582374</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -7634,7 +7628,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7658,13 +7652,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480662</v>
+        <v>480614</v>
       </c>
       <c r="R54" t="n">
-        <v>7026812</v>
+        <v>7026910</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7693,7 +7687,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7703,12 +7697,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7740,10 +7734,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124585986</v>
+        <v>124583496</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7752,40 +7746,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7799,13 +7784,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480716</v>
+        <v>480565</v>
       </c>
       <c r="R55" t="n">
-        <v>7026818</v>
+        <v>7026797</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7834,7 +7819,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7844,12 +7829,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7881,10 +7861,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124591241</v>
+        <v>124588640</v>
       </c>
       <c r="B56" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7893,28 +7873,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7926,13 +7920,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480551</v>
+        <v>480649</v>
       </c>
       <c r="R56" t="n">
-        <v>7026795</v>
+        <v>7026845</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7961,7 +7955,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7971,7 +7965,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8003,10 +8002,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124588640</v>
+        <v>124587436</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8015,45 +8014,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8062,10 +8047,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480649</v>
+        <v>480669</v>
       </c>
       <c r="R57" t="n">
-        <v>7026845</v>
+        <v>7026780</v>
       </c>
       <c r="S57" t="n">
         <v>8</v>
@@ -8097,7 +8082,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8107,12 +8092,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8127,6 +8112,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8144,7 +8149,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124585658</v>
+        <v>124581847</v>
       </c>
       <c r="B58" t="n">
         <v>100279</v>
@@ -8180,7 +8185,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8194,10 +8199,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480707</v>
+        <v>480610</v>
       </c>
       <c r="R58" t="n">
-        <v>7026812</v>
+        <v>7026917</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -8229,7 +8234,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8239,7 +8244,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8271,10 +8276,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124589949</v>
+        <v>124580022</v>
       </c>
       <c r="B59" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8283,31 +8288,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8321,13 +8335,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480553</v>
+        <v>480658</v>
       </c>
       <c r="R59" t="n">
-        <v>7026841</v>
+        <v>7026927</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8356,7 +8370,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8366,7 +8380,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8398,10 +8417,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124591533</v>
+        <v>124591111</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8410,38 +8429,57 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480527</v>
+        <v>480594</v>
       </c>
       <c r="R60" t="n">
-        <v>7026752</v>
+        <v>7026755</v>
       </c>
       <c r="S60" t="n">
         <v>8</v>
@@ -8473,7 +8511,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8483,7 +8521,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8498,26 +8541,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8535,10 +8558,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124585231</v>
+        <v>124588170</v>
       </c>
       <c r="B61" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8547,31 +8570,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8585,13 +8617,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480686</v>
+        <v>480634</v>
       </c>
       <c r="R61" t="n">
-        <v>7026765</v>
+        <v>7026772</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8620,7 +8652,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8630,7 +8662,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8662,7 +8699,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124587258</v>
+        <v>124589949</v>
       </c>
       <c r="B62" t="n">
         <v>100279</v>
@@ -8712,13 +8749,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480668</v>
+        <v>480553</v>
       </c>
       <c r="R62" t="n">
-        <v>7026796</v>
+        <v>7026841</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8747,7 +8784,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8757,7 +8794,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8789,10 +8826,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124589389</v>
+        <v>124593040</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8801,40 +8838,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8848,10 +8890,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480597</v>
+        <v>480614</v>
       </c>
       <c r="R63" t="n">
-        <v>7026837</v>
+        <v>7026982</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -8883,7 +8925,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8893,12 +8935,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8930,10 +8972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124584890</v>
+        <v>124585986</v>
       </c>
       <c r="B64" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8942,45 +8984,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8994,13 +9031,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480617</v>
+        <v>480716</v>
       </c>
       <c r="R64" t="n">
-        <v>7026780</v>
+        <v>7026818</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9029,7 +9066,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9039,12 +9076,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9076,7 +9113,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124583865</v>
+        <v>124585231</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -9115,19 +9152,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480592</v>
+        <v>480686</v>
       </c>
       <c r="R65" t="n">
-        <v>7026811</v>
+        <v>7026765</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9156,7 +9198,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9166,7 +9208,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9198,10 +9240,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124585037</v>
+        <v>124591241</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9210,42 +9252,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9257,13 +9285,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480624</v>
+        <v>480551</v>
       </c>
       <c r="R66" t="n">
-        <v>7026760</v>
+        <v>7026795</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9292,7 +9320,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9302,12 +9330,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9339,7 +9362,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124588170</v>
+        <v>124584501</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9374,7 +9397,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9398,13 +9421,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480634</v>
+        <v>480613</v>
       </c>
       <c r="R67" t="n">
-        <v>7026772</v>
+        <v>7026805</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9433,7 +9456,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9443,12 +9466,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9480,10 +9503,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124581805</v>
+        <v>124578750</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9492,45 +9515,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9539,13 +9548,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480633</v>
+        <v>480662</v>
       </c>
       <c r="R68" t="n">
-        <v>7026927</v>
+        <v>7026990</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9574,7 +9583,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9584,12 +9593,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9621,7 +9625,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124580705</v>
+        <v>124585555</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9656,7 +9660,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9680,13 +9684,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480654</v>
+        <v>480684</v>
       </c>
       <c r="R69" t="n">
-        <v>7026946</v>
+        <v>7026753</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9715,7 +9719,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9725,12 +9729,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9762,10 +9766,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124591111</v>
+        <v>124591533</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9774,57 +9778,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480594</v>
+        <v>480527</v>
       </c>
       <c r="R70" t="n">
-        <v>7026755</v>
+        <v>7026752</v>
       </c>
       <c r="S70" t="n">
         <v>8</v>
@@ -9856,7 +9841,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9866,12 +9851,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9886,6 +9866,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9903,10 +9903,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124585555</v>
+        <v>124580257</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9915,40 +9915,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9958,17 +9963,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480684</v>
+        <v>480661</v>
       </c>
       <c r="R71" t="n">
-        <v>7026753</v>
+        <v>7026890</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9997,7 +10002,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10007,12 +10012,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10044,10 +10049,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124578750</v>
+        <v>124584890</v>
       </c>
       <c r="B72" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10060,27 +10065,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10089,13 +10113,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480662</v>
+        <v>480617</v>
       </c>
       <c r="R72" t="n">
-        <v>7026990</v>
+        <v>7026780</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10124,7 +10148,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10134,7 +10158,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10166,7 +10195,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124581847</v>
+        <v>124585658</v>
       </c>
       <c r="B73" t="n">
         <v>100279</v>
@@ -10202,7 +10231,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10216,10 +10245,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480610</v>
+        <v>480707</v>
       </c>
       <c r="R73" t="n">
-        <v>7026917</v>
+        <v>7026812</v>
       </c>
       <c r="S73" t="n">
         <v>9</v>
@@ -10251,7 +10280,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10261,7 +10290,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10293,10 +10322,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124584501</v>
+        <v>124590712</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10305,40 +10334,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10352,10 +10372,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480613</v>
+        <v>480584</v>
       </c>
       <c r="R74" t="n">
-        <v>7026805</v>
+        <v>7026737</v>
       </c>
       <c r="S74" t="n">
         <v>8</v>
@@ -10387,7 +10407,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10397,12 +10417,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10434,10 +10449,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124583496</v>
+        <v>124582437</v>
       </c>
       <c r="B75" t="n">
-        <v>100279</v>
+        <v>79919</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10450,47 +10465,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480565</v>
+        <v>480564</v>
       </c>
       <c r="R75" t="n">
-        <v>7026797</v>
+        <v>7026877</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10519,7 +10524,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10529,7 +10534,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10561,10 +10566,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124586281</v>
+        <v>124586809</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10573,31 +10578,40 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10607,17 +10621,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480719</v>
+        <v>480678</v>
       </c>
       <c r="R76" t="n">
-        <v>7026862</v>
+        <v>7026830</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10646,7 +10660,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10656,7 +10670,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10688,10 +10707,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124586809</v>
+        <v>124583865</v>
       </c>
       <c r="B77" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10700,60 +10719,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480678</v>
+        <v>480592</v>
       </c>
       <c r="R77" t="n">
-        <v>7026830</v>
+        <v>7026811</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10782,7 +10787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10792,12 +10797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10829,7 +10829,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124591424</v>
+        <v>124582743</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10865,7 +10865,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10879,13 +10879,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480520</v>
+        <v>480571</v>
       </c>
       <c r="R78" t="n">
-        <v>7026793</v>
+        <v>7026896</v>
       </c>
       <c r="S78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10981,7 +10981,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124591947</v>
+        <v>124591844</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -11017,7 +11017,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11031,13 +11031,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480629</v>
+        <v>480608</v>
       </c>
       <c r="R79" t="n">
-        <v>7026719</v>
+        <v>7026725</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11133,7 +11133,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124583745</v>
+        <v>124583407</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -11169,7 +11169,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480563</v>
+        <v>480522</v>
       </c>
       <c r="R80" t="n">
-        <v>7026812</v>
+        <v>7026804</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11285,7 +11285,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124591844</v>
+        <v>124591424</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -11335,13 +11335,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480608</v>
+        <v>480520</v>
       </c>
       <c r="R81" t="n">
-        <v>7026725</v>
+        <v>7026793</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11437,7 +11437,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124583407</v>
+        <v>124591947</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11487,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480522</v>
+        <v>480629</v>
       </c>
       <c r="R82" t="n">
-        <v>7026804</v>
+        <v>7026719</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124582743</v>
+        <v>124583310</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11625,7 +11625,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480571</v>
+        <v>480524</v>
       </c>
       <c r="R83" t="n">
-        <v>7026896</v>
+        <v>7026808</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124583310</v>
+        <v>124583745</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480524</v>
+        <v>480563</v>
       </c>
       <c r="R85" t="n">
-        <v>7026808</v>
+        <v>7026812</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6498,10 +6498,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124586736</v>
+        <v>124582915</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>58055</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6510,40 +6510,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6557,13 +6557,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480710</v>
+        <v>480596</v>
       </c>
       <c r="R46" t="n">
-        <v>7026857</v>
+        <v>7026957</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6602,12 +6602,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6639,10 +6634,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124586281</v>
+        <v>124586736</v>
       </c>
       <c r="B47" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6651,28 +6646,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6689,13 +6693,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480719</v>
+        <v>480710</v>
       </c>
       <c r="R47" t="n">
-        <v>7026862</v>
+        <v>7026857</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6724,7 +6728,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6734,7 +6738,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6766,10 +6775,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124582915</v>
+        <v>124586281</v>
       </c>
       <c r="B48" t="n">
-        <v>58055</v>
+        <v>105102</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6782,36 +6791,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102990</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6825,13 +6825,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480596</v>
+        <v>480719</v>
       </c>
       <c r="R48" t="n">
-        <v>7026957</v>
+        <v>7026862</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124585037</v>
+        <v>124591533</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,60 +6087,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480624</v>
+        <v>480527</v>
       </c>
       <c r="R43" t="n">
-        <v>7026760</v>
+        <v>7026752</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6169,7 +6150,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6179,12 +6160,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6199,6 +6175,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6216,10 +6212,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124579158</v>
+        <v>124589949</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6228,40 +6224,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6275,13 +6262,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480668</v>
+        <v>480553</v>
       </c>
       <c r="R44" t="n">
-        <v>7026971</v>
+        <v>7026841</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6310,7 +6297,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6320,12 +6307,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6357,10 +6339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124589882</v>
+        <v>124590712</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6369,40 +6351,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6416,10 +6389,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480585</v>
+        <v>480584</v>
       </c>
       <c r="R45" t="n">
-        <v>7026859</v>
+        <v>7026737</v>
       </c>
       <c r="S45" t="n">
         <v>8</v>
@@ -6451,7 +6424,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6461,12 +6434,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6498,10 +6466,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124582915</v>
+        <v>124584501</v>
       </c>
       <c r="B46" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6510,40 +6478,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6557,13 +6525,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480596</v>
+        <v>480613</v>
       </c>
       <c r="R46" t="n">
-        <v>7026957</v>
+        <v>7026805</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6592,7 +6560,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6602,7 +6570,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6634,7 +6607,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124586736</v>
+        <v>124580022</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -6669,7 +6642,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6693,10 +6666,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480710</v>
+        <v>480658</v>
       </c>
       <c r="R47" t="n">
-        <v>7026857</v>
+        <v>7026927</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -6728,7 +6701,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6738,12 +6711,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6775,10 +6748,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124586281</v>
+        <v>124591111</v>
       </c>
       <c r="B48" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6787,28 +6760,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6825,13 +6807,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480719</v>
+        <v>480594</v>
       </c>
       <c r="R48" t="n">
-        <v>7026862</v>
+        <v>7026755</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6860,7 +6842,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6870,7 +6852,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6902,7 +6889,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124580705</v>
+        <v>124587192</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6937,7 +6924,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6961,13 +6948,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480654</v>
+        <v>480662</v>
       </c>
       <c r="R49" t="n">
-        <v>7026946</v>
+        <v>7026812</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6996,7 +6983,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7006,12 +6993,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7043,10 +7030,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124587258</v>
+        <v>124593040</v>
       </c>
       <c r="B50" t="n">
-        <v>100279</v>
+        <v>56722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7059,27 +7046,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7093,13 +7094,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480668</v>
+        <v>480614</v>
       </c>
       <c r="R50" t="n">
-        <v>7026796</v>
+        <v>7026982</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7128,7 +7129,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7138,7 +7139,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7170,10 +7176,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124589389</v>
+        <v>124585231</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7182,40 +7188,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7229,13 +7226,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480597</v>
+        <v>480686</v>
       </c>
       <c r="R51" t="n">
-        <v>7026837</v>
+        <v>7026765</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7264,7 +7261,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7274,12 +7271,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7311,10 +7303,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124587192</v>
+        <v>124578750</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7323,45 +7315,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7373,7 +7351,7 @@
         <v>480662</v>
       </c>
       <c r="R52" t="n">
-        <v>7026812</v>
+        <v>7026990</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -7405,7 +7383,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7415,12 +7393,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7452,10 +7425,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124581805</v>
+        <v>124582915</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>58055</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7464,40 +7437,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7511,13 +7484,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480633</v>
+        <v>480596</v>
       </c>
       <c r="R53" t="n">
-        <v>7026927</v>
+        <v>7026957</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7546,7 +7519,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7556,12 +7529,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7593,7 +7561,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124582374</v>
+        <v>124580705</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -7628,7 +7596,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7652,13 +7620,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480614</v>
+        <v>480654</v>
       </c>
       <c r="R54" t="n">
-        <v>7026910</v>
+        <v>7026946</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7687,7 +7655,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7697,12 +7665,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 87 plantor och 7 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7734,10 +7702,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124583496</v>
+        <v>124587436</v>
       </c>
       <c r="B55" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7746,36 +7714,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7784,10 +7747,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480565</v>
+        <v>480669</v>
       </c>
       <c r="R55" t="n">
-        <v>7026797</v>
+        <v>7026780</v>
       </c>
       <c r="S55" t="n">
         <v>8</v>
@@ -7819,7 +7782,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7829,7 +7792,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7844,6 +7812,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7861,7 +7849,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124588640</v>
+        <v>124585986</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -7896,7 +7884,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7920,13 +7908,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480649</v>
+        <v>480716</v>
       </c>
       <c r="R56" t="n">
-        <v>7026845</v>
+        <v>7026818</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7955,7 +7943,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7965,12 +7953,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8002,10 +7990,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124587436</v>
+        <v>124582374</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8014,31 +8002,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8047,13 +8049,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480669</v>
+        <v>480614</v>
       </c>
       <c r="R57" t="n">
-        <v>7026780</v>
+        <v>7026910</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8082,7 +8084,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8092,12 +8094,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8112,26 +8114,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8149,10 +8131,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124581847</v>
+        <v>124586736</v>
       </c>
       <c r="B58" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8161,31 +8143,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8199,10 +8190,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480610</v>
+        <v>480710</v>
       </c>
       <c r="R58" t="n">
-        <v>7026917</v>
+        <v>7026857</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -8234,7 +8225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8244,7 +8235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8276,7 +8272,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124580022</v>
+        <v>124588640</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -8311,7 +8307,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8335,13 +8331,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480658</v>
+        <v>480649</v>
       </c>
       <c r="R59" t="n">
-        <v>7026927</v>
+        <v>7026845</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8370,7 +8366,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8380,12 +8376,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8417,10 +8413,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124591111</v>
+        <v>124583496</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8429,40 +8425,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8476,10 +8463,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480594</v>
+        <v>480565</v>
       </c>
       <c r="R60" t="n">
-        <v>7026755</v>
+        <v>7026797</v>
       </c>
       <c r="S60" t="n">
         <v>8</v>
@@ -8511,7 +8498,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8521,12 +8508,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8558,10 +8540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124588170</v>
+        <v>124585658</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8570,37 +8552,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8617,13 +8590,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480634</v>
+        <v>480707</v>
       </c>
       <c r="R61" t="n">
-        <v>7026772</v>
+        <v>7026812</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8652,7 +8625,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8662,12 +8635,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8699,10 +8667,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124589949</v>
+        <v>124585037</v>
       </c>
       <c r="B62" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8711,31 +8679,40 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8749,13 +8726,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480553</v>
+        <v>480624</v>
       </c>
       <c r="R62" t="n">
-        <v>7026841</v>
+        <v>7026760</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8784,7 +8761,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8794,7 +8771,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8826,10 +8808,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124593040</v>
+        <v>124586809</v>
       </c>
       <c r="B63" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8838,25 +8820,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8864,19 +8846,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8886,17 +8863,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480614</v>
+        <v>480678</v>
       </c>
       <c r="R63" t="n">
-        <v>7026982</v>
+        <v>7026830</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8925,7 +8902,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8935,12 +8912,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8972,7 +8949,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124585986</v>
+        <v>124588170</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -9007,7 +8984,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9031,13 +9008,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480716</v>
+        <v>480634</v>
       </c>
       <c r="R64" t="n">
-        <v>7026818</v>
+        <v>7026772</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9066,7 +9043,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9076,12 +9053,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9113,10 +9090,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124585231</v>
+        <v>124586281</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9129,27 +9106,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9163,13 +9140,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480686</v>
+        <v>480719</v>
       </c>
       <c r="R65" t="n">
-        <v>7026765</v>
+        <v>7026862</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9198,7 +9175,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9208,7 +9185,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9240,10 +9217,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124591241</v>
+        <v>124579158</v>
       </c>
       <c r="B66" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9252,28 +9229,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9285,13 +9276,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480551</v>
+        <v>480668</v>
       </c>
       <c r="R66" t="n">
-        <v>7026795</v>
+        <v>7026971</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9320,7 +9311,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9330,7 +9321,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9362,10 +9358,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124584501</v>
+        <v>124584890</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9374,40 +9370,45 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9421,13 +9422,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480613</v>
+        <v>480617</v>
       </c>
       <c r="R67" t="n">
-        <v>7026805</v>
+        <v>7026780</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9456,7 +9457,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9466,12 +9467,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9503,10 +9504,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124578750</v>
+        <v>124585555</v>
       </c>
       <c r="B68" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9515,31 +9516,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9548,10 +9563,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480662</v>
+        <v>480684</v>
       </c>
       <c r="R68" t="n">
-        <v>7026990</v>
+        <v>7026753</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -9583,7 +9598,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9593,7 +9608,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9625,10 +9645,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124585555</v>
+        <v>124583865</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9637,45 +9657,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9684,13 +9690,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480684</v>
+        <v>480592</v>
       </c>
       <c r="R69" t="n">
-        <v>7026753</v>
+        <v>7026811</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9719,7 +9725,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9729,12 +9735,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9766,10 +9767,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124591533</v>
+        <v>124580257</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9782,37 +9783,61 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480527</v>
+        <v>480661</v>
       </c>
       <c r="R70" t="n">
-        <v>7026752</v>
+        <v>7026890</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9841,7 +9866,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9851,7 +9876,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9866,26 +9896,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9903,10 +9913,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124580257</v>
+        <v>124581847</v>
       </c>
       <c r="B71" t="n">
-        <v>56714</v>
+        <v>100279</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9915,45 +9925,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9963,17 +9959,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480661</v>
+        <v>480610</v>
       </c>
       <c r="R71" t="n">
-        <v>7026890</v>
+        <v>7026917</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10002,7 +9998,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10012,12 +10008,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10049,10 +10040,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124584890</v>
+        <v>124581805</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10061,45 +10052,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10113,13 +10099,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480617</v>
+        <v>480633</v>
       </c>
       <c r="R72" t="n">
-        <v>7026780</v>
+        <v>7026927</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10148,7 +10134,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10158,12 +10144,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10195,10 +10181,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124585658</v>
+        <v>124582437</v>
       </c>
       <c r="B73" t="n">
-        <v>100279</v>
+        <v>79919</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10211,47 +10197,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480707</v>
+        <v>480564</v>
       </c>
       <c r="R73" t="n">
-        <v>7026812</v>
+        <v>7026877</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10280,7 +10256,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10290,7 +10266,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10322,10 +10298,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124590712</v>
+        <v>124589389</v>
       </c>
       <c r="B74" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10334,31 +10310,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10372,10 +10357,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480584</v>
+        <v>480597</v>
       </c>
       <c r="R74" t="n">
-        <v>7026737</v>
+        <v>7026837</v>
       </c>
       <c r="S74" t="n">
         <v>8</v>
@@ -10407,7 +10392,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10417,7 +10402,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10449,10 +10439,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124582437</v>
+        <v>124589882</v>
       </c>
       <c r="B75" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10461,41 +10451,60 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480564</v>
+        <v>480585</v>
       </c>
       <c r="R75" t="n">
-        <v>7026877</v>
+        <v>7026859</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10524,7 +10533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10534,7 +10543,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10566,10 +10580,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124586809</v>
+        <v>124587258</v>
       </c>
       <c r="B76" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10578,40 +10592,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10621,17 +10626,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480678</v>
+        <v>480668</v>
       </c>
       <c r="R76" t="n">
-        <v>7026830</v>
+        <v>7026796</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10660,7 +10665,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10670,12 +10675,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10707,10 +10707,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124583865</v>
+        <v>124591241</v>
       </c>
       <c r="B77" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10723,27 +10723,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10752,13 +10752,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480592</v>
+        <v>480551</v>
       </c>
       <c r="R77" t="n">
-        <v>7026811</v>
+        <v>7026795</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10829,7 +10829,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124582743</v>
+        <v>124592046</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10879,13 +10879,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480571</v>
+        <v>480633</v>
       </c>
       <c r="R78" t="n">
-        <v>7026896</v>
+        <v>7026727</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10981,7 +10981,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124591844</v>
+        <v>124583407</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -11017,7 +11017,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11031,13 +11031,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480608</v>
+        <v>480522</v>
       </c>
       <c r="R79" t="n">
-        <v>7026725</v>
+        <v>7026804</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11133,7 +11133,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124583407</v>
+        <v>124591844</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -11169,7 +11169,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480522</v>
+        <v>480608</v>
       </c>
       <c r="R80" t="n">
-        <v>7026804</v>
+        <v>7026725</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11285,7 +11285,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124591424</v>
+        <v>124583310</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -11335,13 +11335,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480520</v>
+        <v>480524</v>
       </c>
       <c r="R81" t="n">
-        <v>7026793</v>
+        <v>7026808</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11437,7 +11437,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124591947</v>
+        <v>124582743</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11487,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480629</v>
+        <v>480571</v>
       </c>
       <c r="R82" t="n">
-        <v>7026719</v>
+        <v>7026896</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124583310</v>
+        <v>124583745</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480524</v>
+        <v>480563</v>
       </c>
       <c r="R83" t="n">
-        <v>7026808</v>
+        <v>7026812</v>
       </c>
       <c r="S83" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124592046</v>
+        <v>124591947</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480633</v>
+        <v>480629</v>
       </c>
       <c r="R84" t="n">
-        <v>7026727</v>
+        <v>7026719</v>
       </c>
       <c r="S84" t="n">
         <v>7</v>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), några meter upp på en granstam.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124583745</v>
+        <v>124591424</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11943,10 +11943,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480563</v>
+        <v>480520</v>
       </c>
       <c r="R85" t="n">
-        <v>7026812</v>
+        <v>7026793</v>
       </c>
       <c r="S85" t="n">
         <v>7</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124591533</v>
+        <v>124585658</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6087,41 +6087,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480527</v>
+        <v>480707</v>
       </c>
       <c r="R43" t="n">
-        <v>7026752</v>
+        <v>7026812</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6150,7 +6160,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6160,7 +6170,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6175,26 +6185,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6212,7 +6202,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124589949</v>
+        <v>124578750</v>
       </c>
       <c r="B44" t="n">
         <v>100279</v>
@@ -6251,24 +6241,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480553</v>
+        <v>480662</v>
       </c>
       <c r="R44" t="n">
-        <v>7026841</v>
+        <v>7026990</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6297,7 +6282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6307,7 +6292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6339,10 +6324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124590712</v>
+        <v>124584890</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6355,27 +6340,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6389,13 +6388,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480584</v>
+        <v>480617</v>
       </c>
       <c r="R45" t="n">
-        <v>7026737</v>
+        <v>7026780</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6424,7 +6423,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6434,7 +6433,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6466,7 +6470,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124584501</v>
+        <v>124588640</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -6501,7 +6505,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6525,10 +6529,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480613</v>
+        <v>480649</v>
       </c>
       <c r="R46" t="n">
-        <v>7026805</v>
+        <v>7026845</v>
       </c>
       <c r="S46" t="n">
         <v>8</v>
@@ -6560,7 +6564,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6570,12 +6574,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
+          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6607,7 +6611,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124580022</v>
+        <v>124589882</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -6642,7 +6646,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6666,13 +6670,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480658</v>
+        <v>480585</v>
       </c>
       <c r="R47" t="n">
-        <v>7026927</v>
+        <v>7026859</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6701,7 +6705,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6711,12 +6715,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
+          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6748,10 +6752,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124591111</v>
+        <v>124585231</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6760,40 +6764,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6807,13 +6802,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480594</v>
+        <v>480686</v>
       </c>
       <c r="R48" t="n">
-        <v>7026755</v>
+        <v>7026765</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6842,7 +6837,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6852,12 +6847,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6889,7 +6879,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124587192</v>
+        <v>124582374</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6924,7 +6914,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6948,13 +6938,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480662</v>
+        <v>480614</v>
       </c>
       <c r="R49" t="n">
-        <v>7026812</v>
+        <v>7026910</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6983,7 +6973,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6993,12 +6983,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
+          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7030,10 +7020,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124593040</v>
+        <v>124585986</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7042,45 +7032,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7094,13 +7079,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480614</v>
+        <v>480716</v>
       </c>
       <c r="R50" t="n">
-        <v>7026982</v>
+        <v>7026818</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7129,7 +7114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7139,12 +7124,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
+          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7176,7 +7161,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124585231</v>
+        <v>124583496</v>
       </c>
       <c r="B51" t="n">
         <v>100279</v>
@@ -7226,13 +7211,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480686</v>
+        <v>480565</v>
       </c>
       <c r="R51" t="n">
-        <v>7026765</v>
+        <v>7026797</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7261,7 +7246,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7271,7 +7256,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7303,10 +7288,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124578750</v>
+        <v>124582437</v>
       </c>
       <c r="B52" t="n">
-        <v>100279</v>
+        <v>79919</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7319,42 +7304,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480662</v>
+        <v>480564</v>
       </c>
       <c r="R52" t="n">
-        <v>7026990</v>
+        <v>7026877</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7383,7 +7363,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7393,7 +7373,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7425,10 +7405,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124582915</v>
+        <v>124587192</v>
       </c>
       <c r="B53" t="n">
-        <v>58055</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7437,40 +7417,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7484,13 +7464,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480596</v>
+        <v>480662</v>
       </c>
       <c r="R53" t="n">
-        <v>7026957</v>
+        <v>7026812</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7519,7 +7499,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7529,7 +7509,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 5 m2 runt en tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7702,7 +7687,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124587436</v>
+        <v>124591533</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -7736,21 +7721,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480669</v>
+        <v>480527</v>
       </c>
       <c r="R55" t="n">
-        <v>7026780</v>
+        <v>7026752</v>
       </c>
       <c r="S55" t="n">
         <v>8</v>
@@ -7782,7 +7762,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7792,12 +7772,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7826,12 +7801,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7849,10 +7824,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124585986</v>
+        <v>124583865</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7861,45 +7836,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7908,13 +7869,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480716</v>
+        <v>480592</v>
       </c>
       <c r="R56" t="n">
-        <v>7026818</v>
+        <v>7026811</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7943,7 +7904,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7953,12 +7914,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 75 plantor och 5 vinterståndare inom ca 4 m2 yta intill en mossöverväxt blocksamling.</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7990,10 +7946,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124582374</v>
+        <v>124587436</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8002,45 +7958,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8049,13 +7991,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480614</v>
+        <v>480669</v>
       </c>
       <c r="R57" t="n">
-        <v>7026910</v>
+        <v>7026780</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8084,7 +8026,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8094,12 +8036,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 200 plantor och 4 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8114,6 +8056,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8131,7 +8093,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124586736</v>
+        <v>124579158</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8166,7 +8128,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8190,10 +8152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480710</v>
+        <v>480668</v>
       </c>
       <c r="R58" t="n">
-        <v>7026857</v>
+        <v>7026971</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -8225,7 +8187,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8235,12 +8197,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8272,7 +8234,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124588640</v>
+        <v>124588170</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -8307,7 +8269,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8331,13 +8293,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480649</v>
+        <v>480634</v>
       </c>
       <c r="R59" t="n">
-        <v>7026845</v>
+        <v>7026772</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8366,7 +8328,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8376,12 +8338,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 47 plantor och 6 vinterståndare inom ca 3 x 1 m2 yta.</t>
+          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8413,10 +8375,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124583496</v>
+        <v>124586736</v>
       </c>
       <c r="B60" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8425,31 +8387,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8463,13 +8434,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480565</v>
+        <v>480710</v>
       </c>
       <c r="R60" t="n">
-        <v>7026797</v>
+        <v>7026857</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8498,7 +8469,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8508,7 +8479,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor och 3 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8540,10 +8516,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124585658</v>
+        <v>124585555</v>
       </c>
       <c r="B61" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8552,28 +8528,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8590,13 +8575,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480707</v>
+        <v>480684</v>
       </c>
       <c r="R61" t="n">
-        <v>7026812</v>
+        <v>7026753</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8625,7 +8610,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8635,7 +8620,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8667,10 +8657,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124585037</v>
+        <v>124586281</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8679,37 +8669,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8726,13 +8707,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480624</v>
+        <v>480719</v>
       </c>
       <c r="R62" t="n">
-        <v>7026760</v>
+        <v>7026862</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8761,7 +8742,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8771,12 +8752,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8808,10 +8784,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124586809</v>
+        <v>124582915</v>
       </c>
       <c r="B63" t="n">
-        <v>57529</v>
+        <v>58055</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8820,20 +8796,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>102990</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8863,17 +8839,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480678</v>
+        <v>480596</v>
       </c>
       <c r="R63" t="n">
-        <v>7026830</v>
+        <v>7026957</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8902,7 +8878,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8912,12 +8888,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Både ljudlig sång och trummande.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8949,10 +8920,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124588170</v>
+        <v>124581847</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8961,40 +8932,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9008,13 +8970,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480634</v>
+        <v>480610</v>
       </c>
       <c r="R64" t="n">
-        <v>7026772</v>
+        <v>7026917</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9043,7 +9005,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9053,12 +9015,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor och 9 vinterståndare inom ca 5 m2 yta.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9090,10 +9047,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124586281</v>
+        <v>124580022</v>
       </c>
       <c r="B65" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9102,28 +9059,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -9140,13 +9106,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480719</v>
+        <v>480658</v>
       </c>
       <c r="R65" t="n">
-        <v>7026862</v>
+        <v>7026927</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9175,7 +9141,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9185,7 +9151,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor och 4 vinterståndare inom ca 2 x 1 m2 yta i en lucka i skogen med gräsinslag och vinterståndare av annan orkidéart (ev. grönkulla).</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9217,10 +9188,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124579158</v>
+        <v>124587258</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9229,40 +9200,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9279,10 +9241,10 @@
         <v>480668</v>
       </c>
       <c r="R66" t="n">
-        <v>7026971</v>
+        <v>7026796</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9311,7 +9273,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9321,12 +9283,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 105 plantor och 10 vinterståndare inom ca 4 m2 yta.</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9358,10 +9315,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124584890</v>
+        <v>124591111</v>
       </c>
       <c r="B67" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9370,45 +9327,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9422,13 +9374,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480617</v>
+        <v>480594</v>
       </c>
       <c r="R67" t="n">
-        <v>7026780</v>
+        <v>7026755</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9457,7 +9409,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9467,12 +9419,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad barrblandskog.</t>
+          <t>Minst 17 plantor inom ca 0,3 m2 yta intill en gammal mossöverväxt stubbe nära en myrstack vid en stig.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9504,7 +9456,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124585555</v>
+        <v>124585037</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -9539,7 +9491,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9563,13 +9515,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480684</v>
+        <v>480624</v>
       </c>
       <c r="R68" t="n">
-        <v>7026753</v>
+        <v>7026760</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9598,7 +9550,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9608,12 +9560,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 8 vinterståndare inom ca 1 m2 yta intill ett mossöverväxt stenblock.</t>
+          <t>Minst 32 plantor inom ca 0,5 m2 yta intill en tall och en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9645,10 +9597,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124583865</v>
+        <v>124584501</v>
       </c>
       <c r="B69" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9657,31 +9609,45 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9690,13 +9656,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480592</v>
+        <v>480613</v>
       </c>
       <c r="R69" t="n">
-        <v>7026811</v>
+        <v>7026805</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9725,7 +9691,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9735,7 +9701,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 5 vinterståndare inom ca 4 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9767,10 +9738,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124580257</v>
+        <v>124581805</v>
       </c>
       <c r="B70" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9779,45 +9750,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9827,17 +9793,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
+          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480661</v>
+        <v>480633</v>
       </c>
       <c r="R70" t="n">
-        <v>7026890</v>
+        <v>7026927</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9866,7 +9832,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9876,12 +9842,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Observerad i äldre flerskiktad barrblandskog.</t>
+          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9913,7 +9879,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124581847</v>
+        <v>124590712</v>
       </c>
       <c r="B71" t="n">
         <v>100279</v>
@@ -9963,13 +9929,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480610</v>
+        <v>480584</v>
       </c>
       <c r="R71" t="n">
-        <v>7026917</v>
+        <v>7026737</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9998,7 +9964,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10008,7 +9974,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10040,10 +10006,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124581805</v>
+        <v>124580257</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10052,40 +10018,45 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10095,17 +10066,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480633</v>
+        <v>480661</v>
       </c>
       <c r="R72" t="n">
-        <v>7026927</v>
+        <v>7026890</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10134,7 +10105,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10144,12 +10115,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 109 plantor och 8 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Observerad i äldre flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10181,10 +10152,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124582437</v>
+        <v>124589389</v>
       </c>
       <c r="B73" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10193,41 +10164,60 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480564</v>
+        <v>480597</v>
       </c>
       <c r="R73" t="n">
-        <v>7026877</v>
+        <v>7026837</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10256,7 +10246,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10266,7 +10256,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10298,10 +10293,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124589389</v>
+        <v>124589949</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10310,40 +10305,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10357,13 +10343,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480597</v>
+        <v>480553</v>
       </c>
       <c r="R74" t="n">
-        <v>7026837</v>
+        <v>7026841</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10392,7 +10378,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10402,12 +10388,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 170 plantor och 2 vinterståndare inom ca 2 m2 yta vid en gammal mossöverväxt stubbe.</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10439,10 +10420,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124589882</v>
+        <v>124593040</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10451,40 +10432,45 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10498,10 +10484,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480585</v>
+        <v>480614</v>
       </c>
       <c r="R75" t="n">
-        <v>7026859</v>
+        <v>7026982</v>
       </c>
       <c r="S75" t="n">
         <v>8</v>
@@ -10533,7 +10519,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10543,12 +10529,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 55 plantor och 4 vinterståndare inom ca 0,5 m2 yta intill en gammal mossöverväxt stubbe.</t>
+          <t>Födosökande/vilande tjäderhona som blev skrämd och lyfte.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10580,10 +10566,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124587258</v>
+        <v>124591241</v>
       </c>
       <c r="B76" t="n">
-        <v>100279</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10596,29 +10582,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -10630,10 +10611,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480668</v>
+        <v>480551</v>
       </c>
       <c r="R76" t="n">
-        <v>7026796</v>
+        <v>7026795</v>
       </c>
       <c r="S76" t="n">
         <v>11</v>
@@ -10665,7 +10646,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10675,7 +10656,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10707,10 +10688,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124591241</v>
+        <v>124586809</v>
       </c>
       <c r="B77" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10719,28 +10700,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -10748,17 +10743,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480551</v>
+        <v>480678</v>
       </c>
       <c r="R77" t="n">
-        <v>7026795</v>
+        <v>7026830</v>
       </c>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10787,7 +10782,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10797,7 +10792,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Både ljudlig sång och trummande.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10981,7 +10981,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124583407</v>
+        <v>124583310</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -11017,7 +11017,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11031,13 +11031,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480522</v>
+        <v>480524</v>
       </c>
       <c r="R79" t="n">
-        <v>7026804</v>
+        <v>7026808</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11133,7 +11133,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124591844</v>
+        <v>124591947</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -11169,7 +11169,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480608</v>
+        <v>480629</v>
       </c>
       <c r="R80" t="n">
-        <v>7026725</v>
+        <v>7026719</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
+          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11285,7 +11285,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124583310</v>
+        <v>124583745</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -11335,13 +11335,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480524</v>
+        <v>480563</v>
       </c>
       <c r="R81" t="n">
-        <v>7026808</v>
+        <v>7026812</v>
       </c>
       <c r="S81" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11437,7 +11437,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124582743</v>
+        <v>124583407</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11487,13 +11487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480571</v>
+        <v>480522</v>
       </c>
       <c r="R82" t="n">
-        <v>7026896</v>
+        <v>7026804</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124583745</v>
+        <v>124591844</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480563</v>
+        <v>480608</v>
       </c>
       <c r="R83" t="n">
-        <v>7026812</v>
+        <v>7026725</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en smal gran.</t>
+          <t>Ringhack, äldre (max 10 år), några meter upp på en gran nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11741,7 +11741,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124591947</v>
+        <v>124591424</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11777,7 +11777,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480629</v>
+        <v>480520</v>
       </c>
       <c r="R84" t="n">
-        <v>7026719</v>
+        <v>7026793</v>
       </c>
       <c r="S84" t="n">
         <v>7</v>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, färska (under 5 år gamla), längs några meter på en gran intill en myrstack nära hyggeskanten.</t>
+          <t>Ringhack, äldre, på en smal gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11893,7 +11893,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124591424</v>
+        <v>124582743</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11929,7 +11929,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480520</v>
+        <v>480571</v>
       </c>
       <c r="R85" t="n">
-        <v>7026793</v>
+        <v>7026896</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en smal gran.</t>
+          <t>Savhack (kort ringhack), som bedöms vara skapat inom 5 år tillbaks, vid ca 4 meters höjd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 5073-2025 artfynd.xlsx
+++ b/artfynd/A 5073-2025 artfynd.xlsx
@@ -9879,10 +9879,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124590712</v>
+        <v>124580257</v>
       </c>
       <c r="B71" t="n">
-        <v>100279</v>
+        <v>56714</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9891,31 +9891,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9925,17 +9939,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Per-Olsbodarna, Per-Olsbodarna, Jmt</t>
+          <t>Per-Olsbodarna, Nedre Blekan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480584</v>
+        <v>480661</v>
       </c>
       <c r="R71" t="n">
-        <v>7026737</v>
+        <v>7026890</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9964,7 +9978,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9974,7 +9988,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>11:54</t>
